--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,35 +497,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2128700220578449</v>
+        <v>0.1895993884990348</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1877645774924658</v>
+        <v>0.2128965758215698</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09681935613608007</v>
+        <v>0.076498488927154</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8052029440010022</v>
+        <v>0.8964135384897927</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="3">
@@ -534,32 +534,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1726955524175409</v>
+        <v>0.1863799078182438</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2550049474038672</v>
+        <v>0.1394502454784851</v>
       </c>
       <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0786023016451418</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.05890572813767921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
       <c r="I3" t="n">
-        <v>0.7352728413241967</v>
+        <v>0.8025643705288577</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -571,32 +571,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.155373894144235</v>
+        <v>0.1722449729920567</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2124390411836954</v>
+        <v>0.2117024883225277</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04792471370267602</v>
+        <v>0.06350743649260301</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.832300569993353</v>
+        <v>0.8259050747058545</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.169343241173428</v>
+        <v>0.1743128923182218</v>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2613226798127818</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06181643966256478</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.1744350581792361</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0730931963743295</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.7318322783757218</v>
+        <v>0.794075476273445</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1805565935178201</v>
+        <v>0.01373555658939222</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03546048089762658</v>
+        <v>0.05772983474934443</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06396827197102427</v>
+        <v>0.01403631419907501</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5611059388288644</v>
+        <v>2.631337739190347</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02882494253111246</v>
+        <v>0.1471175553736196</v>
       </c>
       <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02657584683154118</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.1037377805379329</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>0.04627937973001606</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.02400491779231429</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
       <c r="I7" t="n">
-        <v>2.890038601811702</v>
+        <v>0.5085561467031074</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007353381305462209</v>
+        <v>0.009875821513102748</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002282169965660086</v>
+        <v>0.007925353131043219</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006038162562890126</v>
+        <v>0.0108627751643316</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1211253122235236</v>
+        <v>0.84414326112049</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.008424129878328513</v>
+        <v>0.006465707044746236</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004811780800832394</v>
+        <v>0.006999688162288626</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002518326872225341</v>
+        <v>0.009340866100761435</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07263073275152809</v>
+        <v>0.1217566041760496</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -797,31 +797,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006182716946290316</v>
+        <v>0.004256660767050036</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002497602858663936</v>
+        <v>0.00368188004904298</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00101182869482267</v>
+        <v>0.002599188242755779</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1147215263164183</v>
+        <v>0.1549274159863225</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005343970982071787</v>
+        <v>0.004644313470562978</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001307921899287243</v>
+        <v>0.00229197580494917</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003360326777835787</v>
+        <v>0.002496873146861323</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1165284854805528</v>
+        <v>0.1509021465815614</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>11.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004919043110034691</v>
+        <v>0.01392701517609831</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002184962663933855</v>
+        <v>0.01491971142731746</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001144692448092488</v>
+        <v>0.02147053133543304</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1062133481965581</v>
+        <v>0.06476447633751148</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.005656850857799768</v>
+        <v>0.003612716197254826</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001798985109664039</v>
+        <v>0.001602535112577621</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002045982204766994</v>
+        <v>0.0008154266106803254</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06203163285463065</v>
+        <v>0.1109950779114004</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>12.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005496464584536629</v>
+        <v>0.002669730723085642</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003369724241032781</v>
+        <v>0.002315306987611006</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0001839689688576396</v>
+        <v>0.0006945157203728902</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07576149635259721</v>
+        <v>0.1366375884758959</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>13.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004564779790471528</v>
+        <v>0.002881142214388859</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002101403392624198</v>
+        <v>0.003416348129179547</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002619645311444785</v>
+        <v>0.0006429383128874422</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004584920809091564</v>
+        <v>0.08700915294395362</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.005060853163403474</v>
+        <v>0.002168916220725689</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001689073284474706</v>
+        <v>0.001799256851576492</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002566469251876369</v>
+        <v>0.0004894569504430458</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.4372963289827863</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.004529263635511884</v>
+        <v>0.000926177612223676</v>
       </c>
       <c r="D17" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.003592776110369847</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0005797252702846034</v>
+      </c>
+      <c r="H17" t="n">
         <v>19</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.001447406120851198</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.00188215491710213</v>
-      </c>
-      <c r="H17" t="n">
-        <v>13</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.03512771156409134</v>
+        <v>0.3837169217768097</v>
       </c>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>16.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.004721925810051671</v>
+        <v>0.003188477971760697</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001188707301711295</v>
+        <v>0.00166725284638349</v>
       </c>
       <c r="F18" t="n">
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>4.182626249683574e-05</v>
+        <v>0.000282417024415671</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06802057224543567</v>
+        <v>0.06884801987848466</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>16.75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.004652566672927638</v>
+        <v>0.00238196920097417</v>
       </c>
       <c r="D19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.002013273746452132</v>
+      </c>
+      <c r="F19" t="n">
         <v>17</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.001180847607216071</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21</v>
-      </c>
       <c r="G19" t="n">
-        <v>0.0008802553137954416</v>
+        <v>0.0001186848419381326</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06747324440377911</v>
+        <v>0.1049004435149481</v>
       </c>
       <c r="J19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.004662206183007066</v>
+        <v>0.003421955714025784</v>
       </c>
       <c r="D20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.002108636815222021</v>
+      </c>
+      <c r="F20" t="n">
         <v>16</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.001770982514894319</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14</v>
-      </c>
       <c r="G20" t="n">
-        <v>-8.56275263337647e-05</v>
+        <v>0.0002630852770621361</v>
       </c>
       <c r="H20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.06444049026894305</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>17.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.004048317196363302</v>
+        <v>0.002948726526417326</v>
       </c>
       <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.00160249396898531</v>
+      </c>
+      <c r="F21" t="n">
         <v>21</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.001259351757291416</v>
-      </c>
-      <c r="F21" t="n">
-        <v>18</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.0004208432562574749</v>
+        <v>0.0001075392008770382</v>
       </c>
       <c r="H21" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05145270426009407</v>
+        <v>0.08520098426131995</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K21" t="n">
-        <v>18.25</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.004295717768149976</v>
+        <v>0.00356076912017135</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001182660933016564</v>
+        <v>0.002138499160000766</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0009398935353682969</v>
+        <v>-0.0003017517144763948</v>
       </c>
       <c r="H22" t="n">
+        <v>53</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.09533893131514493</v>
+      </c>
+      <c r="J22" t="n">
         <v>16</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.04023718152039546</v>
-      </c>
-      <c r="J22" t="n">
-        <v>17</v>
-      </c>
       <c r="K22" t="n">
-        <v>18.25</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001745806656416192</v>
+        <v>0.001995297701238362</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0008226583014454383</v>
+        <v>0.001195573840022569</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001470228139266006</v>
+        <v>0.001176911602381203</v>
       </c>
       <c r="H23" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.07699352883582034</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>21</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,1145 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000248985607966633</v>
+        <v>0.002831784189687003</v>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0002618755525764824</v>
+        <v>0.001393077784191214</v>
       </c>
       <c r="F24" t="n">
         <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0001109784989616558</v>
+        <v>0.001086721183328443</v>
       </c>
       <c r="H24" t="n">
+        <v>14</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0317247736777615</v>
+      </c>
+      <c r="J24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.003150126612262545</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001203222741841466</v>
+      </c>
+      <c r="F25" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.001708226103672161</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.02771808103828732</v>
+      </c>
+      <c r="J25" t="n">
+        <v>47</v>
+      </c>
+      <c r="K25" t="n">
+        <v>25.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.002133463418664557</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.001272127791727995</v>
+      </c>
+      <c r="F26" t="n">
+        <v>26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0002453289065024289</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.07461436100266861</v>
+      </c>
+      <c r="J26" t="n">
+        <v>27</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.002814191906194162</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.00126940119254888</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0005649273774046559</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.02843002005720718</v>
+      </c>
+      <c r="J27" t="n">
+        <v>46</v>
+      </c>
+      <c r="K27" t="n">
+        <v>28.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.002338953678594916</v>
+      </c>
+      <c r="D28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.001200369173883082</v>
+      </c>
+      <c r="F28" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0004921419944498128</v>
+      </c>
+      <c r="H28" t="n">
+        <v>21</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.0495556552810732</v>
+      </c>
+      <c r="J28" t="n">
+        <v>39</v>
+      </c>
+      <c r="K28" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.002174773169322461</v>
+      </c>
+      <c r="D29" t="n">
+        <v>27</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.001045982881192763</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0002566192068520823</v>
+      </c>
+      <c r="H29" t="n">
+        <v>28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.07881840246990368</v>
+      </c>
+      <c r="J29" t="n">
+        <v>23</v>
+      </c>
+      <c r="K29" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.002134837050977007</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.001277160729039802</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-8.289760053341589e-05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>47</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.0869597385318106</v>
+      </c>
+      <c r="J30" t="n">
+        <v>18</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.002709045200494806</v>
+      </c>
+      <c r="D31" t="n">
+        <v>21</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.001439765033102736</v>
+      </c>
+      <c r="F31" t="n">
         <v>22</v>
       </c>
-      <c r="I24" t="n">
+      <c r="G31" t="n">
+        <v>-0.0002954874911142768</v>
+      </c>
+      <c r="H31" t="n">
+        <v>52</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.07806897311204031</v>
+      </c>
+      <c r="J31" t="n">
+        <v>24</v>
+      </c>
+      <c r="K31" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001964311731130692</v>
+      </c>
+      <c r="D32" t="n">
+        <v>32</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001007145267672297</v>
+      </c>
+      <c r="F32" t="n">
+        <v>40</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0003509782609104839</v>
+      </c>
+      <c r="H32" t="n">
+        <v>23</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.07500992871397116</v>
+      </c>
+      <c r="J32" t="n">
+        <v>26</v>
+      </c>
+      <c r="K32" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001586160837779102</v>
+      </c>
+      <c r="D33" t="n">
+        <v>38</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0007987156867528704</v>
+      </c>
+      <c r="F33" t="n">
+        <v>48</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0003410964696747287</v>
+      </c>
+      <c r="H33" t="n">
+        <v>24</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.08102548883126426</v>
+      </c>
+      <c r="J33" t="n">
+        <v>21</v>
+      </c>
+      <c r="K33" t="n">
+        <v>32.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.002279562527854898</v>
+      </c>
+      <c r="D34" t="n">
+        <v>26</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.001169492161131742</v>
+      </c>
+      <c r="F34" t="n">
+        <v>33</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0002700690732475586</v>
+      </c>
+      <c r="H34" t="n">
+        <v>26</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.01373374091521473</v>
+      </c>
+      <c r="J34" t="n">
+        <v>48</v>
+      </c>
+      <c r="K34" t="n">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001359104839427631</v>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.001185838060400895</v>
+      </c>
+      <c r="F35" t="n">
+        <v>32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0006083250116079908</v>
+      </c>
+      <c r="H35" t="n">
+        <v>18</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.04349804935773127</v>
+      </c>
+      <c r="J35" t="n">
+        <v>43</v>
+      </c>
+      <c r="K35" t="n">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.002367125780258667</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.00133191148165188</v>
+      </c>
+      <c r="F36" t="n">
+        <v>24</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.83680812024112e-05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>44</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.04685155150494591</v>
+      </c>
+      <c r="J36" t="n">
+        <v>41</v>
+      </c>
+      <c r="K36" t="n">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001778947512908662</v>
+      </c>
+      <c r="D37" t="n">
+        <v>36</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.001077908604988344</v>
+      </c>
+      <c r="F37" t="n">
+        <v>36</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0002172060170485879</v>
+      </c>
+      <c r="H37" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.06330762193683892</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34</v>
+      </c>
+      <c r="K37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001815068182513057</v>
+      </c>
+      <c r="D38" t="n">
+        <v>35</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.001066766811210326</v>
+      </c>
+      <c r="F38" t="n">
+        <v>37</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0001090197539356019</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.06614762099327409</v>
+      </c>
+      <c r="J38" t="n">
+        <v>30</v>
+      </c>
+      <c r="K38" t="n">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001718774198605679</v>
+      </c>
+      <c r="D39" t="n">
+        <v>37</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0008419614068759662</v>
+      </c>
+      <c r="F39" t="n">
+        <v>47</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0001118043738159824</v>
+      </c>
+      <c r="H39" t="n">
+        <v>36</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.08468179151501731</v>
+      </c>
+      <c r="J39" t="n">
+        <v>20</v>
+      </c>
+      <c r="K39" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001872026609777217</v>
+      </c>
+      <c r="D40" t="n">
+        <v>34</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.001128491436232877</v>
+      </c>
+      <c r="F40" t="n">
+        <v>34</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.43827438337108e-06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>45</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0660645240209714</v>
+      </c>
+      <c r="J40" t="n">
+        <v>31</v>
+      </c>
+      <c r="K40" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001919842813799432</v>
+      </c>
+      <c r="D41" t="n">
+        <v>33</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.001186911268168921</v>
+      </c>
+      <c r="F41" t="n">
+        <v>31</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.0001528775075287037</v>
+      </c>
+      <c r="H41" t="n">
+        <v>51</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.05789160624387613</v>
+      </c>
+      <c r="J41" t="n">
+        <v>38</v>
+      </c>
+      <c r="K41" t="n">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.00132533566265979</v>
+      </c>
+      <c r="D42" t="n">
+        <v>41</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0009785282428057388</v>
+      </c>
+      <c r="F42" t="n">
+        <v>41</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0001466346449817135</v>
+      </c>
+      <c r="H42" t="n">
+        <v>31</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.03944742758240594</v>
+      </c>
+      <c r="J42" t="n">
+        <v>44</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.001506522590440855</v>
+      </c>
+      <c r="D43" t="n">
+        <v>39</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0009399442045372306</v>
+      </c>
+      <c r="F43" t="n">
+        <v>43</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-8.455425889574153e-05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>48</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.07360700504813256</v>
+      </c>
+      <c r="J43" t="n">
+        <v>28</v>
+      </c>
+      <c r="K43" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.001247224437160192</v>
+      </c>
+      <c r="D44" t="n">
+        <v>42</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0009670203828993465</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0001331909782701035</v>
+      </c>
+      <c r="H44" t="n">
+        <v>33</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.04547430340962144</v>
+      </c>
+      <c r="J44" t="n">
+        <v>42</v>
+      </c>
+      <c r="K44" t="n">
+        <v>39.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0001755422704987392</v>
+      </c>
+      <c r="D45" t="n">
+        <v>49</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.000590661134077099</v>
+      </c>
+      <c r="F45" t="n">
+        <v>50</v>
+      </c>
+      <c r="G45" t="n">
+        <v>9.786120877077752e-05</v>
+      </c>
+      <c r="H45" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.07942924358921877</v>
+      </c>
+      <c r="J45" t="n">
+        <v>22</v>
+      </c>
+      <c r="K45" t="n">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.001212757650961041</v>
+      </c>
+      <c r="D46" t="n">
+        <v>43</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0008903963153521817</v>
+      </c>
+      <c r="F46" t="n">
+        <v>44</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0001135314190647163</v>
+      </c>
+      <c r="H46" t="n">
+        <v>35</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.04801226937526915</v>
+      </c>
+      <c r="J46" t="n">
+        <v>40</v>
+      </c>
+      <c r="K46" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>8.512302449055861e-05</v>
+      </c>
+      <c r="D47" t="n">
+        <v>53</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.001083075854687862</v>
+      </c>
+      <c r="F47" t="n">
+        <v>35</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.368315297419434e-05</v>
+      </c>
+      <c r="H47" t="n">
+        <v>43</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.06016409753460872</v>
+      </c>
+      <c r="J47" t="n">
+        <v>36</v>
+      </c>
+      <c r="K47" t="n">
+        <v>41.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.001081360128776589</v>
+      </c>
+      <c r="D48" t="n">
+        <v>45</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0008733460905374389</v>
+      </c>
+      <c r="F48" t="n">
+        <v>45</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-5.331832821775517e-06</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0615495823953407</v>
+      </c>
+      <c r="J48" t="n">
+        <v>35</v>
+      </c>
+      <c r="K48" t="n">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.001098944777494736</v>
+      </c>
+      <c r="D49" t="n">
+        <v>44</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0008506241691893381</v>
+      </c>
+      <c r="F49" t="n">
+        <v>46</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.0001468207021591006</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.05949283921523474</v>
+      </c>
+      <c r="J49" t="n">
+        <v>37</v>
+      </c>
+      <c r="K49" t="n">
+        <v>44.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0003455470588704608</v>
+      </c>
+      <c r="D50" t="n">
+        <v>47</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.000658463623543061</v>
+      </c>
+      <c r="F50" t="n">
+        <v>49</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0001334733448208669</v>
+      </c>
+      <c r="H50" t="n">
+        <v>32</v>
+      </c>
+      <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" t="n">
-        <v>21.75</v>
+      <c r="J50" t="n">
+        <v>53</v>
+      </c>
+      <c r="K50" t="n">
+        <v>45.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.00024966867261556</v>
+      </c>
+      <c r="D51" t="n">
+        <v>48</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.001020386519460637</v>
+      </c>
+      <c r="F51" t="n">
+        <v>39</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.0001227677575063479</v>
+      </c>
+      <c r="H51" t="n">
+        <v>49</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.004195285673696425</v>
+      </c>
+      <c r="J51" t="n">
+        <v>51</v>
+      </c>
+      <c r="K51" t="n">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0001627048506930618</v>
+      </c>
+      <c r="D52" t="n">
+        <v>50</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0005283516642189685</v>
+      </c>
+      <c r="F52" t="n">
+        <v>51</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0001070521114344247</v>
+      </c>
+      <c r="H52" t="n">
+        <v>39</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.002153536099111397</v>
+      </c>
+      <c r="J52" t="n">
+        <v>52</v>
+      </c>
+      <c r="K52" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0001549947045209417</v>
+      </c>
+      <c r="D53" t="n">
+        <v>51</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0004974821683909026</v>
+      </c>
+      <c r="F53" t="n">
+        <v>52</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6.947384709157233e-05</v>
+      </c>
+      <c r="H53" t="n">
+        <v>41</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.01162991083799847</v>
+      </c>
+      <c r="J53" t="n">
+        <v>49</v>
+      </c>
+      <c r="K53" t="n">
+        <v>48.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>9.050314616939759e-05</v>
+      </c>
+      <c r="D54" t="n">
+        <v>52</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0002772369584139235</v>
+      </c>
+      <c r="F54" t="n">
+        <v>53</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6.30659167733194e-05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>42</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.004676306983799838</v>
+      </c>
+      <c r="J54" t="n">
+        <v>50</v>
+      </c>
+      <c r="K54" t="n">
+        <v>49.25</v>
       </c>
     </row>
   </sheetData>
@@ -1419,35 +2529,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2128700220578449</v>
+        <v>0.1895993884990348</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1877645774924658</v>
+        <v>0.2128965758215698</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09681935613608007</v>
+        <v>0.076498488927154</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8052029440010022</v>
+        <v>0.8964135384897927</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="3">
@@ -1456,32 +2566,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1726955524175409</v>
+        <v>0.1863799078182438</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2550049474038672</v>
+        <v>0.1394502454784851</v>
       </c>
       <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0786023016451418</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.05890572813767921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
       <c r="I3" t="n">
-        <v>0.7352728413241967</v>
+        <v>0.8025643705288577</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -1493,32 +2603,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.155373894144235</v>
+        <v>0.1722449729920567</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2124390411836954</v>
+        <v>0.2117024883225277</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04792471370267602</v>
+        <v>0.06350743649260301</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.832300569993353</v>
+        <v>0.8259050747058545</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -1530,35 +2640,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.169343241173428</v>
+        <v>0.1743128923182218</v>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2613226798127818</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06181643966256478</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.1744350581792361</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0730931963743295</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.7318322783757218</v>
+        <v>0.794075476273445</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -1567,35 +2677,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1805565935178201</v>
+        <v>0.01373555658939222</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03546048089762658</v>
+        <v>0.05772983474934443</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06396827197102427</v>
+        <v>0.01403631419907501</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5611059388288644</v>
+        <v>2.631337739190347</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1604,35 +2714,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02882494253111246</v>
+        <v>0.1471175553736196</v>
       </c>
       <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02657584683154118</v>
+      </c>
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.1037377805379329</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>0.04627937973001606</v>
+      </c>
+      <c r="H7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.02400491779231429</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6</v>
-      </c>
       <c r="I7" t="n">
-        <v>2.890038601811702</v>
+        <v>0.5085561467031074</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="8">
@@ -1641,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007353381305462209</v>
+        <v>0.009875821513102748</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002282169965660086</v>
+        <v>0.007925353131043219</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006038162562890126</v>
+        <v>0.0108627751643316</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1211253122235236</v>
+        <v>0.84414326112049</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
@@ -1678,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.008424129878328513</v>
+        <v>0.006465707044746236</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004811780800832394</v>
+        <v>0.006999688162288626</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002518326872225341</v>
+        <v>0.009340866100761435</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07263073275152809</v>
+        <v>0.1217566041760496</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1719,31 +2829,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006182716946290316</v>
+        <v>0.004256660767050036</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002497602858663936</v>
+        <v>0.00368188004904298</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00101182869482267</v>
+        <v>0.002599188242755779</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1147215263164183</v>
+        <v>0.1549274159863225</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="11">
@@ -1752,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005343970982071787</v>
+        <v>0.004644313470562978</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001307921899287243</v>
+        <v>0.00229197580494917</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003360326777835787</v>
+        <v>0.002496873146861323</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1165284854805528</v>
+        <v>0.1509021465815614</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>11.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
@@ -1789,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004919043110034691</v>
+        <v>0.01392701517609831</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002184962663933855</v>
+        <v>0.01491971142731746</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001144692448092488</v>
+        <v>0.02147053133543304</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1062133481965581</v>
+        <v>0.06476447633751148</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K12" t="n">
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="13">
@@ -1826,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.005656850857799768</v>
+        <v>0.003612716197254826</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001798985109664039</v>
+        <v>0.001602535112577621</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002045982204766994</v>
+        <v>0.0008154266106803254</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06203163285463065</v>
+        <v>0.1109950779114004</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>12.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="14">
@@ -1863,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005496464584536629</v>
+        <v>0.002669730723085642</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003369724241032781</v>
+        <v>0.002315306987611006</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0001839689688576396</v>
+        <v>0.0006945157203728902</v>
       </c>
       <c r="H14" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07576149635259721</v>
+        <v>0.1366375884758959</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>13.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -1900,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004564779790471528</v>
+        <v>0.002881142214388859</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002101403392624198</v>
+        <v>0.003416348129179547</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002619645311444785</v>
+        <v>0.0006429383128874422</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.004584920809091564</v>
+        <v>0.08700915294395362</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1937,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.005060853163403474</v>
+        <v>0.002168916220725689</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001689073284474706</v>
+        <v>0.001799256851576492</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002566469251876369</v>
+        <v>0.0004894569504430458</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.4372963289827863</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1974,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.004529263635511884</v>
+        <v>0.000926177612223676</v>
       </c>
       <c r="D17" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.003592776110369847</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0005797252702846034</v>
+      </c>
+      <c r="H17" t="n">
         <v>19</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.001447406120851198</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.00188215491710213</v>
-      </c>
-      <c r="H17" t="n">
-        <v>13</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.03512771156409134</v>
+        <v>0.3837169217768097</v>
       </c>
       <c r="J17" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>16.5</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="18">
@@ -2011,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.004721925810051671</v>
+        <v>0.003188477971760697</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001188707301711295</v>
+        <v>0.00166725284638349</v>
       </c>
       <c r="F18" t="n">
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>4.182626249683574e-05</v>
+        <v>0.000282417024415671</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06802057224543567</v>
+        <v>0.06884801987848466</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K18" t="n">
-        <v>16.75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -2048,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.004652566672927638</v>
+        <v>0.00238196920097417</v>
       </c>
       <c r="D19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.002013273746452132</v>
+      </c>
+      <c r="F19" t="n">
         <v>17</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.001180847607216071</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21</v>
-      </c>
       <c r="G19" t="n">
-        <v>0.0008802553137954416</v>
+        <v>0.0001186848419381326</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06747324440377911</v>
+        <v>0.1049004435149481</v>
       </c>
       <c r="J19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="20">
@@ -2085,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.004662206183007066</v>
+        <v>0.003421955714025784</v>
       </c>
       <c r="D20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.002108636815222021</v>
+      </c>
+      <c r="F20" t="n">
         <v>16</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.001770982514894319</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14</v>
-      </c>
       <c r="G20" t="n">
-        <v>-8.56275263337647e-05</v>
+        <v>0.0002630852770621361</v>
       </c>
       <c r="H20" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.06444049026894305</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>17.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="21">
@@ -2122,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.004048317196363302</v>
+        <v>0.002948726526417326</v>
       </c>
       <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.00160249396898531</v>
+      </c>
+      <c r="F21" t="n">
         <v>21</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.001259351757291416</v>
-      </c>
-      <c r="F21" t="n">
-        <v>18</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.0004208432562574749</v>
+        <v>0.0001075392008770382</v>
       </c>
       <c r="H21" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05145270426009407</v>
+        <v>0.08520098426131995</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K21" t="n">
-        <v>18.25</v>
+        <v>23.75</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2190,11 +3300,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2128700220578449</v>
+        <v>0.1895993884990348</v>
       </c>
     </row>
     <row r="3">
@@ -2203,11 +3313,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1805565935178201</v>
+        <v>0.1863799078182438</v>
       </c>
     </row>
     <row r="4">
@@ -2220,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1726955524175409</v>
+        <v>0.1743128923182218</v>
       </c>
     </row>
     <row r="5">
@@ -2229,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.169343241173428</v>
+        <v>0.1722449729920567</v>
       </c>
     </row>
     <row r="6">
@@ -2242,11 +3352,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.155373894144235</v>
+        <v>0.1471175553736196</v>
       </c>
     </row>
     <row r="7">
@@ -2255,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02882494253111246</v>
+        <v>0.01392701517609831</v>
       </c>
     </row>
     <row r="8">
@@ -2268,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.008424129878328513</v>
+        <v>0.01373555658939222</v>
       </c>
     </row>
     <row r="9">
@@ -2281,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007353381305462209</v>
+        <v>0.009875821513102748</v>
       </c>
     </row>
     <row r="10">
@@ -2294,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006182716946290316</v>
+        <v>0.006465707044746236</v>
       </c>
     </row>
     <row r="11">
@@ -2307,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005656850857799768</v>
+        <v>0.004644313470562978</v>
       </c>
     </row>
     <row r="12">
@@ -2320,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005496464584536629</v>
+        <v>0.004256660767050036</v>
       </c>
     </row>
     <row r="13">
@@ -2337,7 +3447,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.005343970982071787</v>
+        <v>0.003612716197254826</v>
       </c>
     </row>
     <row r="14">
@@ -2346,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005060853163403474</v>
+        <v>0.00356076912017135</v>
       </c>
     </row>
     <row r="15">
@@ -2359,11 +3469,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004919043110034691</v>
+        <v>0.003421955714025784</v>
       </c>
     </row>
     <row r="16">
@@ -2372,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.004721925810051671</v>
+        <v>0.003188477971760697</v>
       </c>
     </row>
     <row r="17">
@@ -2385,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.004662206183007066</v>
+        <v>0.003150126612262545</v>
       </c>
     </row>
     <row r="18">
@@ -2398,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.004652566672927638</v>
+        <v>0.002948726526417326</v>
       </c>
     </row>
     <row r="19">
@@ -2411,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.004564779790471528</v>
+        <v>0.002881142214388859</v>
       </c>
     </row>
     <row r="20">
@@ -2424,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.004529263635511884</v>
+        <v>0.002831784189687003</v>
       </c>
     </row>
     <row r="21">
@@ -2437,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.004295717768149976</v>
+        <v>0.002814191906194162</v>
       </c>
     </row>
     <row r="22">
@@ -2450,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.004048317196363302</v>
+        <v>0.002709045200494806</v>
       </c>
     </row>
     <row r="23">
@@ -2463,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000248985607966633</v>
+        <v>0.002669730723085642</v>
       </c>
     </row>
     <row r="24">
@@ -2476,11 +3586,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.00238196920097417</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.002367125780258667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.002338953678594916</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.002279562527854898</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.002174773169322461</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>report_date_day</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.002168916220725689</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.002134837050977007</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.002133463418664557</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001995297701238362</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001964311731130692</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001919842813799432</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001872026609777217</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001815068182513057</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001778947512908662</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001718774198605679</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001586160837779102</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001506522590440855</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001359104839427631</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.00132533566265979</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.001247224437160192</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.001212757650961041</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.001098944777494736</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.001081360128776589</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>report_date_month</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.000926177612223676</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0003455470588704608</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.00024966867261556</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0001755422704987392</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0001627048506930618</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0001549947045209417</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0001745806656416192</v>
+      <c r="C53" t="n">
+        <v>9.050314616939759e-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8.512302449055861e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2550049474038672</v>
+        <v>0.2613226798127818</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2124390411836954</v>
+        <v>0.2128965758215698</v>
       </c>
     </row>
     <row r="4">
@@ -2550,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1877645774924658</v>
+        <v>0.2117024883225277</v>
       </c>
     </row>
     <row r="5">
@@ -2563,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1744350581792361</v>
+        <v>0.1394502454784851</v>
       </c>
     </row>
     <row r="6">
@@ -2576,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1037377805379329</v>
+        <v>0.05772983474934443</v>
       </c>
     </row>
     <row r="7">
@@ -2589,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03546048089762658</v>
+        <v>0.02657584683154118</v>
       </c>
     </row>
     <row r="8">
@@ -2598,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.004811780800832394</v>
+        <v>0.01491971142731746</v>
       </c>
     </row>
     <row r="9">
@@ -2611,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003369724241032781</v>
+        <v>0.007925353131043219</v>
       </c>
     </row>
     <row r="10">
@@ -2624,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002497602858663936</v>
+        <v>0.006999688162288626</v>
       </c>
     </row>
     <row r="11">
@@ -2637,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002282169965660086</v>
+        <v>0.00368188004904298</v>
       </c>
     </row>
     <row r="12">
@@ -2650,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002184962663933855</v>
+        <v>0.003592776110369847</v>
       </c>
     </row>
     <row r="13">
@@ -2663,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002101403392624198</v>
+        <v>0.003416348129179547</v>
       </c>
     </row>
     <row r="14">
@@ -2676,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001798985109664039</v>
+        <v>0.002315306987611006</v>
       </c>
     </row>
     <row r="15">
@@ -2689,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001770982514894319</v>
+        <v>0.00229197580494917</v>
       </c>
     </row>
     <row r="16">
@@ -2702,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001689073284474706</v>
+        <v>0.002138499160000766</v>
       </c>
     </row>
     <row r="17">
@@ -2719,7 +4219,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001447406120851198</v>
+        <v>0.002108636815222021</v>
       </c>
     </row>
     <row r="18">
@@ -2728,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001307921899287243</v>
+        <v>0.002013273746452132</v>
       </c>
     </row>
     <row r="19">
@@ -2741,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001259351757291416</v>
+        <v>0.001799256851576492</v>
       </c>
     </row>
     <row r="20">
@@ -2754,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001188707301711295</v>
+        <v>0.00166725284638349</v>
       </c>
     </row>
     <row r="21">
@@ -2767,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001182660933016564</v>
+        <v>0.001602535112577621</v>
       </c>
     </row>
     <row r="22">
@@ -2780,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001180847607216071</v>
+        <v>0.00160249396898531</v>
       </c>
     </row>
     <row r="23">
@@ -2793,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0008226583014454383</v>
+        <v>0.001439765033102736</v>
       </c>
     </row>
     <row r="24">
@@ -2806,11 +4306,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.001393077784191214</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.00133191148165188</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.001277160729039802</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.001272127791727995</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.00126940119254888</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.001203222741841466</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.001200369173883082</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001195573840022569</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001186911268168921</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001185838060400895</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001169492161131742</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001128491436232877</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001083075854687862</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001077908604988344</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001066766811210326</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001045982881192763</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0002618755525764824</v>
+      <c r="C40" t="n">
+        <v>0.001020386519460637</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001007145267672297</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0009785282428057388</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0009670203828993465</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0009399442045372306</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0008903963153521817</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0008733460905374389</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0008506241691893381</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0008419614068759662</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0007987156867528704</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.000658463623543061</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.000590661134077099</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0005283516642189685</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0004974821683909026</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0002772369584139235</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2855,14 +4745,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09681935613608007</v>
+        <v>0.0786023016451418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01645222337844762</v>
+        <v>0.01247587325798385</v>
       </c>
     </row>
     <row r="3">
@@ -2871,14 +4761,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0730931963743295</v>
+        <v>0.076498488927154</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01292811743276488</v>
+        <v>0.0111318893079271</v>
       </c>
     </row>
     <row r="4">
@@ -2887,14 +4777,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06396827197102427</v>
+        <v>0.06350743649260301</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01307948868612627</v>
+        <v>0.009833519898741981</v>
       </c>
     </row>
     <row r="5">
@@ -2907,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05890572813767921</v>
+        <v>0.06181643966256478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01275290323514349</v>
+        <v>0.009674024373500806</v>
       </c>
     </row>
     <row r="6">
@@ -2919,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04792471370267602</v>
+        <v>0.04627937973001606</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01091848228605446</v>
+        <v>0.00814832919404985</v>
       </c>
     </row>
     <row r="7">
@@ -2935,14 +4825,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02400491779231429</v>
+        <v>0.02147053133543304</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005445118258499703</v>
+        <v>0.002867227169834236</v>
       </c>
     </row>
     <row r="8">
@@ -2951,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006038162562890126</v>
+        <v>0.01403631419907501</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001645270508287588</v>
+        <v>0.003264207197172632</v>
       </c>
     </row>
     <row r="9">
@@ -2967,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003360326777835787</v>
+        <v>0.0108627751643316</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001040721689453628</v>
+        <v>0.001063293966612009</v>
       </c>
     </row>
     <row r="10">
@@ -2983,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002619645311444785</v>
+        <v>0.009340866100761435</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001125912199083516</v>
+        <v>0.00132612628452035</v>
       </c>
     </row>
     <row r="11">
@@ -2999,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002566469251876369</v>
+        <v>0.002599188242755779</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001090951121766948</v>
+        <v>0.001048424422067876</v>
       </c>
     </row>
     <row r="12">
@@ -3015,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002518326872225341</v>
+        <v>0.002496873146861323</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002049332254921119</v>
+        <v>0.001060092833364865</v>
       </c>
     </row>
     <row r="13">
@@ -3031,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002045982204766994</v>
+        <v>0.001708226103672161</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00119383414397655</v>
+        <v>0.0003792613466814832</v>
       </c>
     </row>
     <row r="14">
@@ -3047,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00188215491710213</v>
+        <v>0.001176911602381203</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000390651814649415</v>
+        <v>0.000301656377598539</v>
       </c>
     </row>
     <row r="15">
@@ -3063,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001144692448092488</v>
+        <v>0.001086721183328443</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0006476664634350757</v>
+        <v>0.0005534466286314848</v>
       </c>
     </row>
     <row r="16">
@@ -3079,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00101182869482267</v>
+        <v>0.0008154266106803254</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005564864788654174</v>
+        <v>0.000599927412855309</v>
       </c>
     </row>
     <row r="17">
@@ -3095,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0009398935353682969</v>
+        <v>0.0006945157203728902</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002864683515036186</v>
+        <v>0.0003190097556945896</v>
       </c>
     </row>
     <row r="18">
@@ -3111,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0008802553137954416</v>
+        <v>0.0006429383128874422</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004794313704920435</v>
+        <v>0.0003980646005040217</v>
       </c>
     </row>
     <row r="19">
@@ -3127,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004208432562574749</v>
+        <v>0.0006083250116079908</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0005548434506302549</v>
+        <v>0.000188985070610162</v>
       </c>
     </row>
     <row r="20">
@@ -3143,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0001470228139266006</v>
+        <v>0.0005797252702846034</v>
       </c>
       <c r="D20" t="n">
-        <v>8.03271408118182e-05</v>
+        <v>0.0001364816009534266</v>
       </c>
     </row>
     <row r="21">
@@ -3159,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.182626249683574e-05</v>
+        <v>0.0005649273774046559</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0006275736380283573</v>
+        <v>0.0003847971639680782</v>
       </c>
     </row>
     <row r="22">
@@ -3175,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-8.56275263337647e-05</v>
+        <v>0.0004921419944498128</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0006967988937813982</v>
+        <v>0.0003197093876250444</v>
       </c>
     </row>
     <row r="23">
@@ -3191,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.0001109784989616558</v>
+        <v>0.0004894569504430458</v>
       </c>
       <c r="D23" t="n">
-        <v>5.879560013297241e-05</v>
+        <v>0.000232162427251662</v>
       </c>
     </row>
     <row r="24">
@@ -3207,14 +5097,494 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0003509782609104839</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0002014319633463902</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0003410964696747287</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0001707113490920854</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.000282417024415671</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0005019314448220851</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0002700690732475586</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0001982817009273197</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0002630852770621361</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0004522063131532431</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002566192068520823</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0001839495869689221</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0002453289065024289</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.000184189097662136</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0002172060170485879</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0001679433348069475</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0001466346449817135</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8.705111281042808e-05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0001334733448208669</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.396422697634806e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0001331909782701035</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9.668121772104136e-05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0001186848419381326</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0001766239713753093</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0001135314190647163</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7.966894351280815e-05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0001118043738159824</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0002258424310842761</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0001090197539356019</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0001575667877766174</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0001075392008770382</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0002835892220985219</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0001070521114344247</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5.782955631025041e-05</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9.786120877077752e-05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5.992596384600983e-05</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6.947384709157233e-05</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7.239675991665917e-05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6.30659167733194e-05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.781378163215048e-05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4.368315297419434e-05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.985434012294052e-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3.83680812024112e-05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.0002610280273108268</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8.43827438337108e-06</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8.157963971255147e-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-5.331832821775517e-06</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8.37501071737505e-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-8.289760053341589e-05</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0002350362630497358</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-8.455425889574153e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0001121915011527222</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.0001227677575063479</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7.961533954136406e-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.0001468207021591006</v>
+      </c>
+      <c r="D51" t="n">
+        <v>9.963330108161264e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0001528775075287037</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0002440775868241019</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0002954874911142768</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.0003338176457716292</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>sweetwater_brix</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>-0.0001839689688576396</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0006898829819675362</v>
+      <c r="C54" t="n">
+        <v>-0.0003017517144763948</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0003484399488751379</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.890038601811702</v>
+        <v>2.631337739190347</v>
       </c>
     </row>
     <row r="3">
@@ -3271,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.832300569993353</v>
+        <v>0.8964135384897927</v>
       </c>
     </row>
     <row r="4">
@@ -3280,11 +5650,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8052029440010022</v>
+        <v>0.84414326112049</v>
       </c>
     </row>
     <row r="5">
@@ -3293,11 +5663,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7352728413241967</v>
+        <v>0.8259050747058545</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +5680,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7318322783757218</v>
+        <v>0.8025643705288577</v>
       </c>
     </row>
     <row r="7">
@@ -3319,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5611059388288644</v>
+        <v>0.794075476273445</v>
       </c>
     </row>
     <row r="8">
@@ -3332,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1211253122235236</v>
+        <v>0.5085561467031074</v>
       </c>
     </row>
     <row r="9">
@@ -3345,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1165284854805528</v>
+        <v>0.4372963289827863</v>
       </c>
     </row>
     <row r="10">
@@ -3358,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1147215263164183</v>
+        <v>0.3837169217768097</v>
       </c>
     </row>
     <row r="11">
@@ -3371,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1062133481965581</v>
+        <v>0.1549274159863225</v>
       </c>
     </row>
     <row r="12">
@@ -3384,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.07576149635259721</v>
+        <v>0.1509021465815614</v>
       </c>
     </row>
     <row r="13">
@@ -3397,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.07263073275152809</v>
+        <v>0.1366375884758959</v>
       </c>
     </row>
     <row r="14">
@@ -3410,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.06802057224543567</v>
+        <v>0.1217566041760496</v>
       </c>
     </row>
     <row r="15">
@@ -3423,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.06747324440377911</v>
+        <v>0.1109950779114004</v>
       </c>
     </row>
     <row r="16">
@@ -3436,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.06203163285463065</v>
+        <v>0.1049004435149481</v>
       </c>
     </row>
     <row r="17">
@@ -3449,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.05145270426009407</v>
+        <v>0.09533893131514493</v>
       </c>
     </row>
     <row r="18">
@@ -3462,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.04023718152039546</v>
+        <v>0.08700915294395362</v>
       </c>
     </row>
     <row r="19">
@@ -3475,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03512771156409134</v>
+        <v>0.0869597385318106</v>
       </c>
     </row>
     <row r="20">
@@ -3488,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.004584920809091564</v>
+        <v>0.08520098426131995</v>
       </c>
     </row>
     <row r="21">
@@ -3501,49 +5871,439 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.08468179151501731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.08102548883126426</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.07942924358921877</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.07881840246990368</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.07806897311204031</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.07699352883582034</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.07500992871397116</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.07461436100266861</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.07360700504813256</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.06884801987848466</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.06614762099327409</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0660645240209714</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.06476447633751148</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.06444049026894305</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.06330762193683892</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0615495823953407</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.06016409753460872</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.05949283921523474</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.05789160624387613</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0495556552810732</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.04801226937526915</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.04685155150494591</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.04547430340962144</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.04349804935773127</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.03944742758240594</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0317247736777615</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.02843002005720718</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.02771808103828732</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>standard_liquor_color</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C49" t="n">
+        <v>0.01373374091521473</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.01162991083799847</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.004676306983799838</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.004195285673696425</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.002153536099111397</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,17 +6355,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:47:44 UTC</t>
+          <t>2026-06-11 05:09:00 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.076498488927154</v>
+        <v>0.07649848892715405</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -550,7 +550,7 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0786023016451418</v>
+        <v>0.07860230164514195</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06350743649260301</v>
+        <v>0.0635074364926031</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06181643966256478</v>
+        <v>0.06181643966256491</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403631419907501</v>
+        <v>0.01403631419911995</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04627937973001606</v>
+        <v>0.04627937973001618</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -735,7 +735,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0108627751643316</v>
+        <v>0.0108627751643317</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009340866100761435</v>
+        <v>0.009340866100761546</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002599188242755779</v>
+        <v>0.002599188242755868</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002496873146861323</v>
+        <v>0.002496873146861467</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -883,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02147053133543304</v>
+        <v>0.02147053133543316</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
@@ -920,7 +920,7 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0008154266106803254</v>
+        <v>0.0008154266106804586</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -957,7 +957,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0006945157203728902</v>
+        <v>0.0006945157203729569</v>
       </c>
       <c r="H14" t="n">
         <v>16</v>
@@ -994,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006429383128874422</v>
+        <v>0.0006429383128874977</v>
       </c>
       <c r="H15" t="n">
         <v>17</v>
@@ -1031,7 +1031,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004894569504430458</v>
+        <v>0.0004894569504431456</v>
       </c>
       <c r="H16" t="n">
         <v>22</v>
@@ -1068,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005797252702846034</v>
+        <v>0.0005797252702847144</v>
       </c>
       <c r="H17" t="n">
         <v>19</v>
@@ -1105,7 +1105,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000282417024415671</v>
+        <v>0.0002824170244158042</v>
       </c>
       <c r="H18" t="n">
         <v>25</v>
@@ -1142,7 +1142,7 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001186848419381326</v>
+        <v>0.0001186848419382436</v>
       </c>
       <c r="H19" t="n">
         <v>34</v>
@@ -1179,7 +1179,7 @@
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002630852770621361</v>
+        <v>0.0002630852770622583</v>
       </c>
       <c r="H20" t="n">
         <v>27</v>
@@ -1216,7 +1216,7 @@
         <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001075392008770382</v>
+        <v>0.0001075392008771492</v>
       </c>
       <c r="H21" t="n">
         <v>38</v>
@@ -1253,7 +1253,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0003017517144763948</v>
+        <v>-0.0003017517144762838</v>
       </c>
       <c r="H22" t="n">
         <v>53</v>
@@ -1290,7 +1290,7 @@
         <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001176911602381203</v>
+        <v>0.001176911602381303</v>
       </c>
       <c r="H23" t="n">
         <v>13</v>
@@ -1327,7 +1327,7 @@
         <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001086721183328443</v>
+        <v>0.001086721183328554</v>
       </c>
       <c r="H24" t="n">
         <v>14</v>
@@ -1364,7 +1364,7 @@
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001708226103672161</v>
+        <v>0.001708226103672239</v>
       </c>
       <c r="H25" t="n">
         <v>12</v>
@@ -1401,7 +1401,7 @@
         <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002453289065024289</v>
+        <v>0.0002453289065025177</v>
       </c>
       <c r="H26" t="n">
         <v>29</v>
@@ -1438,7 +1438,7 @@
         <v>27</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0005649273774046559</v>
+        <v>0.0005649273774047225</v>
       </c>
       <c r="H27" t="n">
         <v>20</v>
@@ -1475,7 +1475,7 @@
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0004921419944498128</v>
+        <v>0.0004921419944499239</v>
       </c>
       <c r="H28" t="n">
         <v>21</v>
@@ -1512,7 +1512,7 @@
         <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002566192068520823</v>
+        <v>0.0002566192068522155</v>
       </c>
       <c r="H29" t="n">
         <v>28</v>
@@ -1549,7 +1549,7 @@
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>-8.289760053341589e-05</v>
+        <v>-8.289760053328265e-05</v>
       </c>
       <c r="H30" t="n">
         <v>47</v>
@@ -1586,7 +1586,7 @@
         <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0002954874911142768</v>
+        <v>-0.0002954874911141325</v>
       </c>
       <c r="H31" t="n">
         <v>52</v>
@@ -1623,7 +1623,7 @@
         <v>40</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0003509782609104839</v>
+        <v>0.000350978260910606</v>
       </c>
       <c r="H32" t="n">
         <v>23</v>
@@ -1660,7 +1660,7 @@
         <v>48</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003410964696747287</v>
+        <v>0.0003410964696748398</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1697,7 +1697,7 @@
         <v>33</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0002700690732475586</v>
+        <v>0.0002700690732476807</v>
       </c>
       <c r="H34" t="n">
         <v>26</v>
@@ -1734,7 +1734,7 @@
         <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0006083250116079908</v>
+        <v>0.0006083250116080685</v>
       </c>
       <c r="H35" t="n">
         <v>18</v>
@@ -1771,7 +1771,7 @@
         <v>24</v>
       </c>
       <c r="G36" t="n">
-        <v>3.83680812024112e-05</v>
+        <v>3.836808120251111e-05</v>
       </c>
       <c r="H36" t="n">
         <v>44</v>
@@ -1808,7 +1808,7 @@
         <v>36</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0002172060170485879</v>
+        <v>0.0002172060170486989</v>
       </c>
       <c r="H37" t="n">
         <v>30</v>
@@ -1845,7 +1845,7 @@
         <v>37</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0001090197539356019</v>
+        <v>0.0001090197539357018</v>
       </c>
       <c r="H38" t="n">
         <v>37</v>
@@ -1882,7 +1882,7 @@
         <v>47</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001118043738159824</v>
+        <v>0.0001118043738160712</v>
       </c>
       <c r="H39" t="n">
         <v>36</v>
@@ -1919,7 +1919,7 @@
         <v>34</v>
       </c>
       <c r="G40" t="n">
-        <v>8.43827438337108e-06</v>
+        <v>8.438274383426591e-06</v>
       </c>
       <c r="H40" t="n">
         <v>45</v>
@@ -1956,7 +1956,7 @@
         <v>31</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0001528775075287037</v>
+        <v>-0.0001528775075286259</v>
       </c>
       <c r="H41" t="n">
         <v>51</v>
@@ -1993,7 +1993,7 @@
         <v>41</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001466346449817135</v>
+        <v>0.0001466346449818467</v>
       </c>
       <c r="H42" t="n">
         <v>31</v>
@@ -2030,7 +2030,7 @@
         <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>-8.455425889574153e-05</v>
+        <v>-8.455425889563051e-05</v>
       </c>
       <c r="H43" t="n">
         <v>48</v>
@@ -2067,7 +2067,7 @@
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0001331909782701035</v>
+        <v>0.0001331909782702034</v>
       </c>
       <c r="H44" t="n">
         <v>33</v>
@@ -2104,7 +2104,7 @@
         <v>50</v>
       </c>
       <c r="G45" t="n">
-        <v>9.786120877077752e-05</v>
+        <v>9.786120877085525e-05</v>
       </c>
       <c r="H45" t="n">
         <v>40</v>
@@ -2141,7 +2141,7 @@
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0001135314190647163</v>
+        <v>0.0001135314190648051</v>
       </c>
       <c r="H46" t="n">
         <v>35</v>
@@ -2178,7 +2178,7 @@
         <v>35</v>
       </c>
       <c r="G47" t="n">
-        <v>4.368315297419434e-05</v>
+        <v>4.368315297437197e-05</v>
       </c>
       <c r="H47" t="n">
         <v>43</v>
@@ -2215,7 +2215,7 @@
         <v>45</v>
       </c>
       <c r="G48" t="n">
-        <v>-5.331832821775517e-06</v>
+        <v>-5.331832821675598e-06</v>
       </c>
       <c r="H48" t="n">
         <v>46</v>
@@ -2252,7 +2252,7 @@
         <v>46</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0001468207021591006</v>
+        <v>-0.0001468207021590007</v>
       </c>
       <c r="H49" t="n">
         <v>50</v>
@@ -2289,7 +2289,7 @@
         <v>49</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0001334733448208669</v>
+        <v>0.0001334733448209335</v>
       </c>
       <c r="H50" t="n">
         <v>32</v>
@@ -2326,7 +2326,7 @@
         <v>39</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0001227677575063479</v>
+        <v>-0.0001227677575061925</v>
       </c>
       <c r="H51" t="n">
         <v>49</v>
@@ -2363,7 +2363,7 @@
         <v>51</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0001070521114344247</v>
+        <v>0.0001070521114344913</v>
       </c>
       <c r="H52" t="n">
         <v>39</v>
@@ -2400,7 +2400,7 @@
         <v>52</v>
       </c>
       <c r="G53" t="n">
-        <v>6.947384709157233e-05</v>
+        <v>6.947384709169447e-05</v>
       </c>
       <c r="H53" t="n">
         <v>41</v>
@@ -2437,7 +2437,7 @@
         <v>53</v>
       </c>
       <c r="G54" t="n">
-        <v>6.30659167733194e-05</v>
+        <v>6.306591677343043e-05</v>
       </c>
       <c r="H54" t="n">
         <v>42</v>
@@ -2545,7 +2545,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.076498488927154</v>
+        <v>0.07649848892715405</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -2582,7 +2582,7 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0786023016451418</v>
+        <v>0.07860230164514195</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06350743649260301</v>
+        <v>0.0635074364926031</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06181643966256478</v>
+        <v>0.06181643966256491</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403631419907501</v>
+        <v>0.01403631419911995</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04627937973001606</v>
+        <v>0.04627937973001618</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
@@ -2767,7 +2767,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0108627751643316</v>
+        <v>0.0108627751643317</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009340866100761435</v>
+        <v>0.009340866100761546</v>
       </c>
       <c r="H9" t="n">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002599188242755779</v>
+        <v>0.002599188242755868</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -2878,7 +2878,7 @@
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002496873146861323</v>
+        <v>0.002496873146861467</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -2915,7 +2915,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02147053133543304</v>
+        <v>0.02147053133543316</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
@@ -2952,7 +2952,7 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0008154266106803254</v>
+        <v>0.0008154266106804586</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0006945157203728902</v>
+        <v>0.0006945157203729569</v>
       </c>
       <c r="H14" t="n">
         <v>16</v>
@@ -3026,7 +3026,7 @@
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006429383128874422</v>
+        <v>0.0006429383128874977</v>
       </c>
       <c r="H15" t="n">
         <v>17</v>
@@ -3063,7 +3063,7 @@
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004894569504430458</v>
+        <v>0.0004894569504431456</v>
       </c>
       <c r="H16" t="n">
         <v>22</v>
@@ -3100,7 +3100,7 @@
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005797252702846034</v>
+        <v>0.0005797252702847144</v>
       </c>
       <c r="H17" t="n">
         <v>19</v>
@@ -3137,7 +3137,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000282417024415671</v>
+        <v>0.0002824170244158042</v>
       </c>
       <c r="H18" t="n">
         <v>25</v>
@@ -3174,7 +3174,7 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001186848419381326</v>
+        <v>0.0001186848419382436</v>
       </c>
       <c r="H19" t="n">
         <v>34</v>
@@ -3211,7 +3211,7 @@
         <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002630852770621361</v>
+        <v>0.0002630852770622583</v>
       </c>
       <c r="H20" t="n">
         <v>27</v>
@@ -3248,7 +3248,7 @@
         <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001075392008770382</v>
+        <v>0.0001075392008771492</v>
       </c>
       <c r="H21" t="n">
         <v>38</v>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0786023016451418</v>
+        <v>0.07860230164514195</v>
       </c>
       <c r="D2" t="n">
         <v>0.01247587325798385</v>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.076498488927154</v>
+        <v>0.07649848892715405</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0111318893079271</v>
+        <v>0.01113188930792712</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06350743649260301</v>
+        <v>0.0635074364926031</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009833519898741981</v>
+        <v>0.009833519898741983</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06181643966256478</v>
+        <v>0.06181643966256491</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009674024373500806</v>
+        <v>0.009674024373500815</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04627937973001606</v>
+        <v>0.04627937973001618</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00814832919404985</v>
+        <v>0.008148329194049821</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02147053133543304</v>
+        <v>0.02147053133543316</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002867227169834236</v>
+        <v>0.002867227169834253</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01403631419907501</v>
+        <v>0.01403631419911995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003264207197172632</v>
+        <v>0.003264207197172888</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0108627751643316</v>
+        <v>0.0108627751643317</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001063293966612009</v>
+        <v>0.00106329396661205</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009340866100761435</v>
+        <v>0.009340866100761546</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00132612628452035</v>
+        <v>0.001326126284520369</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002599188242755779</v>
+        <v>0.002599188242755868</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001048424422067876</v>
+        <v>0.001048424422067855</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002496873146861323</v>
+        <v>0.002496873146861467</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001060092833364865</v>
+        <v>0.001060092833364844</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001708226103672161</v>
+        <v>0.001708226103672239</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003792613466814832</v>
+        <v>0.0003792613466815153</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001176911602381203</v>
+        <v>0.001176911602381303</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000301656377598539</v>
+        <v>0.0003016563775985857</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001086721183328443</v>
+        <v>0.001086721183328554</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0005534466286314848</v>
+        <v>0.0005534466286314996</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008154266106803254</v>
+        <v>0.0008154266106804586</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000599927412855309</v>
+        <v>0.0005999274128553415</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0006945157203728902</v>
+        <v>0.0006945157203729569</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003190097556945896</v>
+        <v>0.0003190097556946082</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0006429383128874422</v>
+        <v>0.0006429383128874977</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0003980646005040217</v>
+        <v>0.0003980646005040254</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006083250116079908</v>
+        <v>0.0006083250116080685</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000188985070610162</v>
+        <v>0.0001889850706101278</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005797252702846034</v>
+        <v>0.0005797252702847144</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001364816009534266</v>
+        <v>0.0001364816009534143</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005649273774046559</v>
+        <v>0.0005649273774047225</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0003847971639680782</v>
+        <v>0.0003847971639680674</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004921419944498128</v>
+        <v>0.0004921419944499239</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003197093876250444</v>
+        <v>0.0003197093876250583</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004894569504430458</v>
+        <v>0.0004894569504431456</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000232162427251662</v>
+        <v>0.0002321624272516576</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003509782609104839</v>
+        <v>0.000350978260910606</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0002014319633463902</v>
+        <v>0.0002014319633464083</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003410964696747287</v>
+        <v>0.0003410964696748398</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001707113490920854</v>
+        <v>0.0001707113490920687</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.000282417024415671</v>
+        <v>0.0002824170244158042</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0005019314448220851</v>
+        <v>0.0005019314448220945</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002700690732475586</v>
+        <v>0.0002700690732476807</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001982817009273197</v>
+        <v>0.0001982817009273181</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002630852770621361</v>
+        <v>0.0002630852770622583</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0004522063131532431</v>
+        <v>0.0004522063131532384</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002566192068520823</v>
+        <v>0.0002566192068522155</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001839495869689221</v>
+        <v>0.0001839495869689226</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002453289065024289</v>
+        <v>0.0002453289065025177</v>
       </c>
       <c r="D30" t="n">
-        <v>0.000184189097662136</v>
+        <v>0.000184189097662153</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002172060170485879</v>
+        <v>0.0002172060170486989</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001679433348069475</v>
+        <v>0.0001679433348069088</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001466346449817135</v>
+        <v>0.0001466346449818467</v>
       </c>
       <c r="D32" t="n">
-        <v>8.705111281042808e-05</v>
+        <v>8.705111281041989e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001334733448208669</v>
+        <v>0.0001334733448209335</v>
       </c>
       <c r="D33" t="n">
-        <v>3.396422697634806e-05</v>
+        <v>3.396422697634077e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001331909782701035</v>
+        <v>0.0001331909782702034</v>
       </c>
       <c r="D34" t="n">
-        <v>9.668121772104136e-05</v>
+        <v>9.668121772100634e-05</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001186848419381326</v>
+        <v>0.0001186848419382436</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001766239713753093</v>
+        <v>0.0001766239713753026</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001135314190647163</v>
+        <v>0.0001135314190648051</v>
       </c>
       <c r="D36" t="n">
-        <v>7.966894351280815e-05</v>
+        <v>7.966894351275279e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001118043738159824</v>
+        <v>0.0001118043738160712</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0002258424310842761</v>
+        <v>0.0002258424310842831</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001090197539356019</v>
+        <v>0.0001090197539357018</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001575667877766174</v>
+        <v>0.0001575667877766118</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0001075392008770382</v>
+        <v>0.0001075392008771492</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0002835892220985219</v>
+        <v>0.0002835892220985357</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0001070521114344247</v>
+        <v>0.0001070521114344913</v>
       </c>
       <c r="D40" t="n">
-        <v>5.782955631025041e-05</v>
+        <v>5.782955631025541e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9.786120877077752e-05</v>
+        <v>9.786120877085525e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>5.992596384600983e-05</v>
+        <v>5.992596384599741e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.947384709157233e-05</v>
+        <v>6.947384709169447e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>7.239675991665917e-05</v>
+        <v>7.23967599166721e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.30659167733194e-05</v>
+        <v>6.306591677343043e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>1.781378163215048e-05</v>
+        <v>1.781378163219343e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.368315297419434e-05</v>
+        <v>4.368315297437197e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>1.985434012294052e-05</v>
+        <v>1.985434012297735e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.83680812024112e-05</v>
+        <v>3.836808120251111e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002610280273108268</v>
+        <v>0.0002610280273108099</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.43827438337108e-06</v>
+        <v>8.438274383426591e-06</v>
       </c>
       <c r="D46" t="n">
-        <v>8.157963971255147e-05</v>
+        <v>8.157963971252458e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-5.331832821775517e-06</v>
+        <v>-5.331832821675598e-06</v>
       </c>
       <c r="D47" t="n">
-        <v>8.37501071737505e-05</v>
+        <v>8.375010717378523e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-8.289760053341589e-05</v>
+        <v>-8.289760053328265e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0002350362630497358</v>
+        <v>0.0002350362630497555</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-8.455425889574153e-05</v>
+        <v>-8.455425889563051e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0001121915011527222</v>
+        <v>0.0001121915011527019</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001227677575063479</v>
+        <v>-0.0001227677575061925</v>
       </c>
       <c r="D50" t="n">
-        <v>7.961533954136406e-05</v>
+        <v>7.961533954136952e-05</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001468207021591006</v>
+        <v>-0.0001468207021590007</v>
       </c>
       <c r="D51" t="n">
-        <v>9.963330108161264e-05</v>
+        <v>9.963330108163093e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001528775075287037</v>
+        <v>-0.0001528775075286259</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0002440775868241019</v>
+        <v>0.0002440775868240744</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0002954874911142768</v>
+        <v>-0.0002954874911141325</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0003338176457716292</v>
+        <v>0.000333817645771642</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0003017517144763948</v>
+        <v>-0.0003017517144762838</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003484399488751379</v>
+        <v>0.0003484399488751553</v>
       </c>
     </row>
   </sheetData>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:09:00 UTC</t>
+          <t>2026-06-11 11:19:13 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -501,31 +501,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1895993884990348</v>
+        <v>0.197031979916397</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2128965758215698</v>
+        <v>0.2151142192809106</v>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.08218501444886407</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6825846368058115</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.07649848892715405</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8964135384897927</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.75</v>
       </c>
     </row>
     <row r="3">
@@ -534,35 +534,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1863799078182438</v>
+        <v>0.1822093135670322</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1394502454784851</v>
+        <v>0.2303183402681055</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07162232356024348</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6200899517242822</v>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.07860230164514195</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8025643705288577</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1722449729920567</v>
+        <v>0.1432788772187993</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2478405711645279</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04169327757849408</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.601764780857478</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2117024883225277</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0635074364926031</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8259050747058545</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1743128923182218</v>
+        <v>0.1707695756402855</v>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.144698018739101</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06790920862648733</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.2613226798127818</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.06181643966256491</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.794075476273445</v>
+        <v>0.5310680760333479</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="6">
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01373555658939222</v>
+        <v>0.01371427929077212</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05772983474934443</v>
+        <v>0.05775896239923025</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403631419911995</v>
+        <v>0.01403367403849274</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.631337739190347</v>
+        <v>2.626237445197282</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1471175553736196</v>
+        <v>0.1780106703426724</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02657584683154118</v>
+        <v>0.01597906069969937</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04627937973001618</v>
+        <v>0.06739341884767287</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5085561467031074</v>
+        <v>0.4693524717652289</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -723,28 +723,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009875821513102748</v>
+        <v>0.008314331122088188</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007925353131043219</v>
+        <v>0.006835148585456436</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0108627751643317</v>
+        <v>0.01051785434685317</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.84414326112049</v>
+        <v>0.6862377076477033</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>6.75</v>
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006465707044746236</v>
+        <v>0.01390980338324053</v>
       </c>
       <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01491685955454073</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02109745917280919</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09421368555932741</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
         <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.006999688162288626</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009340866100761546</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1217566041760496</v>
-      </c>
-      <c r="J9" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -797,31 +797,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004256660767050036</v>
+        <v>0.004248967520419441</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00368188004904298</v>
+        <v>0.003845010451561188</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002599188242755868</v>
+        <v>0.002592940647117026</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1549274159863225</v>
+        <v>0.135460058653166</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>10.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
@@ -834,28 +834,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004644313470562978</v>
+        <v>0.004565168569245587</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00229197580494917</v>
+        <v>0.002114894388361565</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002496873146861467</v>
+        <v>0.002420162849803742</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1509021465815614</v>
+        <v>0.1526701842303604</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
         <v>11.5</v>
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01392701517609831</v>
+        <v>0.006486740520454934</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01491971142731746</v>
+        <v>0.007049071314577241</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02147053133543316</v>
+        <v>0.009235213308433566</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06476447633751148</v>
+        <v>0.04589542792206514</v>
       </c>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>12.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003612716197254826</v>
+        <v>0.002849862762434156</v>
       </c>
       <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.003127706299701867</v>
+      </c>
+      <c r="F13" t="n">
         <v>12</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.001602535112577621</v>
-      </c>
-      <c r="F13" t="n">
-        <v>20</v>
-      </c>
       <c r="G13" t="n">
-        <v>0.0008154266106804586</v>
+        <v>0.0006130076013525665</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1109950779114004</v>
+        <v>0.09466269310465947</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>15.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -945,31 +945,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002669730723085642</v>
+        <v>0.002688148546326715</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002315306987611006</v>
+        <v>0.003341993402721055</v>
       </c>
       <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0005878733118516611</v>
+      </c>
+      <c r="H14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1178889635020983</v>
+      </c>
+      <c r="J14" t="n">
         <v>13</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0006945157203729569</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>16</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1366375884758959</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002881142214388859</v>
+        <v>0.003595278350624291</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003416348129179547</v>
+        <v>0.001608605619664584</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006429383128874977</v>
+        <v>0.001027549058435584</v>
       </c>
       <c r="H15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.07428057261443222</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21</v>
+      </c>
+      <c r="K15" t="n">
         <v>17</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.08700915294395362</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002168916220725689</v>
+        <v>0.002236047327322062</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001799256851576492</v>
+        <v>0.001643514043991867</v>
       </c>
       <c r="F16" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.000643083991171689</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3031789140189818</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
         <v>18</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0004894569504431456</v>
-      </c>
-      <c r="H16" t="n">
-        <v>22</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4372963289827863</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.000926177612223676</v>
+        <v>0.003244512335033077</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003592776110369847</v>
+        <v>0.001583519635159759</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005797252702847144</v>
+        <v>0.0004073596329023266</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3837169217768097</v>
+        <v>0.07069768157613066</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.003188477971760697</v>
+        <v>0.0009079583826754834</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00166725284638349</v>
+        <v>0.002669343987540694</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002824170244158042</v>
+        <v>0.0005685433167898823</v>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06884801987848466</v>
+        <v>0.3506721756022313</v>
       </c>
       <c r="J18" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00238196920097417</v>
+        <v>0.002813202939694079</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002013273746452132</v>
+        <v>0.001799890106828131</v>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001186848419382436</v>
+        <v>0.001139467083597867</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1049004435149481</v>
+        <v>0.04066904872453581</v>
       </c>
       <c r="J19" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.003421955714025784</v>
+        <v>0.002445006205074117</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002108636815222021</v>
+        <v>0.001744319092412727</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002630852770622583</v>
+        <v>9.419230065841334e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06444049026894305</v>
+        <v>0.1330697997089101</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002948726526417326</v>
+        <v>0.003139731583109222</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00160249396898531</v>
+        <v>0.001132974778342241</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001075392008771492</v>
+        <v>0.001651166613885435</v>
       </c>
       <c r="H21" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08520098426131995</v>
+        <v>0.04564151511307379</v>
       </c>
       <c r="J21" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>23.75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1237,32 +1237,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00356076912017135</v>
+        <v>0.003412132915666005</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002138499160000766</v>
+        <v>0.002172888587112184</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0003017517144762838</v>
+        <v>0.0002508035987043522</v>
       </c>
       <c r="H22" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09533893131514493</v>
+        <v>0.0432485231175872</v>
       </c>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
         <v>24.25</v>
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001995297701238362</v>
+        <v>0.002144640109328005</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001195573840022569</v>
+        <v>0.001239108793164929</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001176911602381303</v>
+        <v>0.000282624680491228</v>
       </c>
       <c r="H23" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.07699352883582034</v>
+        <v>0.08429095909465323</v>
       </c>
       <c r="J23" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" t="n">
         <v>25</v>
-      </c>
-      <c r="K23" t="n">
-        <v>24.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.002831784189687003</v>
+        <v>0.001990095665097817</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>0.001393077784191214</v>
+        <v>0.001214862866781157</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001086721183328554</v>
+        <v>0.001103279195960572</v>
       </c>
       <c r="H24" t="n">
         <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0317247736777615</v>
+        <v>0.06001416912472735</v>
       </c>
       <c r="J24" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="K24" t="n">
-        <v>25.25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.003150126612262545</v>
+        <v>0.001995631583116888</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001203222741841466</v>
+        <v>0.001093984071412021</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001708226103672239</v>
+        <v>0.000324552027778946</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02771808103828732</v>
+        <v>0.08755417700795398</v>
       </c>
       <c r="J25" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="K25" t="n">
-        <v>25.75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.002133463418664557</v>
+        <v>0.002836662632711747</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001272127791727995</v>
+        <v>0.001349305935299087</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0002453289065025177</v>
+        <v>0.0006761052879341589</v>
       </c>
       <c r="H26" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07461436100266861</v>
+        <v>0.002951470240392329</v>
       </c>
       <c r="J26" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002814191906194162</v>
+        <v>0.002959161625982222</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00126940119254888</v>
+        <v>0.001497754221972584</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0005649273774047225</v>
+        <v>0.0001490539406376556</v>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.02843002005720718</v>
+        <v>0.0455889057521599</v>
       </c>
       <c r="J27" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K27" t="n">
-        <v>28.25</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.002338953678594916</v>
+        <v>0.00358464268418929</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001200369173883082</v>
+        <v>0.001907090410030094</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0004921419944499239</v>
+        <v>-0.0003997428023372551</v>
       </c>
       <c r="H28" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0495556552810732</v>
+        <v>0.05395565520421641</v>
       </c>
       <c r="J28" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>28.5</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.002174773169322461</v>
+        <v>0.002334541725108366</v>
       </c>
       <c r="D29" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.001231221978513675</v>
+      </c>
+      <c r="F29" t="n">
         <v>27</v>
       </c>
-      <c r="E29" t="n">
-        <v>0.001045982881192763</v>
-      </c>
-      <c r="F29" t="n">
-        <v>38</v>
-      </c>
       <c r="G29" t="n">
-        <v>0.0002566192068522155</v>
+        <v>0.0005390648583790458</v>
       </c>
       <c r="H29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
-        <v>0.07881840246990368</v>
+        <v>0.03780709217900924</v>
       </c>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="K29" t="n">
-        <v>29</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="30">
@@ -1537,31 +1537,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.002134837050977007</v>
+        <v>0.002142708186341778</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001277160729039802</v>
+        <v>0.001220283562262262</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>-8.289760053328265e-05</v>
+        <v>-0.0001259134161154862</v>
       </c>
       <c r="H30" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0869597385318106</v>
+        <v>0.1104152722501901</v>
       </c>
       <c r="J30" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>29.75</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.002709045200494806</v>
+        <v>0.001730764595016379</v>
       </c>
       <c r="D31" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001439765033102736</v>
+        <v>0.0008199308959394844</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0002954874911141325</v>
+        <v>0.0003586824013083745</v>
       </c>
       <c r="H31" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07806897311204031</v>
+        <v>0.09077149718766542</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>29.75</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001964311731130692</v>
+        <v>0.002175155303313864</v>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001007145267672297</v>
+        <v>0.001045149111347222</v>
       </c>
       <c r="F32" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000350978260910606</v>
+        <v>0.0002606351639304116</v>
       </c>
       <c r="H32" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07500992871397116</v>
+        <v>0.04812671572012839</v>
       </c>
       <c r="J32" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>30.25</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001586160837779102</v>
+        <v>0.002651597576798392</v>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0007987156867528704</v>
+        <v>0.001238094691828089</v>
       </c>
       <c r="F33" t="n">
+        <v>26</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.0001155041660675815</v>
+      </c>
+      <c r="H33" t="n">
         <v>48</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.0003410964696748398</v>
-      </c>
-      <c r="H33" t="n">
-        <v>24</v>
-      </c>
       <c r="I33" t="n">
-        <v>0.08102548883126426</v>
+        <v>0.05544883926129751</v>
       </c>
       <c r="J33" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K33" t="n">
-        <v>32.75</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.002279562527854898</v>
+        <v>0.00186160791803372</v>
       </c>
       <c r="D34" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001169492161131742</v>
+        <v>0.001062720717738418</v>
       </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0002700690732476807</v>
+        <v>0.0001113065420641712</v>
       </c>
       <c r="H34" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01373374091521473</v>
+        <v>0.07358509242456135</v>
       </c>
       <c r="J34" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>33.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001359104839427631</v>
+        <v>0.001887100017356224</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001185838060400895</v>
+        <v>0.00101160823327368</v>
       </c>
       <c r="F35" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0006083250116080685</v>
+        <v>0.0001328263492481829</v>
       </c>
       <c r="H35" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04349804935773127</v>
+        <v>0.07154468054081509</v>
       </c>
       <c r="J35" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K35" t="n">
-        <v>33.25</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.002367125780258667</v>
+        <v>0.001608372972853025</v>
       </c>
       <c r="D36" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00133191148165188</v>
+        <v>0.000776526603760119</v>
       </c>
       <c r="F36" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G36" t="n">
-        <v>3.836808120251111e-05</v>
+        <v>0.0002131281393188966</v>
       </c>
       <c r="H36" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04685155150494591</v>
+        <v>0.1133893110299296</v>
       </c>
       <c r="J36" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>33.25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001778947512908662</v>
+        <v>0.00234330921351191</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001077908604988344</v>
+        <v>0.001477805675243302</v>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0002172060170486989</v>
+        <v>5.023641873698192e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I37" t="n">
-        <v>0.06330762193683892</v>
+        <v>0.04230193990077913</v>
       </c>
       <c r="J37" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001815068182513057</v>
+        <v>0.002259585179662545</v>
       </c>
       <c r="D38" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001066766811210326</v>
+        <v>0.001153249291774402</v>
       </c>
       <c r="F38" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0001090197539357018</v>
+        <v>0.0002475134427031844</v>
       </c>
       <c r="H38" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.06614762099327409</v>
+        <v>0.03742666251680671</v>
       </c>
       <c r="J38" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K38" t="n">
-        <v>34.75</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001718774198605679</v>
+        <v>0.001350173311601951</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0008419614068759662</v>
+        <v>0.0008815156503392778</v>
       </c>
       <c r="F39" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001118043738160712</v>
+        <v>0.0003265698677199391</v>
       </c>
       <c r="H39" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I39" t="n">
-        <v>0.08468179151501731</v>
+        <v>0.06823029410260384</v>
       </c>
       <c r="J39" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>35</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001872026609777217</v>
+        <v>0.001227115416713972</v>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001128491436232877</v>
+        <v>0.0009428627077181219</v>
       </c>
       <c r="F40" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>8.438274383426591e-06</v>
+        <v>0.0002586429798237311</v>
       </c>
       <c r="H40" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0660645240209714</v>
+        <v>0.06499045206156984</v>
       </c>
       <c r="J40" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>36</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001919842813799432</v>
+        <v>0.001283303293776476</v>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001186911268168921</v>
+        <v>0.001000011170424423</v>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0001528775075286259</v>
+        <v>0.0001214486152627092</v>
       </c>
       <c r="H41" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I41" t="n">
-        <v>0.05789160624387613</v>
+        <v>0.0537388094101563</v>
       </c>
       <c r="J41" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K41" t="n">
-        <v>38.25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.00132533566265979</v>
+        <v>0.001167662558019662</v>
       </c>
       <c r="D42" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0009785282428057388</v>
+        <v>0.001049591901587422</v>
       </c>
       <c r="F42" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001466346449818467</v>
+        <v>0.0001663068606845841</v>
       </c>
       <c r="H42" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I42" t="n">
-        <v>0.03944742758240594</v>
+        <v>0.04508849545986449</v>
       </c>
       <c r="J42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
-        <v>39.25</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001506522590440855</v>
+        <v>0.001104109263332111</v>
       </c>
       <c r="D43" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0009399442045372306</v>
+        <v>0.000865793983920894</v>
       </c>
       <c r="F43" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>-8.455425889563051e-05</v>
+        <v>0.0001178070486130389</v>
       </c>
       <c r="H43" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.07360700504813256</v>
+        <v>0.07264352192166257</v>
       </c>
       <c r="J43" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K43" t="n">
-        <v>39.5</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001247224437160192</v>
+        <v>0.001731580648066713</v>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0009670203828993465</v>
+        <v>0.000968009359778049</v>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0001331909782702034</v>
+        <v>0.000249494465474287</v>
       </c>
       <c r="H44" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I44" t="n">
-        <v>0.04547430340962144</v>
+        <v>0.006997474455073149</v>
       </c>
       <c r="J44" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>39.75</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0001755422704987392</v>
+        <v>0.001515408891322052</v>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E45" t="n">
-        <v>0.000590661134077099</v>
+        <v>0.0009832362775042921</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>9.786120877085525e-05</v>
+        <v>-0.0001087868324821439</v>
       </c>
       <c r="H45" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I45" t="n">
-        <v>0.07942924358921877</v>
+        <v>0.05146667654081938</v>
       </c>
       <c r="J45" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K45" t="n">
-        <v>40.25</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="46">
@@ -2125,35 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001212757650961041</v>
+        <v>0.001899029504987533</v>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0008903963153521817</v>
+        <v>0.001205054300212215</v>
       </c>
       <c r="F46" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0001135314190648051</v>
+        <v>-0.0001576675489359247</v>
       </c>
       <c r="H46" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I46" t="n">
-        <v>0.04801226937526915</v>
+        <v>0.03093975615808375</v>
       </c>
       <c r="J46" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K46" t="n">
-        <v>40.5</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="47">
@@ -2162,35 +2162,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.512302449055861e-05</v>
+        <v>0.001090508675920083</v>
       </c>
       <c r="D47" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001083075854687862</v>
+        <v>0.0008711113564648789</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>4.368315297437197e-05</v>
+        <v>-0.0001482889034667201</v>
       </c>
       <c r="H47" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I47" t="n">
-        <v>0.06016409753460872</v>
+        <v>0.07251336273382991</v>
       </c>
       <c r="J47" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>41.75</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
@@ -2199,35 +2199,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.001081360128776589</v>
+        <v>0.0003376471091931949</v>
       </c>
       <c r="D48" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0008733460905374389</v>
+        <v>0.0006833324838897081</v>
       </c>
       <c r="F48" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G48" t="n">
-        <v>-5.331832821675598e-06</v>
+        <v>0.0001310618297204469</v>
       </c>
       <c r="H48" t="n">
+        <v>36</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.03328204574181282</v>
+      </c>
+      <c r="J48" t="n">
         <v>46</v>
       </c>
-      <c r="I48" t="n">
-        <v>0.0615495823953407</v>
-      </c>
-      <c r="J48" t="n">
-        <v>35</v>
-      </c>
       <c r="K48" t="n">
-        <v>42.75</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="49">
@@ -2236,35 +2236,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.001098944777494736</v>
+        <v>8.383859122599245e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0008506241691893381</v>
+        <v>0.0009950679928468313</v>
       </c>
       <c r="F49" t="n">
+        <v>39</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.006854685429939e-05</v>
+      </c>
+      <c r="H49" t="n">
+        <v>45</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.02752738838177793</v>
+      </c>
+      <c r="J49" t="n">
+        <v>48</v>
+      </c>
+      <c r="K49" t="n">
         <v>46</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.0001468207021590007</v>
-      </c>
-      <c r="H49" t="n">
-        <v>50</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.05949283921523474</v>
-      </c>
-      <c r="J49" t="n">
-        <v>37</v>
-      </c>
-      <c r="K49" t="n">
-        <v>44.25</v>
       </c>
     </row>
     <row r="50">
@@ -2273,35 +2273,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0003455470588704608</v>
+        <v>0.0001460040018972183</v>
       </c>
       <c r="D50" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E50" t="n">
-        <v>0.000658463623543061</v>
+        <v>0.0005720116476741351</v>
       </c>
       <c r="F50" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0001334733448209335</v>
+        <v>8.039867084361774e-05</v>
       </c>
       <c r="H50" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>0.03919358873285139</v>
       </c>
       <c r="J50" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K50" t="n">
-        <v>45.25</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="51">
@@ -2310,35 +2310,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.00024966867261556</v>
+        <v>0.0001711974007209496</v>
       </c>
       <c r="D51" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>0.001020386519460637</v>
+        <v>0.0004505128958804968</v>
       </c>
       <c r="F51" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0001227677575061925</v>
+        <v>0.0001067792396374334</v>
       </c>
       <c r="H51" t="n">
+        <v>40</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.02325339844985908</v>
+      </c>
+      <c r="J51" t="n">
         <v>49</v>
       </c>
-      <c r="I51" t="n">
-        <v>0.004195285673696425</v>
-      </c>
-      <c r="J51" t="n">
-        <v>51</v>
-      </c>
       <c r="K51" t="n">
-        <v>46.75</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="52">
@@ -2347,35 +2347,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0001627048506930618</v>
+        <v>8.005142757552094e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0005283516642189685</v>
+        <v>0.0004057401125536971</v>
       </c>
       <c r="F52" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0001070521114344913</v>
+        <v>3.786355455392965e-05</v>
       </c>
       <c r="H52" t="n">
+        <v>46</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.04365029460796976</v>
+      </c>
+      <c r="J52" t="n">
         <v>39</v>
       </c>
-      <c r="I52" t="n">
-        <v>0.002153536099111397</v>
-      </c>
-      <c r="J52" t="n">
-        <v>52</v>
-      </c>
       <c r="K52" t="n">
-        <v>48</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="53">
@@ -2384,35 +2384,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0001549947045209417</v>
+        <v>0.0002594094891159516</v>
       </c>
       <c r="D53" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0004974821683909026</v>
+        <v>0.000964441945781453</v>
       </c>
       <c r="F53" t="n">
+        <v>42</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.0001886907285609918</v>
+      </c>
+      <c r="H53" t="n">
         <v>52</v>
       </c>
-      <c r="G53" t="n">
-        <v>6.947384709169447e-05</v>
-      </c>
-      <c r="H53" t="n">
-        <v>41</v>
-      </c>
       <c r="I53" t="n">
-        <v>0.01162991083799847</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K53" t="n">
-        <v>48.25</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="54">
@@ -2421,35 +2421,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9.050314616939759e-05</v>
+        <v>0.0001757949887419857</v>
       </c>
       <c r="D54" t="n">
+        <v>49</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0005280967535366773</v>
+      </c>
+      <c r="F54" t="n">
+        <v>51</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7.768872334517063e-05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>43</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
         <v>52</v>
       </c>
-      <c r="E54" t="n">
-        <v>0.0002772369584139235</v>
-      </c>
-      <c r="F54" t="n">
-        <v>53</v>
-      </c>
-      <c r="G54" t="n">
-        <v>6.306591677343043e-05</v>
-      </c>
-      <c r="H54" t="n">
-        <v>42</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.004676306983799838</v>
-      </c>
-      <c r="J54" t="n">
-        <v>50</v>
-      </c>
       <c r="K54" t="n">
-        <v>49.25</v>
+        <v>48.75</v>
       </c>
     </row>
   </sheetData>
@@ -2533,31 +2533,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1895993884990348</v>
+        <v>0.197031979916397</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2128965758215698</v>
+        <v>0.2151142192809106</v>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.08218501444886407</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6825846368058115</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.07649848892715405</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8964135384897927</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.75</v>
       </c>
     </row>
     <row r="3">
@@ -2566,35 +2566,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1863799078182438</v>
+        <v>0.1822093135670322</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1394502454784851</v>
+        <v>0.2303183402681055</v>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07162232356024348</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6200899517242822</v>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.07860230164514195</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8025643705288577</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -2603,35 +2603,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1722449729920567</v>
+        <v>0.1432788772187993</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2478405711645279</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.04169327757849408</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.601764780857478</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2117024883225277</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0635074364926031</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8259050747058545</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -2640,35 +2640,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1743128923182218</v>
+        <v>0.1707695756402855</v>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.144698018739101</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06790920862648733</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.2613226798127818</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.06181643966256491</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.794075476273445</v>
+        <v>0.5310680760333479</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="6">
@@ -2681,25 +2681,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01373555658939222</v>
+        <v>0.01371427929077212</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05772983474934443</v>
+        <v>0.05775896239923025</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403631419911995</v>
+        <v>0.01403367403849274</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.631337739190347</v>
+        <v>2.626237445197282</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -2718,31 +2718,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1471175553736196</v>
+        <v>0.1780106703426724</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02657584683154118</v>
+        <v>0.01597906069969937</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04627937973001618</v>
+        <v>0.06739341884767287</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5085561467031074</v>
+        <v>0.4693524717652289</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2755,28 +2755,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.009875821513102748</v>
+        <v>0.008314331122088188</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007925353131043219</v>
+        <v>0.006835148585456436</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0108627751643317</v>
+        <v>0.01051785434685317</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.84414326112049</v>
+        <v>0.6862377076477033</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>6.75</v>
@@ -2788,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006465707044746236</v>
+        <v>0.01390980338324053</v>
       </c>
       <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01491685955454073</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02109745917280919</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09421368555932741</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" t="n">
         <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.006999688162288626</v>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.009340866100761546</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1217566041760496</v>
-      </c>
-      <c r="J9" t="n">
-        <v>13</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2829,31 +2829,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004256660767050036</v>
+        <v>0.004248967520419441</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00368188004904298</v>
+        <v>0.003845010451561188</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002599188242755868</v>
+        <v>0.002592940647117026</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1549274159863225</v>
+        <v>0.135460058653166</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>10.25</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
@@ -2866,28 +2866,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004644313470562978</v>
+        <v>0.004565168569245587</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00229197580494917</v>
+        <v>0.002114894388361565</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002496873146861467</v>
+        <v>0.002420162849803742</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1509021465815614</v>
+        <v>0.1526701842303604</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
         <v>11.5</v>
@@ -2899,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.01392701517609831</v>
+        <v>0.006486740520454934</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01491971142731746</v>
+        <v>0.007049071314577241</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02147053133543316</v>
+        <v>0.009235213308433566</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06476447633751148</v>
+        <v>0.04589542792206514</v>
       </c>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>12.75</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="13">
@@ -2936,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003612716197254826</v>
+        <v>0.002849862762434156</v>
       </c>
       <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.003127706299701867</v>
+      </c>
+      <c r="F13" t="n">
         <v>12</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.001602535112577621</v>
-      </c>
-      <c r="F13" t="n">
-        <v>20</v>
-      </c>
       <c r="G13" t="n">
-        <v>0.0008154266106804586</v>
+        <v>0.0006130076013525665</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1109950779114004</v>
+        <v>0.09466269310465947</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>15.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -2977,31 +2977,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002669730723085642</v>
+        <v>0.002688148546326715</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002315306987611006</v>
+        <v>0.003341993402721055</v>
       </c>
       <c r="F14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0005878733118516611</v>
+      </c>
+      <c r="H14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1178889635020983</v>
+      </c>
+      <c r="J14" t="n">
         <v>13</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.0006945157203729569</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>16</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1366375884758959</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -3010,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002881142214388859</v>
+        <v>0.003595278350624291</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003416348129179547</v>
+        <v>0.001608605619664584</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0006429383128874977</v>
+        <v>0.001027549058435584</v>
       </c>
       <c r="H15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.07428057261443222</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21</v>
+      </c>
+      <c r="K15" t="n">
         <v>17</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.08700915294395362</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -3051,31 +3051,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002168916220725689</v>
+        <v>0.002236047327322062</v>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001799256851576492</v>
+        <v>0.001643514043991867</v>
       </c>
       <c r="F16" t="n">
+        <v>19</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.000643083991171689</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3031789140189818</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" t="n">
         <v>18</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0004894569504431456</v>
-      </c>
-      <c r="H16" t="n">
-        <v>22</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4372963289827863</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.000926177612223676</v>
+        <v>0.003244512335033077</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003592776110369847</v>
+        <v>0.001583519635159759</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0005797252702847144</v>
+        <v>0.0004073596329023266</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3837169217768097</v>
+        <v>0.07069768157613066</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.003188477971760697</v>
+        <v>0.0009079583826754834</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00166725284638349</v>
+        <v>0.002669343987540694</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002824170244158042</v>
+        <v>0.0005685433167898823</v>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06884801987848466</v>
+        <v>0.3506721756022313</v>
       </c>
       <c r="J18" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>22</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00238196920097417</v>
+        <v>0.002813202939694079</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002013273746452132</v>
+        <v>0.001799890106828131</v>
       </c>
       <c r="F19" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0001186848419382436</v>
+        <v>0.001139467083597867</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1049004435149481</v>
+        <v>0.04066904872453581</v>
       </c>
       <c r="J19" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.003421955714025784</v>
+        <v>0.002445006205074117</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002108636815222021</v>
+        <v>0.001744319092412727</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0002630852770622583</v>
+        <v>9.419230065841334e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06444049026894305</v>
+        <v>0.1330697997089101</v>
       </c>
       <c r="J20" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002948726526417326</v>
+        <v>0.003139731583109222</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00160249396898531</v>
+        <v>0.001132974778342241</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001075392008771492</v>
+        <v>0.001651166613885435</v>
       </c>
       <c r="H21" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08520098426131995</v>
+        <v>0.04564151511307379</v>
       </c>
       <c r="J21" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>23.75</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1895993884990348</v>
+        <v>0.197031979916397</v>
       </c>
     </row>
     <row r="3">
@@ -3313,11 +3313,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1863799078182438</v>
+        <v>0.1822093135670322</v>
       </c>
     </row>
     <row r="4">
@@ -3326,11 +3326,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1743128923182218</v>
+        <v>0.1780106703426724</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1722449729920567</v>
+        <v>0.1707695756402855</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3352,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1471175553736196</v>
+        <v>0.1432788772187993</v>
       </c>
     </row>
     <row r="7">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01392701517609831</v>
+        <v>0.01390980338324053</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01373555658939222</v>
+        <v>0.01371427929077212</v>
       </c>
     </row>
     <row r="9">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.009875821513102748</v>
+        <v>0.008314331122088188</v>
       </c>
     </row>
     <row r="10">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006465707044746236</v>
+        <v>0.006486740520454934</v>
       </c>
     </row>
     <row r="11">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004644313470562978</v>
+        <v>0.004565168569245587</v>
       </c>
     </row>
     <row r="12">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004256660767050036</v>
+        <v>0.004248967520419441</v>
       </c>
     </row>
     <row r="13">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003612716197254826</v>
+        <v>0.003595278350624291</v>
       </c>
     </row>
     <row r="14">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00356076912017135</v>
+        <v>0.00358464268418929</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003421955714025784</v>
+        <v>0.003412132915666005</v>
       </c>
     </row>
     <row r="16">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003188477971760697</v>
+        <v>0.003244512335033077</v>
       </c>
     </row>
     <row r="17">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003150126612262545</v>
+        <v>0.003139731583109222</v>
       </c>
     </row>
     <row r="18">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002948726526417326</v>
+        <v>0.002959161625982222</v>
       </c>
     </row>
     <row r="19">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002881142214388859</v>
+        <v>0.002849862762434156</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002831784189687003</v>
+        <v>0.002836662632711747</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002814191906194162</v>
+        <v>0.002813202939694079</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.002709045200494806</v>
+        <v>0.002688148546326715</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002669730723085642</v>
+        <v>0.002651597576798392</v>
       </c>
     </row>
     <row r="24">
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00238196920097417</v>
+        <v>0.002445006205074117</v>
       </c>
     </row>
     <row r="25">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.002367125780258667</v>
+        <v>0.00234330921351191</v>
       </c>
     </row>
     <row r="26">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.002338953678594916</v>
+        <v>0.002334541725108366</v>
       </c>
     </row>
     <row r="27">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002279562527854898</v>
+        <v>0.002259585179662545</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.002174773169322461</v>
+        <v>0.002236047327322062</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.002168916220725689</v>
+        <v>0.002175155303313864</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3664,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.002134837050977007</v>
+        <v>0.002144640109328005</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3677,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.002133463418664557</v>
+        <v>0.002142708186341778</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001995297701238362</v>
+        <v>0.001995631583116888</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001964311731130692</v>
+        <v>0.001990095665097817</v>
       </c>
     </row>
     <row r="34">
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001919842813799432</v>
+        <v>0.001899029504987533</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3729,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001872026609777217</v>
+        <v>0.001887100017356224</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001815068182513057</v>
+        <v>0.00186160791803372</v>
       </c>
     </row>
     <row r="37">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001778947512908662</v>
+        <v>0.001731580648066713</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001718774198605679</v>
+        <v>0.001730764595016379</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001586160837779102</v>
+        <v>0.001608372972853025</v>
       </c>
     </row>
     <row r="40">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001506522590440855</v>
+        <v>0.001515408891322052</v>
       </c>
     </row>
     <row r="41">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001359104839427631</v>
+        <v>0.001350173311601951</v>
       </c>
     </row>
     <row r="42">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.00132533566265979</v>
+        <v>0.001283303293776476</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3833,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001247224437160192</v>
+        <v>0.001227115416713972</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001212757650961041</v>
+        <v>0.001167662558019662</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001098944777494736</v>
+        <v>0.001104109263332111</v>
       </c>
     </row>
     <row r="46">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001081360128776589</v>
+        <v>0.001090508675920083</v>
       </c>
     </row>
     <row r="47">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.000926177612223676</v>
+        <v>0.0009079583826754834</v>
       </c>
     </row>
     <row r="48">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0003455470588704608</v>
+        <v>0.0003376471091931949</v>
       </c>
     </row>
     <row r="49">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.00024966867261556</v>
+        <v>0.0002594094891159516</v>
       </c>
     </row>
     <row r="50">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0001755422704987392</v>
+        <v>0.0001757949887419857</v>
       </c>
     </row>
     <row r="51">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0001627048506930618</v>
+        <v>0.0001711974007209496</v>
       </c>
     </row>
     <row r="52">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0001549947045209417</v>
+        <v>0.0001460040018972183</v>
       </c>
     </row>
     <row r="53">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.050314616939759e-05</v>
+        <v>8.383859122599245e-05</v>
       </c>
     </row>
     <row r="54">
@@ -3976,11 +3976,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.512302449055861e-05</v>
+        <v>8.005142757552094e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2613226798127818</v>
+        <v>0.2478405711645279</v>
       </c>
     </row>
     <row r="3">
@@ -4033,11 +4033,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2128965758215698</v>
+        <v>0.2303183402681055</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +4046,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2117024883225277</v>
+        <v>0.2151142192809106</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1394502454784851</v>
+        <v>0.144698018739101</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05772983474934443</v>
+        <v>0.05775896239923025</v>
       </c>
     </row>
     <row r="7">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02657584683154118</v>
+        <v>0.01597906069969937</v>
       </c>
     </row>
     <row r="8">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01491971142731746</v>
+        <v>0.01491685955454073</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007925353131043219</v>
+        <v>0.007049071314577241</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006999688162288626</v>
+        <v>0.006835148585456436</v>
       </c>
     </row>
     <row r="11">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.00368188004904298</v>
+        <v>0.003845010451561188</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003592776110369847</v>
+        <v>0.003341993402721055</v>
       </c>
     </row>
     <row r="13">
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003416348129179547</v>
+        <v>0.003127706299701867</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002315306987611006</v>
+        <v>0.002669343987540694</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.00229197580494917</v>
+        <v>0.002172888587112184</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002138499160000766</v>
+        <v>0.002114894388361565</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.002108636815222021</v>
+        <v>0.001907090410030094</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002013273746452132</v>
+        <v>0.001799890106828131</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001799256851576492</v>
+        <v>0.001744319092412727</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00166725284638349</v>
+        <v>0.001643514043991867</v>
       </c>
     </row>
     <row r="21">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001602535112577621</v>
+        <v>0.001608605619664584</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00160249396898531</v>
+        <v>0.001583519635159759</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001439765033102736</v>
+        <v>0.001497754221972584</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001393077784191214</v>
+        <v>0.001477805675243302</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.00133191148165188</v>
+        <v>0.001349305935299087</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001277160729039802</v>
+        <v>0.001239108793164929</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001272127791727995</v>
+        <v>0.001238094691828089</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.00126940119254888</v>
+        <v>0.001231221978513675</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001203222741841466</v>
+        <v>0.001220283562262262</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001200369173883082</v>
+        <v>0.001214862866781157</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001195573840022569</v>
+        <v>0.001205054300212215</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001186911268168921</v>
+        <v>0.001153249291774402</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001185838060400895</v>
+        <v>0.001132974778342241</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001169492161131742</v>
+        <v>0.001093984071412021</v>
       </c>
     </row>
     <row r="35">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001128491436232877</v>
+        <v>0.001062720717738418</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001083075854687862</v>
+        <v>0.001049591901587422</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001077908604988344</v>
+        <v>0.001045149111347222</v>
       </c>
     </row>
     <row r="38">
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001066766811210326</v>
+        <v>0.00101160823327368</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4501,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001045982881192763</v>
+        <v>0.001000011170424423</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4514,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001020386519460637</v>
+        <v>0.0009950679928468313</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4527,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001007145267672297</v>
+        <v>0.0009832362775042921</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4540,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0009785282428057388</v>
+        <v>0.000968009359778049</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0009670203828993465</v>
+        <v>0.000964441945781453</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4566,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0009399442045372306</v>
+        <v>0.0009428627077181219</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0008903963153521817</v>
+        <v>0.0008815156503392778</v>
       </c>
     </row>
     <row r="46">
@@ -4592,11 +4592,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0008733460905374389</v>
+        <v>0.0008711113564648789</v>
       </c>
     </row>
     <row r="47">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0008506241691893381</v>
+        <v>0.000865793983920894</v>
       </c>
     </row>
     <row r="48">
@@ -4618,11 +4618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0008419614068759662</v>
+        <v>0.0008199308959394844</v>
       </c>
     </row>
     <row r="49">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0007987156867528704</v>
+        <v>0.000776526603760119</v>
       </c>
     </row>
     <row r="50">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.000658463623543061</v>
+        <v>0.0006833324838897081</v>
       </c>
     </row>
     <row r="51">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.000590661134077099</v>
+        <v>0.0005720116476741351</v>
       </c>
     </row>
     <row r="52">
@@ -4670,11 +4670,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0005283516642189685</v>
+        <v>0.0005280967535366773</v>
       </c>
     </row>
     <row r="53">
@@ -4683,11 +4683,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0004974821683909026</v>
+        <v>0.0004505128958804968</v>
       </c>
     </row>
     <row r="54">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.0002772369584139235</v>
+        <v>0.0004057401125536971</v>
       </c>
     </row>
   </sheetData>
@@ -4745,14 +4745,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07860230164514195</v>
+        <v>0.08218501444886407</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01247587325798385</v>
+        <v>0.01141698427518707</v>
       </c>
     </row>
     <row r="3">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07649848892715405</v>
+        <v>0.07162232356024348</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01113188930792712</v>
+        <v>0.01066177504862114</v>
       </c>
     </row>
     <row r="4">
@@ -4777,14 +4777,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0635074364926031</v>
+        <v>0.06790920862648733</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009833519898741983</v>
+        <v>0.01155419516112018</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06181643966256491</v>
+        <v>0.06739341884767287</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009674024373500815</v>
+        <v>0.01008795011191899</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04627937973001618</v>
+        <v>0.04169327757849408</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008148329194049821</v>
+        <v>0.007623898478615744</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02147053133543316</v>
+        <v>0.02109745917280919</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002867227169834253</v>
+        <v>0.002949417463791526</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01403631419911995</v>
+        <v>0.01403367403849274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003264207197172888</v>
+        <v>0.003242892811433474</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0108627751643317</v>
+        <v>0.01051785434685317</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00106329396661205</v>
+        <v>0.001076174911258317</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009340866100761546</v>
+        <v>0.009235213308433566</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001326126284520369</v>
+        <v>0.001324303416572418</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002599188242755868</v>
+        <v>0.002592940647117026</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001048424422067855</v>
+        <v>0.001015796128366716</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002496873146861467</v>
+        <v>0.002420162849803742</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001060092833364844</v>
+        <v>0.001109082392080396</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001708226103672239</v>
+        <v>0.001651166613885435</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003792613466815153</v>
+        <v>0.0003524536365500912</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001176911602381303</v>
+        <v>0.001139467083597867</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0003016563775985857</v>
+        <v>0.0006208881009843724</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001086721183328554</v>
+        <v>0.001103279195960572</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0005534466286314996</v>
+        <v>0.0002989338058261137</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008154266106804586</v>
+        <v>0.001027549058435584</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005999274128553415</v>
+        <v>0.0007335523118561347</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0006945157203729569</v>
+        <v>0.0006761052879341589</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003190097556946082</v>
+        <v>0.0003901997982442598</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0006429383128874977</v>
+        <v>0.000643083991171689</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0003980646005040254</v>
+        <v>0.0002453005202181975</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006083250116080685</v>
+        <v>0.0006130076013525665</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001889850706101278</v>
+        <v>0.0003736264974452768</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005797252702847144</v>
+        <v>0.0005878733118516611</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001364816009534143</v>
+        <v>0.0002528177755247611</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005649273774047225</v>
+        <v>0.0005685433167898823</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0003847971639680674</v>
+        <v>0.000134007416767915</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004921419944499239</v>
+        <v>0.0005390648583790458</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003197093876250583</v>
+        <v>0.0002809560041175864</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004894569504431456</v>
+        <v>0.0004073596329023266</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002321624272516576</v>
+        <v>0.0004590466294514283</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000350978260910606</v>
+        <v>0.0003586824013083745</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0002014319633464083</v>
+        <v>0.0002046317526306413</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003410964696748398</v>
+        <v>0.0003265698677199391</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001707113490920687</v>
+        <v>0.0001039044267277166</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0002824170244158042</v>
+        <v>0.000324552027778946</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0005019314448220945</v>
+        <v>0.0001704088168848761</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002700690732476807</v>
+        <v>0.000282624680491228</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001982817009273181</v>
+        <v>0.0002098198022891136</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002630852770622583</v>
+        <v>0.0002606351639304116</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0004522063131532384</v>
+        <v>0.0002308650490474039</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002566192068522155</v>
+        <v>0.0002586429798237311</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001839495869689226</v>
+        <v>0.0001351089986179497</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002453289065025177</v>
+        <v>0.0002508035987043522</v>
       </c>
       <c r="D30" t="n">
-        <v>0.000184189097662153</v>
+        <v>0.0004872567478689483</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002172060170486989</v>
+        <v>0.000249494465474287</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001679433348069088</v>
+        <v>0.0001399111512442106</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001466346449818467</v>
+        <v>0.0002475134427031844</v>
       </c>
       <c r="D32" t="n">
-        <v>8.705111281041989e-05</v>
+        <v>0.0001698229151201552</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001334733448209335</v>
+        <v>0.0002131281393188966</v>
       </c>
       <c r="D33" t="n">
-        <v>3.396422697634077e-05</v>
+        <v>0.0001764127558914285</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001331909782702034</v>
+        <v>0.0001663068606845841</v>
       </c>
       <c r="D34" t="n">
-        <v>9.668121772100634e-05</v>
+        <v>0.0001967176820286803</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001186848419382436</v>
+        <v>0.0001490539406376556</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001766239713753026</v>
+        <v>0.0003291413621283385</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001135314190648051</v>
+        <v>0.0001328263492481829</v>
       </c>
       <c r="D36" t="n">
-        <v>7.966894351275279e-05</v>
+        <v>0.0001153909443612429</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001118043738160712</v>
+        <v>0.0001310618297204469</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0002258424310842831</v>
+        <v>3.08437602860138e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001090197539357018</v>
+        <v>0.0001214486152627092</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001575667877766118</v>
+        <v>0.0001039616189406464</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0001075392008771492</v>
+        <v>0.0001178070486130389</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0002835892220985357</v>
+        <v>0.0001030200286077411</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0001070521114344913</v>
+        <v>0.0001113065420641712</v>
       </c>
       <c r="D40" t="n">
-        <v>5.782955631025541e-05</v>
+        <v>7.446805171638141e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9.786120877085525e-05</v>
+        <v>0.0001067792396374334</v>
       </c>
       <c r="D41" t="n">
-        <v>5.992596384599741e-05</v>
+        <v>6.09335495997491e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.947384709169447e-05</v>
+        <v>9.419230065841334e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>7.23967599166721e-05</v>
+        <v>0.0001731845965015959</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.306591677343043e-05</v>
+        <v>8.039867084361774e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>1.781378163219343e-05</v>
+        <v>5.127768626722146e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.368315297437197e-05</v>
+        <v>7.768872334517063e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>1.985434012297735e-05</v>
+        <v>7.258119592487347e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.836808120251111e-05</v>
+        <v>5.023641873698192e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002610280273108099</v>
+        <v>0.0002133286720324505</v>
       </c>
     </row>
     <row r="46">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.438274383426591e-06</v>
+        <v>4.006854685429939e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>8.157963971252458e-05</v>
+        <v>1.572502966742423e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-5.331832821675598e-06</v>
+        <v>3.786355455392965e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>8.375010717378523e-05</v>
+        <v>1.556803031836518e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-8.289760053328265e-05</v>
+        <v>-0.0001087868324821439</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0002350362630497555</v>
+        <v>0.0001130451266013766</v>
       </c>
     </row>
     <row r="49">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-8.455425889563051e-05</v>
+        <v>-0.0001155041660675815</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0001121915011527019</v>
+        <v>0.0003357481855654086</v>
       </c>
     </row>
     <row r="50">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001227677575061925</v>
+        <v>-0.0001259134161154862</v>
       </c>
       <c r="D50" t="n">
-        <v>7.961533954136952e-05</v>
+        <v>0.000205731715837911</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001468207021590007</v>
+        <v>-0.0001482889034667201</v>
       </c>
       <c r="D51" t="n">
-        <v>9.963330108163093e-05</v>
+        <v>8.77721560419013e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001528775075286259</v>
+        <v>-0.0001576675489359247</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0002440775868240744</v>
+        <v>0.000194874282553393</v>
       </c>
     </row>
     <row r="53">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0002954874911141325</v>
+        <v>-0.0001886907285609918</v>
       </c>
       <c r="D53" t="n">
-        <v>0.000333817645771642</v>
+        <v>9.028791264926092e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0003017517144762838</v>
+        <v>-0.0003997428023372551</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003484399488751553</v>
+        <v>0.0003761327267890014</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.631337739190347</v>
+        <v>2.626237445197282</v>
       </c>
     </row>
     <row r="3">
@@ -5637,11 +5637,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8964135384897927</v>
+        <v>0.6862377076477033</v>
       </c>
     </row>
     <row r="4">
@@ -5650,11 +5650,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.84414326112049</v>
+        <v>0.6825846368058115</v>
       </c>
     </row>
     <row r="5">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8259050747058545</v>
+        <v>0.6200899517242822</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8025643705288577</v>
+        <v>0.601764780857478</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.794075476273445</v>
+        <v>0.5310680760333479</v>
       </c>
     </row>
     <row r="8">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5085561467031074</v>
+        <v>0.4693524717652289</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4372963289827863</v>
+        <v>0.3506721756022313</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3837169217768097</v>
+        <v>0.3031789140189818</v>
       </c>
     </row>
     <row r="11">
@@ -5741,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1549274159863225</v>
+        <v>0.1526701842303604</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1509021465815614</v>
+        <v>0.135460058653166</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1366375884758959</v>
+        <v>0.1330697997089101</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1217566041760496</v>
+        <v>0.1178889635020983</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1109950779114004</v>
+        <v>0.1133893110299296</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1049004435149481</v>
+        <v>0.1104152722501901</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.09533893131514493</v>
+        <v>0.09466269310465947</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.08700915294395362</v>
+        <v>0.09421368555932741</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0869597385318106</v>
+        <v>0.09077149718766542</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.08520098426131995</v>
+        <v>0.08755417700795398</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.08468179151501731</v>
+        <v>0.08429095909465323</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.08102548883126426</v>
+        <v>0.07428057261443222</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.07942924358921877</v>
+        <v>0.07358509242456135</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.07881840246990368</v>
+        <v>0.07264352192166257</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5923,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.07806897311204031</v>
+        <v>0.07251336273382991</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07699352883582034</v>
+        <v>0.07154468054081509</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5949,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07500992871397116</v>
+        <v>0.07069768157613066</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5962,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.07461436100266861</v>
+        <v>0.06823029410260384</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.07360700504813256</v>
+        <v>0.06499045206156984</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.06884801987848466</v>
+        <v>0.06001416912472735</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.06614762099327409</v>
+        <v>0.05544883926129751</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0660645240209714</v>
+        <v>0.05395565520421641</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.06476447633751148</v>
+        <v>0.0537388094101563</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +6040,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.06444049026894305</v>
+        <v>0.05146667654081938</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +6053,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.06330762193683892</v>
+        <v>0.04812671572012839</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0615495823953407</v>
+        <v>0.04589542792206514</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +6079,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.06016409753460872</v>
+        <v>0.04564151511307379</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +6092,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.05949283921523474</v>
+        <v>0.0455889057521599</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.05789160624387613</v>
+        <v>0.04508849545986449</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0495556552810732</v>
+        <v>0.04365029460796976</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.04801226937526915</v>
+        <v>0.0432485231175872</v>
       </c>
     </row>
     <row r="42">
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.04685155150494591</v>
+        <v>0.04230193990077913</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +6157,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.04547430340962144</v>
+        <v>0.04066904872453581</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.04349804935773127</v>
+        <v>0.03919358873285139</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.03944742758240594</v>
+        <v>0.03780709217900924</v>
       </c>
     </row>
     <row r="46">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0317247736777615</v>
+        <v>0.03742666251680671</v>
       </c>
     </row>
     <row r="47">
@@ -6209,11 +6209,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.02843002005720718</v>
+        <v>0.03328204574181282</v>
       </c>
     </row>
     <row r="48">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.02771808103828732</v>
+        <v>0.03093975615808375</v>
       </c>
     </row>
     <row r="49">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.01373374091521473</v>
+        <v>0.02752738838177793</v>
       </c>
     </row>
     <row r="50">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.01162991083799847</v>
+        <v>0.02325339844985908</v>
       </c>
     </row>
     <row r="51">
@@ -6261,11 +6261,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.004676306983799838</v>
+        <v>0.006997474455073149</v>
       </c>
     </row>
     <row r="52">
@@ -6274,11 +6274,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.004195285673696425</v>
+        <v>0.002951470240392329</v>
       </c>
     </row>
     <row r="53">
@@ -6287,20 +6287,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.002153536099111397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6318,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,15 +6334,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>training_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>permutation_rows_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_variables_ranked</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoded_feature_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preprocessing_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_at_utc</t>
         </is>
@@ -6358,14 +6373,25 @@
         <v>788</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E2" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="n">
-        <v>446</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 11:19:13 UTC</t>
+      <c r="F2" t="n">
+        <v>414</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fit_on_training_split_only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:01:33 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -513,7 +513,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08218501444886407</v>
+        <v>0.08218501444886418</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07162232356024348</v>
+        <v>0.0716223235602436</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04169327757849408</v>
+        <v>0.04169327757849419</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06790920862648733</v>
+        <v>0.06790920862648747</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403367403849274</v>
+        <v>0.01403367403853356</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06739341884767287</v>
+        <v>0.067393418847673</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01051785434685317</v>
+        <v>0.01051785434685325</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02109745917280919</v>
+        <v>0.02109745917280935</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002592940647117026</v>
+        <v>0.002592940647117114</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002420162849803742</v>
+        <v>0.002420162849803853</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -883,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009235213308433566</v>
+        <v>0.009235213308433687</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006130076013525665</v>
+        <v>0.0006130076013526776</v>
       </c>
       <c r="H13" t="n">
         <v>18</v>
@@ -957,7 +957,7 @@
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005878733118516611</v>
+        <v>0.0005878733118517942</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -994,7 +994,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001027549058435584</v>
+        <v>0.001027549058435706</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -1031,7 +1031,7 @@
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000643083991171689</v>
+        <v>0.000643083991171789</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004073596329023266</v>
+        <v>0.0004073596329024487</v>
       </c>
       <c r="H17" t="n">
         <v>22</v>
@@ -1105,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005685433167898823</v>
+        <v>0.0005685433167899823</v>
       </c>
       <c r="H18" t="n">
         <v>20</v>
@@ -1142,7 +1142,7 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001139467083597867</v>
+        <v>0.001139467083597945</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -1179,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>9.419230065841334e-05</v>
+        <v>9.419230065853546e-05</v>
       </c>
       <c r="H20" t="n">
         <v>41</v>
@@ -1216,7 +1216,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001651166613885435</v>
+        <v>0.001651166613885535</v>
       </c>
       <c r="H21" t="n">
         <v>12</v>
@@ -1253,7 +1253,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002508035987043522</v>
+        <v>0.0002508035987044743</v>
       </c>
       <c r="H22" t="n">
         <v>29</v>
@@ -1290,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000282624680491228</v>
+        <v>0.0002826246804913058</v>
       </c>
       <c r="H23" t="n">
         <v>26</v>
@@ -1327,7 +1327,7 @@
         <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001103279195960572</v>
+        <v>0.001103279195960694</v>
       </c>
       <c r="H24" t="n">
         <v>14</v>
@@ -1364,7 +1364,7 @@
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000324552027778946</v>
+        <v>0.0003245520277790792</v>
       </c>
       <c r="H25" t="n">
         <v>25</v>
@@ -1401,7 +1401,7 @@
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0006761052879341589</v>
+        <v>0.0006761052879342367</v>
       </c>
       <c r="H26" t="n">
         <v>16</v>
@@ -1438,7 +1438,7 @@
         <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001490539406376556</v>
+        <v>0.0001490539406377667</v>
       </c>
       <c r="H27" t="n">
         <v>34</v>
@@ -1475,7 +1475,7 @@
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0003997428023372551</v>
+        <v>-0.0003997428023371219</v>
       </c>
       <c r="H28" t="n">
         <v>53</v>
@@ -1512,7 +1512,7 @@
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0005390648583790458</v>
+        <v>0.0005390648583792013</v>
       </c>
       <c r="H29" t="n">
         <v>21</v>
@@ -1549,7 +1549,7 @@
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0001259134161154862</v>
+        <v>-0.000125913416115353</v>
       </c>
       <c r="H30" t="n">
         <v>49</v>
@@ -1586,7 +1586,7 @@
         <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003586824013083745</v>
+        <v>0.0003586824013084966</v>
       </c>
       <c r="H31" t="n">
         <v>23</v>
@@ -1623,7 +1623,7 @@
         <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002606351639304116</v>
+        <v>0.0002606351639305005</v>
       </c>
       <c r="H32" t="n">
         <v>27</v>
@@ -1660,7 +1660,7 @@
         <v>26</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0001155041660675815</v>
+        <v>-0.0001155041660674594</v>
       </c>
       <c r="H33" t="n">
         <v>48</v>
@@ -1697,7 +1697,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0001113065420641712</v>
+        <v>0.0001113065420642156</v>
       </c>
       <c r="H34" t="n">
         <v>39</v>
@@ -1734,7 +1734,7 @@
         <v>37</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001328263492481829</v>
+        <v>0.0001328263492482495</v>
       </c>
       <c r="H35" t="n">
         <v>35</v>
@@ -1771,7 +1771,7 @@
         <v>48</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002131281393188966</v>
+        <v>0.0002131281393190188</v>
       </c>
       <c r="H36" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>23</v>
       </c>
       <c r="G37" t="n">
-        <v>5.023641873698192e-05</v>
+        <v>5.023641873712626e-05</v>
       </c>
       <c r="H37" t="n">
         <v>44</v>
@@ -1845,7 +1845,7 @@
         <v>31</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0002475134427031844</v>
+        <v>0.0002475134427032511</v>
       </c>
       <c r="H38" t="n">
         <v>31</v>
@@ -1882,7 +1882,7 @@
         <v>44</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0003265698677199391</v>
+        <v>0.0003265698677200501</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1919,7 +1919,7 @@
         <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002586429798237311</v>
+        <v>0.0002586429798238532</v>
       </c>
       <c r="H40" t="n">
         <v>28</v>
@@ -1956,7 +1956,7 @@
         <v>38</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0001214486152627092</v>
+        <v>0.0001214486152628202</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -1993,7 +1993,7 @@
         <v>35</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001663068606845841</v>
+        <v>0.0001663068606847062</v>
       </c>
       <c r="H42" t="n">
         <v>33</v>
@@ -2030,7 +2030,7 @@
         <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001178070486130389</v>
+        <v>0.0001178070486131277</v>
       </c>
       <c r="H43" t="n">
         <v>38</v>
@@ -2067,7 +2067,7 @@
         <v>41</v>
       </c>
       <c r="G44" t="n">
-        <v>0.000249494465474287</v>
+        <v>0.0002494944654743758</v>
       </c>
       <c r="H44" t="n">
         <v>30</v>
@@ -2104,7 +2104,7 @@
         <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0001087868324821439</v>
+        <v>-0.0001087868324819996</v>
       </c>
       <c r="H45" t="n">
         <v>47</v>
@@ -2141,7 +2141,7 @@
         <v>30</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0001576675489359247</v>
+        <v>-0.0001576675489357915</v>
       </c>
       <c r="H46" t="n">
         <v>51</v>
@@ -2178,7 +2178,7 @@
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0001482889034667201</v>
+        <v>-0.0001482889034666201</v>
       </c>
       <c r="H47" t="n">
         <v>50</v>
@@ -2215,7 +2215,7 @@
         <v>49</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0001310618297204469</v>
+        <v>0.0001310618297205579</v>
       </c>
       <c r="H48" t="n">
         <v>36</v>
@@ -2252,7 +2252,7 @@
         <v>39</v>
       </c>
       <c r="G49" t="n">
-        <v>4.006854685429939e-05</v>
+        <v>4.006854685442152e-05</v>
       </c>
       <c r="H49" t="n">
         <v>45</v>
@@ -2289,7 +2289,7 @@
         <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>8.039867084361774e-05</v>
+        <v>8.039867084372876e-05</v>
       </c>
       <c r="H50" t="n">
         <v>42</v>
@@ -2326,7 +2326,7 @@
         <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0001067792396374334</v>
+        <v>0.0001067792396375777</v>
       </c>
       <c r="H51" t="n">
         <v>40</v>
@@ -2363,7 +2363,7 @@
         <v>53</v>
       </c>
       <c r="G52" t="n">
-        <v>3.786355455392965e-05</v>
+        <v>3.786355455408508e-05</v>
       </c>
       <c r="H52" t="n">
         <v>46</v>
@@ -2400,7 +2400,7 @@
         <v>42</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.0001886907285609918</v>
+        <v>-0.0001886907285608585</v>
       </c>
       <c r="H53" t="n">
         <v>52</v>
@@ -2437,7 +2437,7 @@
         <v>51</v>
       </c>
       <c r="G54" t="n">
-        <v>7.768872334517063e-05</v>
+        <v>7.768872334530385e-05</v>
       </c>
       <c r="H54" t="n">
         <v>43</v>
@@ -2545,7 +2545,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08218501444886407</v>
+        <v>0.08218501444886418</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07162232356024348</v>
+        <v>0.0716223235602436</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04169327757849408</v>
+        <v>0.04169327757849419</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06790920862648733</v>
+        <v>0.06790920862648747</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403367403849274</v>
+        <v>0.01403367403853356</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06739341884767287</v>
+        <v>0.067393418847673</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01051785434685317</v>
+        <v>0.01051785434685325</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02109745917280919</v>
+        <v>0.02109745917280935</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002592940647117026</v>
+        <v>0.002592940647117114</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -2878,7 +2878,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002420162849803742</v>
+        <v>0.002420162849803853</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009235213308433566</v>
+        <v>0.009235213308433687</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -2952,7 +2952,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006130076013525665</v>
+        <v>0.0006130076013526776</v>
       </c>
       <c r="H13" t="n">
         <v>18</v>
@@ -2989,7 +2989,7 @@
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005878733118516611</v>
+        <v>0.0005878733118517942</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -3026,7 +3026,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001027549058435584</v>
+        <v>0.001027549058435706</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -3063,7 +3063,7 @@
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000643083991171689</v>
+        <v>0.000643083991171789</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004073596329023266</v>
+        <v>0.0004073596329024487</v>
       </c>
       <c r="H17" t="n">
         <v>22</v>
@@ -3137,7 +3137,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005685433167898823</v>
+        <v>0.0005685433167899823</v>
       </c>
       <c r="H18" t="n">
         <v>20</v>
@@ -3174,7 +3174,7 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001139467083597867</v>
+        <v>0.001139467083597945</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -3211,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>9.419230065841334e-05</v>
+        <v>9.419230065853546e-05</v>
       </c>
       <c r="H20" t="n">
         <v>41</v>
@@ -3248,7 +3248,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001651166613885435</v>
+        <v>0.001651166613885535</v>
       </c>
       <c r="H21" t="n">
         <v>12</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08218501444886407</v>
+        <v>0.08218501444886418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01141698427518707</v>
+        <v>0.01141698427518706</v>
       </c>
     </row>
     <row r="3">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07162232356024348</v>
+        <v>0.0716223235602436</v>
       </c>
       <c r="D3" t="n">
         <v>0.01066177504862114</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06790920862648733</v>
+        <v>0.06790920862648747</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01155419516112018</v>
+        <v>0.01155419516112021</v>
       </c>
     </row>
     <row r="5">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06739341884767287</v>
+        <v>0.067393418847673</v>
       </c>
       <c r="D5" t="n">
         <v>0.01008795011191899</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04169327757849408</v>
+        <v>0.04169327757849419</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007623898478615744</v>
+        <v>0.007623898478615741</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02109745917280919</v>
+        <v>0.02109745917280935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002949417463791526</v>
+        <v>0.00294941746379156</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01403367403849274</v>
+        <v>0.01403367403853356</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003242892811433474</v>
+        <v>0.003242892811433128</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01051785434685317</v>
+        <v>0.01051785434685325</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001076174911258317</v>
+        <v>0.001076174911258318</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009235213308433566</v>
+        <v>0.009235213308433687</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001324303416572418</v>
+        <v>0.001324303416572421</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002592940647117026</v>
+        <v>0.002592940647117114</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001015796128366716</v>
+        <v>0.001015796128366711</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002420162849803742</v>
+        <v>0.002420162849803853</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001109082392080396</v>
+        <v>0.001109082392080406</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001651166613885435</v>
+        <v>0.001651166613885535</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003524536365500912</v>
+        <v>0.0003524536365501381</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001139467083597867</v>
+        <v>0.001139467083597945</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006208881009843724</v>
+        <v>0.0006208881009843757</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001103279195960572</v>
+        <v>0.001103279195960694</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002989338058261137</v>
+        <v>0.0002989338058261344</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001027549058435584</v>
+        <v>0.001027549058435706</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0007335523118561347</v>
+        <v>0.0007335523118561375</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0006761052879341589</v>
+        <v>0.0006761052879342367</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003901997982442598</v>
+        <v>0.0003901997982442673</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.000643083991171689</v>
+        <v>0.000643083991171789</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0002453005202181975</v>
+        <v>0.00024530052021817</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006130076013525665</v>
+        <v>0.0006130076013526776</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003736264974452768</v>
+        <v>0.0003736264974452791</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005878733118516611</v>
+        <v>0.0005878733118517942</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002528177755247611</v>
+        <v>0.0002528177755247567</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005685433167898823</v>
+        <v>0.0005685433167899823</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000134007416767915</v>
+        <v>0.0001340074167679264</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005390648583790458</v>
+        <v>0.0005390648583792013</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0002809560041175864</v>
+        <v>0.00028095600411759</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004073596329023266</v>
+        <v>0.0004073596329024487</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004590466294514283</v>
+        <v>0.0004590466294514611</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003586824013083745</v>
+        <v>0.0003586824013084966</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0002046317526306413</v>
+        <v>0.0002046317526306474</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003265698677199391</v>
+        <v>0.0003265698677200501</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001039044267277166</v>
+        <v>0.0001039044267277263</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.000324552027778946</v>
+        <v>0.0003245520277790792</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001704088168848761</v>
+        <v>0.0001704088168848598</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.000282624680491228</v>
+        <v>0.0002826246804913058</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002098198022891136</v>
+        <v>0.0002098198022891296</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002606351639304116</v>
+        <v>0.0002606351639305005</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002308650490474039</v>
+        <v>0.0002308650490474207</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002586429798237311</v>
+        <v>0.0002586429798238532</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001351089986179497</v>
+        <v>0.0001351089986179646</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002508035987043522</v>
+        <v>0.0002508035987044743</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0004872567478689483</v>
+        <v>0.0004872567478689348</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.000249494465474287</v>
+        <v>0.0002494944654743758</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001399111512442106</v>
+        <v>0.0001399111512441868</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002475134427031844</v>
+        <v>0.0002475134427032511</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001698229151201552</v>
+        <v>0.0001698229151201856</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002131281393188966</v>
+        <v>0.0002131281393190188</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001764127558914285</v>
+        <v>0.0001764127558914487</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001663068606845841</v>
+        <v>0.0001663068606847062</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001967176820286803</v>
+        <v>0.0001967176820286465</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001490539406376556</v>
+        <v>0.0001490539406377667</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003291413621283385</v>
+        <v>0.0003291413621283354</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001328263492481829</v>
+        <v>0.0001328263492482495</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001153909443612429</v>
+        <v>0.000115390944361242</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001310618297204469</v>
+        <v>0.0001310618297205579</v>
       </c>
       <c r="D37" t="n">
-        <v>3.08437602860138e-05</v>
+        <v>3.084376028602637e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001214486152627092</v>
+        <v>0.0001214486152628202</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001039616189406464</v>
+        <v>0.0001039616189406716</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0001178070486130389</v>
+        <v>0.0001178070486131277</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001030200286077411</v>
+        <v>0.0001030200286077369</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0001113065420641712</v>
+        <v>0.0001113065420642156</v>
       </c>
       <c r="D40" t="n">
-        <v>7.446805171638141e-05</v>
+        <v>7.446805171635298e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0001067792396374334</v>
+        <v>0.0001067792396375777</v>
       </c>
       <c r="D41" t="n">
-        <v>6.09335495997491e-05</v>
+        <v>6.093354959974573e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9.419230065841334e-05</v>
+        <v>9.419230065853546e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001731845965015959</v>
+        <v>0.0001731845965015955</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8.039867084361774e-05</v>
+        <v>8.039867084372876e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>5.127768626722146e-05</v>
+        <v>5.127768626719862e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.768872334517063e-05</v>
+        <v>7.768872334530385e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>7.258119592487347e-05</v>
+        <v>7.258119592486828e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.023641873698192e-05</v>
+        <v>5.023641873712626e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002133286720324505</v>
+        <v>0.0002133286720324657</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.006854685429939e-05</v>
+        <v>4.006854685442152e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>1.572502966742423e-05</v>
+        <v>1.572502966741466e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.786355455392965e-05</v>
+        <v>3.786355455408508e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>1.556803031836518e-05</v>
+        <v>1.556803031834171e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.0001087868324821439</v>
+        <v>-0.0001087868324819996</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001130451266013766</v>
+        <v>0.000113045126601379</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.0001155041660675815</v>
+        <v>-0.0001155041660674594</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0003357481855654086</v>
+        <v>0.0003357481855654071</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001259134161154862</v>
+        <v>-0.000125913416115353</v>
       </c>
       <c r="D50" t="n">
-        <v>0.000205731715837911</v>
+        <v>0.0002057317158379142</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001482889034667201</v>
+        <v>-0.0001482889034666201</v>
       </c>
       <c r="D51" t="n">
-        <v>8.77721560419013e-05</v>
+        <v>8.777215604188761e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001576675489359247</v>
+        <v>-0.0001576675489357915</v>
       </c>
       <c r="D52" t="n">
-        <v>0.000194874282553393</v>
+        <v>0.0001948742825534112</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001886907285609918</v>
+        <v>-0.0001886907285608585</v>
       </c>
       <c r="D53" t="n">
-        <v>9.028791264926092e-05</v>
+        <v>9.028791264923976e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0003997428023372551</v>
+        <v>-0.0003997428023371219</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003761327267890014</v>
+        <v>0.0003761327267890083</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:01:33 UTC</t>
+          <t>2026-06-15 07:28:06 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,29 +497,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.197031979916397</v>
+        <v>0.2249600330622874</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3070676601677713</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.2151142192809106</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.08218501444886418</v>
+        <v>0.1101356574972846</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6825846368058115</v>
+        <v>0.628638765676294</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -534,32 +534,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1822093135670322</v>
+        <v>0.2297371563803232</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2303183402681055</v>
+        <v>0.1884205309998295</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0716223235602436</v>
+        <v>0.1256772075151103</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6200899517242822</v>
+        <v>0.52758974636818</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>2.5</v>
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1432788772187993</v>
+        <v>0.2137569927600728</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2478405711645279</v>
+        <v>0.3030728194555405</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04169327757849419</v>
+        <v>0.09347421320710961</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.601764780857478</v>
+        <v>0.5784427578282538</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1707695756402855</v>
+        <v>0.02074614879464609</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.144698018739101</v>
+        <v>0.08627741451796607</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06790920862648747</v>
+        <v>0.03042873337227854</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5310680760333479</v>
+        <v>3.051682038221639</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01371427929077212</v>
+        <v>0.2076717144263814</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05775896239923025</v>
+        <v>0.03773292007353681</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403367403853356</v>
+        <v>0.09126118549752468</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.626237445197282</v>
+        <v>0.4667763335361963</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -682,32 +682,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1780106703426724</v>
+        <v>0.01075895928057879</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01597906069969937</v>
+        <v>0.01989612114473691</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.067393418847673</v>
+        <v>0.01493386814484415</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4693524717652289</v>
+        <v>0.6677259618624269</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.008314331122088188</v>
+        <v>0.004723082091985941</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006835148585456436</v>
+        <v>0.004129461712466849</v>
       </c>
       <c r="F8" t="n">
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01051785434685325</v>
+        <v>0.003854486980480232</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6862377076477033</v>
+        <v>0.14632018652981</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>6.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,32 +756,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01390980338324053</v>
+        <v>0.006268652532458184</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01491685955454073</v>
+        <v>0.00271234490728671</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02109745917280935</v>
+        <v>0.003231531657921127</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09421368555932741</v>
+        <v>0.1444198025304533</v>
       </c>
       <c r="J9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
         <v>9</v>
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004248967520419441</v>
+        <v>0.003671077398420459</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003845010451561188</v>
+        <v>0.005977165730118234</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002592940647117114</v>
+        <v>0.001199055892000522</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.135460058653166</v>
+        <v>0.1011484633085336</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004565168569245587</v>
+        <v>0.003020422074537093</v>
       </c>
       <c r="D11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.002625110197965464</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001994297951204127</v>
+      </c>
+      <c r="H11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.002114894388361565</v>
-      </c>
-      <c r="F11" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.002420162849803853</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
       <c r="I11" t="n">
-        <v>0.1526701842303604</v>
+        <v>0.2736450829726844</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.006486740520454934</v>
+        <v>0.004963031669853181</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007049071314577241</v>
+        <v>0.001016805652254737</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009235213308433687</v>
+        <v>0.002274792673663329</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04589542792206514</v>
+        <v>0.08454816572163582</v>
       </c>
       <c r="J12" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>15.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002849862762434156</v>
+        <v>0.002865139542388522</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003127706299701867</v>
+        <v>0.001985510658313984</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006130076013526776</v>
+        <v>0.0004977753261798168</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09466269310465947</v>
+        <v>0.1082816052151783</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002688148546326715</v>
+        <v>0.001136976468236945</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003341993402721055</v>
+        <v>0.005882322997085859</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005878733118517942</v>
+        <v>0.0008274528163536576</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1178889635020983</v>
+        <v>0.3565482852349962</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003595278350624291</v>
+        <v>0.005266651839001327</v>
       </c>
       <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.002173698531118813</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001371583978240276</v>
+      </c>
+      <c r="H15" t="n">
         <v>12</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.001608605619664584</v>
-      </c>
-      <c r="F15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.001027549058435706</v>
-      </c>
-      <c r="H15" t="n">
-        <v>15</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.07428057261443222</v>
+        <v>0.03626006248108515</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002236047327322062</v>
+        <v>0.002630331745092964</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001643514043991867</v>
+        <v>0.001349679104284131</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000643083991171789</v>
+        <v>0.001298517390580056</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3031789140189818</v>
+        <v>0.08810704359802912</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003244512335033077</v>
+        <v>0.003250153998648266</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001583519635159759</v>
+        <v>0.00138182994042646</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004073596329024487</v>
+        <v>0.001468179813453951</v>
       </c>
       <c r="H17" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07069768157613066</v>
+        <v>0.04929084117337545</v>
       </c>
       <c r="J17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009079583826754834</v>
+        <v>0.00277665156109347</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002669343987540694</v>
+        <v>0.002714343391779137</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005685433167899823</v>
+        <v>9.819472509370319e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3506721756022313</v>
+        <v>0.142034242013684</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>21.75</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002813202939694079</v>
+        <v>0.003481397940997838</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001799890106828131</v>
+        <v>0.001290822844720225</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001139467083597945</v>
+        <v>0.0004980251420097836</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04066904872453581</v>
+        <v>0.05582197687698809</v>
       </c>
       <c r="J19" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002445006205074117</v>
+        <v>0.003656777401985017</v>
       </c>
       <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.001140531899620989</v>
+      </c>
+      <c r="F20" t="n">
         <v>23</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.001744319092412727</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
+        <v>0.0008720295904171227</v>
+      </c>
+      <c r="H20" t="n">
         <v>18</v>
       </c>
-      <c r="G20" t="n">
-        <v>9.419230065853546e-05</v>
-      </c>
-      <c r="H20" t="n">
-        <v>41</v>
-      </c>
       <c r="I20" t="n">
-        <v>0.1330697997089101</v>
+        <v>0.04741016747281979</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>23.5</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.003139731583109222</v>
+        <v>0.002624496393191303</v>
       </c>
       <c r="D21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.001401227497831593</v>
+      </c>
+      <c r="F21" t="n">
         <v>16</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.001132974778342241</v>
-      </c>
-      <c r="F21" t="n">
-        <v>32</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.001651166613885535</v>
+        <v>0.0001628362567438035</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04564151511307379</v>
+        <v>0.09458496714924447</v>
       </c>
       <c r="J21" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.003412132915666005</v>
+        <v>0.003300842539997743</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002172888587112184</v>
+        <v>0.0009897064782070928</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002508035987044743</v>
+        <v>0.0009362629714557257</v>
       </c>
       <c r="H22" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0432485231175872</v>
+        <v>0.04970375129050941</v>
       </c>
       <c r="J22" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K22" t="n">
-        <v>24.25</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002144640109328005</v>
+        <v>0.002121891681595817</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001239108793164929</v>
+        <v>0.0009450690010157058</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002826246804913058</v>
+        <v>0.001203068630195558</v>
       </c>
       <c r="H23" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08429095909465323</v>
+        <v>0.09382066269136446</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001990095665097817</v>
+        <v>0.003104313280346662</v>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>0.001214862866781157</v>
+        <v>0.0009624745051305981</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001103279195960694</v>
+        <v>0.0004925881431233625</v>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06001416912472735</v>
+        <v>0.05818587490142102</v>
       </c>
       <c r="J24" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001995631583116888</v>
+        <v>0.004007982098901283</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001093984071412021</v>
+        <v>0.001835311298248737</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003245520277790792</v>
+        <v>-0.0003255485579054196</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08755417700795398</v>
+        <v>0.06146607089113942</v>
       </c>
       <c r="J25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>27</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.002836662632711747</v>
+        <v>0.002853630884302312</v>
       </c>
       <c r="D26" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.001361336836835906</v>
+      </c>
+      <c r="F26" t="n">
         <v>19</v>
       </c>
-      <c r="E26" t="n">
-        <v>0.001349305935299087</v>
-      </c>
-      <c r="F26" t="n">
-        <v>24</v>
-      </c>
       <c r="G26" t="n">
-        <v>0.0006761052879342367</v>
+        <v>0.0007376550915579871</v>
       </c>
       <c r="H26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002951470240392329</v>
+        <v>0.0402140669325739</v>
       </c>
       <c r="J26" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002959161625982222</v>
+        <v>0.002188278998077275</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001497754221972584</v>
+        <v>0.0008438933792026576</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001490539406377667</v>
+        <v>0.0002009597504211702</v>
       </c>
       <c r="H27" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0455889057521599</v>
+        <v>0.1109852253967087</v>
       </c>
       <c r="J27" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.00358464268418929</v>
+        <v>0.00214140427216719</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001907090410030094</v>
+        <v>0.0006148936396986308</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0003997428023371219</v>
+        <v>0.0009174934430464688</v>
       </c>
       <c r="H28" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05395565520421641</v>
+        <v>0.09315514744763531</v>
       </c>
       <c r="J28" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>28.25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.002334541725108366</v>
+        <v>0.002488492928014623</v>
       </c>
       <c r="D29" t="n">
         <v>25</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001231221978513675</v>
+        <v>0.00136335667826171</v>
       </c>
       <c r="F29" t="n">
+        <v>18</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0002911331417709828</v>
+      </c>
+      <c r="H29" t="n">
+        <v>28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.04346904896110404</v>
+      </c>
+      <c r="J29" t="n">
+        <v>37</v>
+      </c>
+      <c r="K29" t="n">
         <v>27</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.0005390648583792013</v>
-      </c>
-      <c r="H29" t="n">
-        <v>21</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.03780709217900924</v>
-      </c>
-      <c r="J29" t="n">
-        <v>44</v>
-      </c>
-      <c r="K29" t="n">
-        <v>29.25</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.002142708186341778</v>
+        <v>0.002996567131693547</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001220283562262262</v>
+        <v>0.0009552070340407936</v>
       </c>
       <c r="F30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.000125913416115353</v>
+        <v>0.0007384543079383077</v>
       </c>
       <c r="H30" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1104152722501901</v>
+        <v>0.0056170208959756</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>30.5</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001730764595016379</v>
+        <v>0.002337410163119064</v>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0008199308959394844</v>
+        <v>0.0008398390541596806</v>
       </c>
       <c r="F31" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003586824013084966</v>
+        <v>7.085618611180067e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09077149718766542</v>
+        <v>0.06232311862611217</v>
       </c>
       <c r="J31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>31.25</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.002175155303313864</v>
+        <v>0.0002550375443550137</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001045149111347222</v>
+        <v>0.001109469670293946</v>
       </c>
       <c r="F32" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002606351639305005</v>
+        <v>0.000357700841847286</v>
       </c>
       <c r="H32" t="n">
         <v>27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.04812671572012839</v>
+        <v>0.04986537667656066</v>
       </c>
       <c r="J32" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K32" t="n">
-        <v>31.25</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.002651597576798392</v>
+        <v>0.00140994173483644</v>
       </c>
       <c r="D33" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001238094691828089</v>
+        <v>0.0008413773529255854</v>
       </c>
       <c r="F33" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0001155041660674594</v>
+        <v>0.0002053057573325412</v>
       </c>
       <c r="H33" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I33" t="n">
-        <v>0.05544883926129751</v>
+        <v>0.0544704905465383</v>
       </c>
       <c r="J33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.00186160791803372</v>
+        <v>0.001551323289864225</v>
       </c>
       <c r="D34" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001062720717738418</v>
+        <v>0.0008329472574595422</v>
       </c>
       <c r="F34" t="n">
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0001113065420642156</v>
+        <v>7.759509954886612e-05</v>
       </c>
       <c r="H34" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07358509242456135</v>
+        <v>0.05941103850045604</v>
       </c>
       <c r="J34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K34" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001887100017356224</v>
+        <v>0.0002226970328189405</v>
       </c>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00101160823327368</v>
+        <v>0.001286084909967553</v>
       </c>
       <c r="F35" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001328263492482495</v>
+        <v>0.000282216434646343</v>
       </c>
       <c r="H35" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I35" t="n">
-        <v>0.07154468054081509</v>
+        <v>0.04439662995690563</v>
       </c>
       <c r="J35" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K35" t="n">
-        <v>32.75</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001608372972853025</v>
+        <v>7.968796156534137e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E36" t="n">
-        <v>0.000776526603760119</v>
+        <v>0.001111807069179341</v>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002131281393190188</v>
+        <v>1.256222595352741e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1133893110299296</v>
+        <v>0.06730035974489557</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.00234330921351191</v>
+        <v>0.002213160456900288</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001477805675243302</v>
+        <v>0.0006207177874203655</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G37" t="n">
-        <v>5.023641873712626e-05</v>
+        <v>9.124614615965143e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I37" t="n">
-        <v>0.04230193990077913</v>
+        <v>0.05420509804064144</v>
       </c>
       <c r="J37" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K37" t="n">
-        <v>33</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.002259585179662545</v>
+        <v>0.001561693090291535</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001153249291774402</v>
+        <v>0.0007390823911810214</v>
       </c>
       <c r="F38" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0002475134427032511</v>
+        <v>-0.0001436746150003887</v>
       </c>
       <c r="H38" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03742666251680671</v>
+        <v>0.06696707702325888</v>
       </c>
       <c r="J38" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>33.25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001350173311601951</v>
+        <v>0.001364720713854286</v>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0008815156503392778</v>
+        <v>0.0007211233589692899</v>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0003265698677200501</v>
+        <v>0.0001678639336499033</v>
       </c>
       <c r="H39" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I39" t="n">
-        <v>0.06823029410260384</v>
+        <v>0.04654628224870994</v>
       </c>
       <c r="J39" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K39" t="n">
-        <v>33.75</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001227115416713972</v>
+        <v>0.001510431479491597</v>
       </c>
       <c r="D40" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0009428627077181219</v>
+        <v>0.0008181245475084968</v>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002586429798238532</v>
+        <v>-0.0001548931951984356</v>
       </c>
       <c r="H40" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="I40" t="n">
-        <v>0.06499045206156984</v>
+        <v>0.05743960891639244</v>
       </c>
       <c r="J40" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K40" t="n">
-        <v>35.25</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001283303293776476</v>
+        <v>0.001253598195479421</v>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001000011170424423</v>
+        <v>0.0006345849102692894</v>
       </c>
       <c r="F41" t="n">
+        <v>39</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0004247586407363446</v>
+      </c>
+      <c r="H41" t="n">
+        <v>25</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.04280126128907025</v>
+      </c>
+      <c r="J41" t="n">
         <v>38</v>
       </c>
-      <c r="G41" t="n">
-        <v>0.0001214486152628202</v>
-      </c>
-      <c r="H41" t="n">
-        <v>37</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.0537388094101563</v>
-      </c>
-      <c r="J41" t="n">
-        <v>32</v>
-      </c>
       <c r="K41" t="n">
-        <v>37</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001167662558019662</v>
+        <v>0.0005930573868952084</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E42" t="n">
-        <v>0.001049591901587422</v>
+        <v>0.0007205793920015511</v>
       </c>
       <c r="F42" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001663068606847062</v>
+        <v>0.0003737078159174123</v>
       </c>
       <c r="H42" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.04508849545986449</v>
+        <v>0.004570043147792191</v>
       </c>
       <c r="J42" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K42" t="n">
-        <v>37.25</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001104109263332111</v>
+        <v>0.00195161880257588</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000865793983920894</v>
+        <v>0.0005802728225214927</v>
       </c>
       <c r="F43" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001178070486131277</v>
+        <v>5.706794649815716e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.07264352192166257</v>
+        <v>0.04507494896290476</v>
       </c>
       <c r="J43" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K43" t="n">
-        <v>37.75</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001731580648066713</v>
+        <v>0.000308508794576968</v>
       </c>
       <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0003812747147695615</v>
+      </c>
+      <c r="F44" t="n">
+        <v>44</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7.924446304518052e-05</v>
+      </c>
+      <c r="H44" t="n">
         <v>36</v>
       </c>
-      <c r="E44" t="n">
-        <v>0.000968009359778049</v>
-      </c>
-      <c r="F44" t="n">
-        <v>41</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.0002494944654743758</v>
-      </c>
-      <c r="H44" t="n">
-        <v>30</v>
-      </c>
       <c r="I44" t="n">
-        <v>0.006997474455073149</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>39.25</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001515408891322052</v>
+        <v>9.338909355280864e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0009832362775042921</v>
+        <v>0.0004566433722776589</v>
       </c>
       <c r="F45" t="n">
+        <v>43</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.623479426105748e-05</v>
+      </c>
+      <c r="H45" t="n">
         <v>40</v>
       </c>
-      <c r="G45" t="n">
-        <v>-0.0001087868324819996</v>
-      </c>
-      <c r="H45" t="n">
-        <v>47</v>
-      </c>
       <c r="I45" t="n">
-        <v>0.05146667654081938</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>39.75</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="46">
@@ -2125,331 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001899029504987533</v>
+        <v>0.0001244730825463604</v>
       </c>
       <c r="D46" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001205054300212215</v>
+        <v>0.0001865011137995352</v>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0001576675489357915</v>
+        <v>-7.880653300020856e-05</v>
       </c>
       <c r="H46" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I46" t="n">
-        <v>0.03093975615808375</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>40.25</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>wastewater_r1_pol</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.001090508675920083</v>
-      </c>
-      <c r="D47" t="n">
-        <v>45</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.0008711113564648789</v>
-      </c>
-      <c r="F47" t="n">
-        <v>45</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.0001482889034666201</v>
-      </c>
-      <c r="H47" t="n">
-        <v>50</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.07251336273382991</v>
-      </c>
-      <c r="J47" t="n">
-        <v>24</v>
-      </c>
-      <c r="K47" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0003376471091931949</v>
-      </c>
-      <c r="D48" t="n">
-        <v>47</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.0006833324838897081</v>
-      </c>
-      <c r="F48" t="n">
-        <v>49</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.0001310618297205579</v>
-      </c>
-      <c r="H48" t="n">
-        <v>36</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.03328204574181282</v>
-      </c>
-      <c r="J48" t="n">
-        <v>46</v>
-      </c>
-      <c r="K48" t="n">
-        <v>44.5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>work_period</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>8.383859122599245e-05</v>
-      </c>
-      <c r="D49" t="n">
-        <v>52</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.0009950679928468313</v>
-      </c>
-      <c r="F49" t="n">
-        <v>39</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.006854685442152e-05</v>
-      </c>
-      <c r="H49" t="n">
-        <v>45</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.02752738838177793</v>
-      </c>
-      <c r="J49" t="n">
-        <v>48</v>
-      </c>
-      <c r="K49" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0001460040018972183</v>
-      </c>
-      <c r="D50" t="n">
-        <v>51</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.0005720116476741351</v>
-      </c>
-      <c r="F50" t="n">
-        <v>50</v>
-      </c>
-      <c r="G50" t="n">
-        <v>8.039867084372876e-05</v>
-      </c>
-      <c r="H50" t="n">
-        <v>42</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.03919358873285139</v>
-      </c>
-      <c r="J50" t="n">
-        <v>43</v>
-      </c>
-      <c r="K50" t="n">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0001711974007209496</v>
-      </c>
-      <c r="D51" t="n">
-        <v>50</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.0004505128958804968</v>
-      </c>
-      <c r="F51" t="n">
-        <v>52</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.0001067792396375777</v>
-      </c>
-      <c r="H51" t="n">
-        <v>40</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.02325339844985908</v>
-      </c>
-      <c r="J51" t="n">
-        <v>49</v>
-      </c>
-      <c r="K51" t="n">
-        <v>47.75</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>8.005142757552094e-05</v>
-      </c>
-      <c r="D52" t="n">
-        <v>53</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.0004057401125536971</v>
-      </c>
-      <c r="F52" t="n">
-        <v>53</v>
-      </c>
-      <c r="G52" t="n">
-        <v>3.786355455408508e-05</v>
-      </c>
-      <c r="H52" t="n">
-        <v>46</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.04365029460796976</v>
-      </c>
-      <c r="J52" t="n">
-        <v>39</v>
-      </c>
-      <c r="K52" t="n">
-        <v>47.75</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0002594094891159516</v>
-      </c>
-      <c r="D53" t="n">
-        <v>48</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.000964441945781453</v>
-      </c>
-      <c r="F53" t="n">
-        <v>42</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-0.0001886907285608585</v>
-      </c>
-      <c r="H53" t="n">
-        <v>52</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>52</v>
-      </c>
-      <c r="K53" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0001757949887419857</v>
-      </c>
-      <c r="D54" t="n">
-        <v>49</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0005280967535366773</v>
-      </c>
-      <c r="F54" t="n">
-        <v>51</v>
-      </c>
-      <c r="G54" t="n">
-        <v>7.768872334530385e-05</v>
-      </c>
-      <c r="H54" t="n">
-        <v>43</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>52</v>
-      </c>
-      <c r="K54" t="n">
-        <v>48.75</v>
+        <v>43.25</v>
       </c>
     </row>
   </sheetData>
@@ -2529,29 +2233,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.197031979916397</v>
+        <v>0.2249600330622874</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3070676601677713</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.2151142192809106</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.08218501444886418</v>
+        <v>0.1101356574972846</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6825846368058115</v>
+        <v>0.628638765676294</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -2566,32 +2270,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1822093135670322</v>
+        <v>0.2297371563803232</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2303183402681055</v>
+        <v>0.1884205309998295</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0716223235602436</v>
+        <v>0.1256772075151103</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6200899517242822</v>
+        <v>0.52758974636818</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>2.5</v>
@@ -2607,31 +2311,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1432788772187993</v>
+        <v>0.2137569927600728</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2478405711645279</v>
+        <v>0.3030728194555405</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04169327757849419</v>
+        <v>0.09347421320710961</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.601764780857478</v>
+        <v>0.5784427578282538</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2640,35 +2344,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1707695756402855</v>
+        <v>0.02074614879464609</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.144698018739101</v>
+        <v>0.08627741451796607</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06790920862648747</v>
+        <v>0.03042873337227854</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5310680760333479</v>
+        <v>3.051682038221639</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="6">
@@ -2677,35 +2381,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01371427929077212</v>
+        <v>0.2076717144263814</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05775896239923025</v>
+        <v>0.03773292007353681</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403367403853356</v>
+        <v>0.09126118549752468</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.626237445197282</v>
+        <v>0.4667763335361963</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -2714,32 +2418,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1780106703426724</v>
+        <v>0.01075895928057879</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01597906069969937</v>
+        <v>0.01989612114473691</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.067393418847673</v>
+        <v>0.01493386814484415</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4693524717652289</v>
+        <v>0.6677259618624269</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -2751,35 +2455,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.008314331122088188</v>
+        <v>0.004723082091985941</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006835148585456436</v>
+        <v>0.004129461712466849</v>
       </c>
       <c r="F8" t="n">
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01051785434685325</v>
+        <v>0.003854486980480232</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6862377076477033</v>
+        <v>0.14632018652981</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>6.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="9">
@@ -2788,32 +2492,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01390980338324053</v>
+        <v>0.006268652532458184</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01491685955454073</v>
+        <v>0.00271234490728671</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02109745917280935</v>
+        <v>0.003231531657921127</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09421368555932741</v>
+        <v>0.1444198025304533</v>
       </c>
       <c r="J9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
         <v>9</v>
@@ -2825,35 +2529,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004248967520419441</v>
+        <v>0.003671077398420459</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003845010451561188</v>
+        <v>0.005977165730118234</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002592940647117114</v>
+        <v>0.001199055892000522</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.135460058653166</v>
+        <v>0.1011484633085336</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2566,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004565168569245587</v>
+        <v>0.003020422074537093</v>
       </c>
       <c r="D11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.002625110197965464</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001994297951204127</v>
+      </c>
+      <c r="H11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.002114894388361565</v>
-      </c>
-      <c r="F11" t="n">
-        <v>15</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.002420162849803853</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
       <c r="I11" t="n">
-        <v>0.1526701842303604</v>
+        <v>0.2736450829726844</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2603,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.006486740520454934</v>
+        <v>0.004963031669853181</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007049071314577241</v>
+        <v>0.001016805652254737</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009235213308433687</v>
+        <v>0.002274792673663329</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04589542792206514</v>
+        <v>0.08454816572163582</v>
       </c>
       <c r="J12" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>15.25</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="13">
@@ -2936,35 +2640,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002849862762434156</v>
+        <v>0.002865139542388522</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003127706299701867</v>
+        <v>0.001985510658313984</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006130076013526776</v>
+        <v>0.0004977753261798168</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09466269310465947</v>
+        <v>0.1082816052151783</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="14">
@@ -2973,35 +2677,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002688148546326715</v>
+        <v>0.001136976468236945</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003341993402721055</v>
+        <v>0.005882322997085859</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005878733118517942</v>
+        <v>0.0008274528163536576</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1178889635020983</v>
+        <v>0.3565482852349962</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -3010,35 +2714,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003595278350624291</v>
+        <v>0.005266651839001327</v>
       </c>
       <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.002173698531118813</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001371583978240276</v>
+      </c>
+      <c r="H15" t="n">
         <v>12</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.001608605619664584</v>
-      </c>
-      <c r="F15" t="n">
-        <v>20</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.001027549058435706</v>
-      </c>
-      <c r="H15" t="n">
-        <v>15</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.07428057261443222</v>
+        <v>0.03626006248108515</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>17</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="16">
@@ -3047,35 +2751,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002236047327322062</v>
+        <v>0.002630331745092964</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001643514043991867</v>
+        <v>0.001349679104284131</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000643083991171789</v>
+        <v>0.001298517390580056</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3031789140189818</v>
+        <v>0.08810704359802912</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +2788,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003244512335033077</v>
+        <v>0.003250153998648266</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001583519635159759</v>
+        <v>0.00138182994042646</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004073596329024487</v>
+        <v>0.001468179813453951</v>
       </c>
       <c r="H17" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07069768157613066</v>
+        <v>0.04929084117337545</v>
       </c>
       <c r="J17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +2825,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009079583826754834</v>
+        <v>0.00277665156109347</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002669343987540694</v>
+        <v>0.002714343391779137</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005685433167899823</v>
+        <v>9.819472509370319e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3506721756022313</v>
+        <v>0.142034242013684</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>21.75</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +2862,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002813202939694079</v>
+        <v>0.003481397940997838</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001799890106828131</v>
+        <v>0.001290822844720225</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001139467083597945</v>
+        <v>0.0004980251420097836</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04066904872453581</v>
+        <v>0.05582197687698809</v>
       </c>
       <c r="J19" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +2899,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002445006205074117</v>
+        <v>0.003656777401985017</v>
       </c>
       <c r="D20" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.001140531899620989</v>
+      </c>
+      <c r="F20" t="n">
         <v>23</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.001744319092412727</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
+        <v>0.0008720295904171227</v>
+      </c>
+      <c r="H20" t="n">
         <v>18</v>
       </c>
-      <c r="G20" t="n">
-        <v>9.419230065853546e-05</v>
-      </c>
-      <c r="H20" t="n">
-        <v>41</v>
-      </c>
       <c r="I20" t="n">
-        <v>0.1330697997089101</v>
+        <v>0.04741016747281979</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>23.5</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +2936,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.003139731583109222</v>
+        <v>0.002624496393191303</v>
       </c>
       <c r="D21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.001401227497831593</v>
+      </c>
+      <c r="F21" t="n">
         <v>16</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.001132974778342241</v>
-      </c>
-      <c r="F21" t="n">
-        <v>32</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.001651166613885535</v>
+        <v>0.0001628362567438035</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I21" t="n">
-        <v>0.04564151511307379</v>
+        <v>0.09458496714924447</v>
       </c>
       <c r="J21" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,11 +3004,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.197031979916397</v>
+        <v>0.2297371563803232</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3021,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1822093135670322</v>
+        <v>0.2249600330622874</v>
       </c>
     </row>
     <row r="4">
@@ -3326,11 +3030,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1780106703426724</v>
+        <v>0.2137569927600728</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3043,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1707695756402855</v>
+        <v>0.2076717144263814</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3056,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1432788772187993</v>
+        <v>0.02074614879464609</v>
       </c>
     </row>
     <row r="7">
@@ -3365,11 +3069,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01390980338324053</v>
+        <v>0.01075895928057879</v>
       </c>
     </row>
     <row r="8">
@@ -3378,11 +3082,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01371427929077212</v>
+        <v>0.006268652532458184</v>
       </c>
     </row>
     <row r="9">
@@ -3391,11 +3095,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.008314331122088188</v>
+        <v>0.005266651839001327</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3108,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006486740520454934</v>
+        <v>0.004963031669853181</v>
       </c>
     </row>
     <row r="11">
@@ -3417,11 +3121,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004565168569245587</v>
+        <v>0.004723082091985941</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3134,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004248967520419441</v>
+        <v>0.004007982098901283</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3147,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003595278350624291</v>
+        <v>0.003671077398420459</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3160,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00358464268418929</v>
+        <v>0.003656777401985017</v>
       </c>
     </row>
     <row r="15">
@@ -3469,11 +3173,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003412132915666005</v>
+        <v>0.003481397940997838</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3186,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003244512335033077</v>
+        <v>0.003300842539997743</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3199,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003139731583109222</v>
+        <v>0.003250153998648266</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3212,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002959161625982222</v>
+        <v>0.003104313280346662</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3225,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002849862762434156</v>
+        <v>0.003020422074537093</v>
       </c>
     </row>
     <row r="20">
@@ -3538,7 +3242,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002836662632711747</v>
+        <v>0.002996567131693547</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3251,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002813202939694079</v>
+        <v>0.002865139542388522</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3264,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.002688148546326715</v>
+        <v>0.002853630884302312</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3277,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002651597576798392</v>
+        <v>0.00277665156109347</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3290,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.002445006205074117</v>
+        <v>0.002630331745092964</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3303,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.00234330921351191</v>
+        <v>0.002624496393191303</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3316,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.002334541725108366</v>
+        <v>0.002488492928014623</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3329,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002259585179662545</v>
+        <v>0.002337410163119064</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3342,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.002236047327322062</v>
+        <v>0.002213160456900288</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3355,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.002175155303313864</v>
+        <v>0.002188278998077275</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3368,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.002144640109328005</v>
+        <v>0.00214140427216719</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3381,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.002142708186341778</v>
+        <v>0.002121891681595817</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3394,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001995631583116888</v>
+        <v>0.00195161880257588</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3407,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001990095665097817</v>
+        <v>0.001561693090291535</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3420,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001899029504987533</v>
+        <v>0.001551323289864225</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3433,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001887100017356224</v>
+        <v>0.001510431479491597</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3446,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.00186160791803372</v>
+        <v>0.00140994173483644</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3459,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001731580648066713</v>
+        <v>0.001364720713854286</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3472,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001730764595016379</v>
+        <v>0.001253598195479421</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3485,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001608372972853025</v>
+        <v>0.001136976468236945</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3498,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001515408891322052</v>
+        <v>0.0005930573868952084</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3511,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001350173311601951</v>
+        <v>0.000308508794576968</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3524,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001283303293776476</v>
+        <v>0.0002550375443550137</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3537,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001227115416713972</v>
+        <v>0.0002226970328189405</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3550,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001167662558019662</v>
+        <v>0.0001244730825463604</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3563,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001104109263332111</v>
+        <v>9.338909355280864e-05</v>
       </c>
     </row>
     <row r="46">
@@ -3872,115 +3576,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001090508675920083</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>report_date_month</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0009079583826754834</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0003376471091931949</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0002594094891159516</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0001757949887419857</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0001711974007209496</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0001460040018972183</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>work_period</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>8.383859122599245e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>8.005142757552094e-05</v>
+        <v>7.968796156534137e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3994,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4020,11 +3620,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2478405711645279</v>
+        <v>0.3070676601677713</v>
       </c>
     </row>
     <row r="3">
@@ -4033,11 +3633,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2303183402681055</v>
+        <v>0.3030728194555405</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +3646,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2151142192809106</v>
+        <v>0.1884205309998295</v>
       </c>
     </row>
     <row r="5">
@@ -4059,11 +3659,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.144698018739101</v>
+        <v>0.08627741451796607</v>
       </c>
     </row>
     <row r="6">
@@ -4072,11 +3672,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05775896239923025</v>
+        <v>0.03773292007353681</v>
       </c>
     </row>
     <row r="7">
@@ -4085,11 +3685,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01597906069969937</v>
+        <v>0.01989612114473691</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +3698,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01491685955454073</v>
+        <v>0.005977165730118234</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +3711,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007049071314577241</v>
+        <v>0.005882322997085859</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +3724,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006835148585456436</v>
+        <v>0.004129461712466849</v>
       </c>
     </row>
     <row r="11">
@@ -4137,11 +3737,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003845010451561188</v>
+        <v>0.002714343391779137</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +3750,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003341993402721055</v>
+        <v>0.00271234490728671</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +3763,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003127706299701867</v>
+        <v>0.002625110197965464</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +3776,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002669343987540694</v>
+        <v>0.002173698531118813</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +3789,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002172888587112184</v>
+        <v>0.001985510658313984</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +3802,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002114894388361565</v>
+        <v>0.001835311298248737</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +3815,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001907090410030094</v>
+        <v>0.001401227497831593</v>
       </c>
     </row>
     <row r="18">
@@ -4232,7 +3832,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001799890106828131</v>
+        <v>0.00138182994042646</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +3841,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001744319092412727</v>
+        <v>0.00136335667826171</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +3854,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001643514043991867</v>
+        <v>0.001361336836835906</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +3867,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001608605619664584</v>
+        <v>0.001349679104284131</v>
       </c>
     </row>
     <row r="22">
@@ -4284,7 +3884,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001583519635159759</v>
+        <v>0.001290822844720225</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +3893,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001497754221972584</v>
+        <v>0.001286084909967553</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +3906,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001477805675243302</v>
+        <v>0.001140531899620989</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +3919,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001349305935299087</v>
+        <v>0.001111807069179341</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +3932,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001239108793164929</v>
+        <v>0.001109469670293946</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +3945,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001238094691828089</v>
+        <v>0.001016805652254737</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +3958,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001231221978513675</v>
+        <v>0.0009897064782070928</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +3971,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001220283562262262</v>
+        <v>0.0009624745051305981</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +3984,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001214862866781157</v>
+        <v>0.0009552070340407936</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +3997,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001205054300212215</v>
+        <v>0.0009450690010157058</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4010,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001153249291774402</v>
+        <v>0.0008438933792026576</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4023,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001132974778342241</v>
+        <v>0.0008413773529255854</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4036,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001093984071412021</v>
+        <v>0.0008398390541596806</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4049,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001062720717738418</v>
+        <v>0.0008329472574595422</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4062,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001049591901587422</v>
+        <v>0.0008181245475084968</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4075,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001045149111347222</v>
+        <v>0.0007390823911810214</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4088,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00101160823327368</v>
+        <v>0.0007211233589692899</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4101,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001000011170424423</v>
+        <v>0.0007205793920015511</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4114,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0009950679928468313</v>
+        <v>0.0006345849102692894</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4127,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0009832362775042921</v>
+        <v>0.0006207177874203655</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4140,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.000968009359778049</v>
+        <v>0.0006148936396986308</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4153,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.000964441945781453</v>
+        <v>0.0005802728225214927</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4166,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0009428627077181219</v>
+        <v>0.0004566433722776589</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4179,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0008815156503392778</v>
+        <v>0.0003812747147695615</v>
       </c>
     </row>
     <row r="46">
@@ -4592,115 +4192,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0008711113564648789</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>boiling_r1_pol</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.000865793983920894</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>boiling_r1_q</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0008199308959394844</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>wastewater_r1_q</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.000776526603760119</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0006833324838897081</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0005720116476741351</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0005280967535366773</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0004505128958804968</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0004057401125536971</v>
+        <v>0.0001865011137995352</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4745,14 +4241,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08218501444886418</v>
+        <v>0.1256772075151103</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01141698427518706</v>
+        <v>0.016835141956822</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0716223235602436</v>
+        <v>0.1101356574972846</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01066177504862114</v>
+        <v>0.01389034505627971</v>
       </c>
     </row>
     <row r="4">
@@ -4777,14 +4273,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06790920862648747</v>
+        <v>0.09347421320710961</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01155419516112021</v>
+        <v>0.01255366006353837</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.067393418847673</v>
+        <v>0.09126118549752468</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01008795011191899</v>
+        <v>0.01196930717930915</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4305,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04169327757849419</v>
+        <v>0.03042873337227854</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007623898478615741</v>
+        <v>0.00561072410377823</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4321,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02109745917280935</v>
+        <v>0.01493386814484415</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00294941746379156</v>
+        <v>0.001401253832068063</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4337,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01403367403853356</v>
+        <v>0.003854486980480232</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003242892811433128</v>
+        <v>0.00114503134251664</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4353,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01051785434685325</v>
+        <v>0.003231531657921127</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001076174911258318</v>
+        <v>0.001836698712560252</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4369,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009235213308433687</v>
+        <v>0.002274792673663329</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001324303416572421</v>
+        <v>0.001055469594516226</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4385,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002592940647117114</v>
+        <v>0.001994297951204127</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001015796128366711</v>
+        <v>0.0003342616438628584</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4401,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002420162849803853</v>
+        <v>0.001468179813453951</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001109082392080406</v>
+        <v>0.0005916779556746199</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4417,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001651166613885535</v>
+        <v>0.001371583978240276</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003524536365501381</v>
+        <v>0.0008166311074285969</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4433,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001139467083597945</v>
+        <v>0.001298517390580056</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006208881009843757</v>
+        <v>0.0004506783649985769</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4449,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001103279195960694</v>
+        <v>0.001203068630195558</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002989338058261344</v>
+        <v>0.0003205316879511416</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4465,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001027549058435706</v>
+        <v>0.001199055892000522</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0007335523118561375</v>
+        <v>0.0004887136503401856</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4481,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0006761052879342367</v>
+        <v>0.0009362629714557257</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003901997982442673</v>
+        <v>0.0003387140973519214</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +4497,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.000643083991171789</v>
+        <v>0.0009174934430464688</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00024530052021817</v>
+        <v>0.0003191821293565187</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +4513,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006130076013526776</v>
+        <v>0.0008720295904171227</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003736264974452791</v>
+        <v>0.0005568892976235559</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +4529,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005878733118517942</v>
+        <v>0.0008274528163536576</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002528177755247567</v>
+        <v>0.0002367955934665124</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +4545,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005685433167899823</v>
+        <v>0.0007384543079383077</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001340074167679264</v>
+        <v>0.000363259904288909</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +4561,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005390648583792013</v>
+        <v>0.0007376550915579871</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00028095600411759</v>
+        <v>0.0006034839796972832</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004073596329024487</v>
+        <v>0.0004980251420097836</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004590466294514611</v>
+        <v>0.0003977421186679194</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +4593,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003586824013084966</v>
+        <v>0.0004977753261798168</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0002046317526306474</v>
+        <v>0.000352275326366964</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +4609,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003265698677200501</v>
+        <v>0.0004925881431233625</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001039044267277263</v>
+        <v>0.000295463675228595</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +4625,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003245520277790792</v>
+        <v>0.0004247586407363446</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001704088168848598</v>
+        <v>0.0001571132393653013</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +4641,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0002826246804913058</v>
+        <v>0.0003737078159174123</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002098198022891296</v>
+        <v>0.0001808774615860588</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +4657,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002606351639305005</v>
+        <v>0.000357700841847286</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002308650490474207</v>
+        <v>0.0001254973962729597</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +4673,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002586429798238532</v>
+        <v>0.0002911331417709828</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001351089986179646</v>
+        <v>0.0002061970932727222</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +4689,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002508035987044743</v>
+        <v>0.000282216434646343</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0004872567478689348</v>
+        <v>8.934620799273859e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +4705,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002494944654743758</v>
+        <v>0.0002053057573325412</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001399111512441868</v>
+        <v>9.770461187118603e-05</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +4721,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002475134427032511</v>
+        <v>0.0002009597504211702</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001698229151201856</v>
+        <v>0.0001884746095905928</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +4737,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002131281393190188</v>
+        <v>0.0001678639336499033</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001764127558914487</v>
+        <v>9.294777128641642e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +4753,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001663068606847062</v>
+        <v>0.0001628362567438035</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001967176820286465</v>
+        <v>0.0003491156731842648</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +4769,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001490539406377667</v>
+        <v>9.819472509370319e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003291413621283354</v>
+        <v>0.0001433059865535373</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001328263492482495</v>
+        <v>9.124614615965143e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.000115390944361242</v>
+        <v>0.0002304749620182342</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001310618297205579</v>
+        <v>7.924446304518052e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>3.084376028602637e-05</v>
+        <v>3.618811264371063e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +4817,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001214486152628202</v>
+        <v>7.759509954886612e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001039616189406716</v>
+        <v>0.000231849276150103</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +4833,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0001178070486131277</v>
+        <v>7.085618611180067e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001030200286077369</v>
+        <v>0.0001995517907383684</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +4849,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0001113065420642156</v>
+        <v>5.706794649815716e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>7.446805171635298e-05</v>
+        <v>0.0002066002025036027</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +4865,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0001067792396375777</v>
+        <v>4.623479426105748e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>6.093354959974573e-05</v>
+        <v>2.488269909435861e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +4881,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9.419230065853546e-05</v>
+        <v>1.256222595352741e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001731845965015955</v>
+        <v>1.52615584480706e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +4897,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8.039867084372876e-05</v>
+        <v>-7.880653300020856e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>5.127768626719862e-05</v>
+        <v>3.254056014070438e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +4913,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.768872334530385e-05</v>
+        <v>-0.0001436746150003887</v>
       </c>
       <c r="D44" t="n">
-        <v>7.258119592486828e-05</v>
+        <v>0.000151125619662043</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +4929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.023641873712626e-05</v>
+        <v>-0.0001548931951984356</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002133286720324657</v>
+        <v>0.000215128270584015</v>
       </c>
     </row>
     <row r="46">
@@ -5449,142 +4945,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.006854685442152e-05</v>
+        <v>-0.0003255485579054196</v>
       </c>
       <c r="D46" t="n">
-        <v>1.572502966741466e-05</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>3.786355455408508e-05</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1.556803031834171e-05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.0001087868324819996</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.000113045126601379</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.0001155041660674594</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.0003357481855654071</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiler_pH</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.000125913416115353</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.0002057317158379142</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>wastewater_r1_pol</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.0001482889034666201</v>
-      </c>
-      <c r="D51" t="n">
-        <v>8.777215604188761e-05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>white_quality_apparent_color_2</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.0001576675489357915</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.0001948742825534112</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0001886907285608585</v>
-      </c>
-      <c r="D53" t="n">
-        <v>9.028791264923976e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>sweetwater_brix</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.0003997428023371219</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.0003761327267890083</v>
+        <v>0.0003965749009709757</v>
       </c>
     </row>
   </sheetData>
@@ -5598,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5628,7 +4996,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.626237445197282</v>
+        <v>3.051682038221639</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5009,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.6862377076477033</v>
+        <v>0.6677259618624269</v>
       </c>
     </row>
     <row r="4">
@@ -5650,11 +5018,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6825846368058115</v>
+        <v>0.628638765676294</v>
       </c>
     </row>
     <row r="5">
@@ -5663,11 +5031,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6200899517242822</v>
+        <v>0.5784427578282538</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5044,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.601764780857478</v>
+        <v>0.52758974636818</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5057,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5310680760333479</v>
+        <v>0.4667763335361963</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5070,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4693524717652289</v>
+        <v>0.3565482852349962</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5083,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3506721756022313</v>
+        <v>0.2736450829726844</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5096,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3031789140189818</v>
+        <v>0.14632018652981</v>
       </c>
     </row>
     <row r="11">
@@ -5745,7 +5113,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1526701842303604</v>
+        <v>0.1444198025304533</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5122,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.135460058653166</v>
+        <v>0.142034242013684</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5135,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1330697997089101</v>
+        <v>0.1109852253967087</v>
       </c>
     </row>
     <row r="14">
@@ -5784,7 +5152,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1178889635020983</v>
+        <v>0.1082816052151783</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5161,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1133893110299296</v>
+        <v>0.1011484633085336</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5174,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1104152722501901</v>
+        <v>0.09458496714924447</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5187,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.09466269310465947</v>
+        <v>0.09382066269136446</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5200,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.09421368555932741</v>
+        <v>0.09315514744763531</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5213,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.09077149718766542</v>
+        <v>0.08810704359802912</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5226,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.08755417700795398</v>
+        <v>0.08454816572163582</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5239,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.08429095909465323</v>
+        <v>0.06730035974489557</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5252,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.07428057261443222</v>
+        <v>0.06696707702325888</v>
       </c>
     </row>
     <row r="23">
@@ -5901,7 +5269,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.07358509242456135</v>
+        <v>0.06232311862611217</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5278,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.07264352192166257</v>
+        <v>0.06146607089113942</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5291,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.07251336273382991</v>
+        <v>0.05941103850045604</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5304,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07154468054081509</v>
+        <v>0.05818587490142102</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5317,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.07069768157613066</v>
+        <v>0.05743960891639244</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5330,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.06823029410260384</v>
+        <v>0.05582197687698809</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5343,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.06499045206156984</v>
+        <v>0.0544704905465383</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5356,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.06001416912472735</v>
+        <v>0.05420509804064144</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5369,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.05544883926129751</v>
+        <v>0.04986537667656066</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +5382,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.05395565520421641</v>
+        <v>0.04970375129050941</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +5395,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0537388094101563</v>
+        <v>0.04929084117337545</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +5408,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.05146667654081938</v>
+        <v>0.04741016747281979</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +5421,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.04812671572012839</v>
+        <v>0.04654628224870994</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +5434,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.04589542792206514</v>
+        <v>0.04507494896290476</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +5447,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.04564151511307379</v>
+        <v>0.04439662995690563</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +5460,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0455889057521599</v>
+        <v>0.04346904896110404</v>
       </c>
     </row>
     <row r="39">
@@ -6109,7 +5477,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.04508849545986449</v>
+        <v>0.04280126128907025</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +5486,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.04365029460796976</v>
+        <v>0.0402140669325739</v>
       </c>
     </row>
     <row r="41">
@@ -6135,7 +5503,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0432485231175872</v>
+        <v>0.03626006248108515</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +5512,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.04230193990077913</v>
+        <v>0.0056170208959756</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +5525,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.04066904872453581</v>
+        <v>0.004570043147792191</v>
       </c>
     </row>
     <row r="44">
@@ -6170,140 +5538,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.03919358873285139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.03780709217900924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.03742666251680671</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.03328204574181282</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_apparent_color_2</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.03093975615808375</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>work_period</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.02752738838177793</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.02325339844985908</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>white_quality_solution_color_1</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.006997474455073149</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>standard_liquor_brix</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.002951470240392329</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6379,10 +5643,10 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6391,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:28:06 UTC</t>
+          <t>2026-06-16 11:50:39 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1101356574972846</v>
+        <v>0.1101356574972847</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1256772075151103</v>
+        <v>0.1256772075151104</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -587,7 +587,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09347421320710961</v>
+        <v>0.09347421320710972</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03042873337227854</v>
+        <v>0.0304287333723191</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09126118549752468</v>
+        <v>0.09126118549752479</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01493386814484415</v>
+        <v>0.01493386814484425</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003854486980480232</v>
+        <v>0.003854486980480354</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003231531657921127</v>
+        <v>0.003231531657921271</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -809,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001199055892000522</v>
+        <v>0.001199055892000633</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001994297951204127</v>
+        <v>0.001994297951204193</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
         <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002274792673663329</v>
+        <v>0.00227479267366345</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -920,7 +920,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004977753261798168</v>
+        <v>0.0004977753261799056</v>
       </c>
       <c r="H13" t="n">
         <v>23</v>
@@ -957,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008274528163536576</v>
+        <v>0.0008274528163537242</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -994,7 +994,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001371583978240276</v>
+        <v>0.001371583978240421</v>
       </c>
       <c r="H15" t="n">
         <v>12</v>
@@ -1031,7 +1031,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001298517390580056</v>
+        <v>0.001298517390580178</v>
       </c>
       <c r="H16" t="n">
         <v>13</v>
@@ -1068,7 +1068,7 @@
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001468179813453951</v>
+        <v>0.001468179813454051</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -1105,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>9.819472509370319e-05</v>
+        <v>9.819472509383642e-05</v>
       </c>
       <c r="H18" t="n">
         <v>34</v>
@@ -1142,7 +1142,7 @@
         <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004980251420097836</v>
+        <v>0.0004980251420098836</v>
       </c>
       <c r="H19" t="n">
         <v>22</v>
@@ -1179,7 +1179,7 @@
         <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008720295904171227</v>
+        <v>0.0008720295904172781</v>
       </c>
       <c r="H20" t="n">
         <v>18</v>
@@ -1216,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001628362567438035</v>
+        <v>0.000162836256743959</v>
       </c>
       <c r="H21" t="n">
         <v>33</v>
@@ -1253,7 +1253,7 @@
         <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0009362629714557257</v>
+        <v>0.0009362629714558479</v>
       </c>
       <c r="H22" t="n">
         <v>16</v>
@@ -1290,7 +1290,7 @@
         <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001203068630195558</v>
+        <v>0.001203068630195692</v>
       </c>
       <c r="H23" t="n">
         <v>14</v>
@@ -1327,7 +1327,7 @@
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004925881431233625</v>
+        <v>0.0004925881431234846</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0003255485579054196</v>
+        <v>-0.0003255485579052864</v>
       </c>
       <c r="H25" t="n">
         <v>45</v>
@@ -1401,7 +1401,7 @@
         <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0007376550915579871</v>
+        <v>0.0007376550915580537</v>
       </c>
       <c r="H26" t="n">
         <v>21</v>
@@ -1438,7 +1438,7 @@
         <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0002009597504211702</v>
+        <v>0.0002009597504212701</v>
       </c>
       <c r="H27" t="n">
         <v>31</v>
@@ -1475,7 +1475,7 @@
         <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0009174934430464688</v>
+        <v>0.0009174934430465686</v>
       </c>
       <c r="H28" t="n">
         <v>17</v>
@@ -1512,7 +1512,7 @@
         <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002911331417709828</v>
+        <v>0.000291133141771105</v>
       </c>
       <c r="H29" t="n">
         <v>28</v>
@@ -1549,7 +1549,7 @@
         <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0007384543079383077</v>
+        <v>0.0007384543079383854</v>
       </c>
       <c r="H30" t="n">
         <v>20</v>
@@ -1586,7 +1586,7 @@
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>7.085618611180067e-05</v>
+        <v>7.085618611188949e-05</v>
       </c>
       <c r="H31" t="n">
         <v>38</v>
@@ -1623,7 +1623,7 @@
         <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>0.000357700841847286</v>
+        <v>0.0003577008418473859</v>
       </c>
       <c r="H32" t="n">
         <v>27</v>
@@ -1660,7 +1660,7 @@
         <v>32</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002053057573325412</v>
+        <v>0.0002053057573326633</v>
       </c>
       <c r="H33" t="n">
         <v>30</v>
@@ -1697,7 +1697,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>7.759509954886612e-05</v>
+        <v>7.759509954898824e-05</v>
       </c>
       <c r="H34" t="n">
         <v>37</v>
@@ -1734,7 +1734,7 @@
         <v>22</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000282216434646343</v>
+        <v>0.0002822164346464873</v>
       </c>
       <c r="H35" t="n">
         <v>29</v>
@@ -1771,7 +1771,7 @@
         <v>24</v>
       </c>
       <c r="G36" t="n">
-        <v>1.256222595352741e-05</v>
+        <v>1.256222595363843e-05</v>
       </c>
       <c r="H36" t="n">
         <v>41</v>
@@ -1808,7 +1808,7 @@
         <v>40</v>
       </c>
       <c r="G37" t="n">
-        <v>9.124614615965143e-05</v>
+        <v>9.124614615974025e-05</v>
       </c>
       <c r="H37" t="n">
         <v>35</v>
@@ -1845,7 +1845,7 @@
         <v>36</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0001436746150003887</v>
+        <v>-0.0001436746150002888</v>
       </c>
       <c r="H38" t="n">
         <v>43</v>
@@ -1882,7 +1882,7 @@
         <v>37</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001678639336499033</v>
+        <v>0.0001678639336500143</v>
       </c>
       <c r="H39" t="n">
         <v>32</v>
@@ -1919,7 +1919,7 @@
         <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0001548931951984356</v>
+        <v>-0.0001548931951983246</v>
       </c>
       <c r="H40" t="n">
         <v>44</v>
@@ -1956,7 +1956,7 @@
         <v>39</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0004247586407363446</v>
+        <v>0.0004247586407364334</v>
       </c>
       <c r="H41" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0003737078159174123</v>
+        <v>0.0003737078159175455</v>
       </c>
       <c r="H42" t="n">
         <v>26</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>5.706794649815716e-05</v>
+        <v>5.706794649823488e-05</v>
       </c>
       <c r="H43" t="n">
         <v>39</v>
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>7.924446304518052e-05</v>
+        <v>7.924446304525823e-05</v>
       </c>
       <c r="H44" t="n">
         <v>36</v>
@@ -2104,7 +2104,7 @@
         <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>4.623479426105748e-05</v>
+        <v>4.62347942611685e-05</v>
       </c>
       <c r="H45" t="n">
         <v>40</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-7.880653300020856e-05</v>
+        <v>-7.880653300009754e-05</v>
       </c>
       <c r="H46" t="n">
         <v>42</v>
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1101356574972846</v>
+        <v>0.1101356574972847</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1256772075151103</v>
+        <v>0.1256772075151104</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2323,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09347421320710961</v>
+        <v>0.09347421320710972</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2360,7 +2360,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03042873337227854</v>
+        <v>0.0304287333723191</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -2397,7 +2397,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09126118549752468</v>
+        <v>0.09126118549752479</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01493386814484415</v>
+        <v>0.01493386814484425</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003854486980480232</v>
+        <v>0.003854486980480354</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -2508,7 +2508,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003231531657921127</v>
+        <v>0.003231531657921271</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -2545,7 +2545,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001199055892000522</v>
+        <v>0.001199055892000633</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -2582,7 +2582,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001994297951204127</v>
+        <v>0.001994297951204193</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -2619,7 +2619,7 @@
         <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002274792673663329</v>
+        <v>0.00227479267366345</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -2656,7 +2656,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004977753261798168</v>
+        <v>0.0004977753261799056</v>
       </c>
       <c r="H13" t="n">
         <v>23</v>
@@ -2693,7 +2693,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008274528163536576</v>
+        <v>0.0008274528163537242</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -2730,7 +2730,7 @@
         <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001371583978240276</v>
+        <v>0.001371583978240421</v>
       </c>
       <c r="H15" t="n">
         <v>12</v>
@@ -2767,7 +2767,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001298517390580056</v>
+        <v>0.001298517390580178</v>
       </c>
       <c r="H16" t="n">
         <v>13</v>
@@ -2804,7 +2804,7 @@
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001468179813453951</v>
+        <v>0.001468179813454051</v>
       </c>
       <c r="H17" t="n">
         <v>11</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>9.819472509370319e-05</v>
+        <v>9.819472509383642e-05</v>
       </c>
       <c r="H18" t="n">
         <v>34</v>
@@ -2878,7 +2878,7 @@
         <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004980251420097836</v>
+        <v>0.0004980251420098836</v>
       </c>
       <c r="H19" t="n">
         <v>22</v>
@@ -2915,7 +2915,7 @@
         <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008720295904171227</v>
+        <v>0.0008720295904172781</v>
       </c>
       <c r="H20" t="n">
         <v>18</v>
@@ -2952,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001628362567438035</v>
+        <v>0.000162836256743959</v>
       </c>
       <c r="H21" t="n">
         <v>33</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1256772075151103</v>
+        <v>0.1256772075151104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.016835141956822</v>
+        <v>0.01683514195682198</v>
       </c>
     </row>
     <row r="3">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1101356574972846</v>
+        <v>0.1101356574972847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01389034505627971</v>
+        <v>0.01389034505627969</v>
       </c>
     </row>
     <row r="4">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09347421320710961</v>
+        <v>0.09347421320710972</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01255366006353837</v>
+        <v>0.01255366006353835</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09126118549752468</v>
+        <v>0.09126118549752479</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01196930717930915</v>
+        <v>0.01196930717930913</v>
       </c>
     </row>
     <row r="6">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03042873337227854</v>
+        <v>0.0304287333723191</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00561072410377823</v>
+        <v>0.005610724103778292</v>
       </c>
     </row>
     <row r="7">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01493386814484415</v>
+        <v>0.01493386814484425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001401253832068063</v>
+        <v>0.00140125383206801</v>
       </c>
     </row>
     <row r="8">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.003854486980480232</v>
+        <v>0.003854486980480354</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00114503134251664</v>
+        <v>0.001145031342516599</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003231531657921127</v>
+        <v>0.003231531657921271</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001836698712560252</v>
+        <v>0.001836698712560209</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002274792673663329</v>
+        <v>0.00227479267366345</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001055469594516226</v>
+        <v>0.001055469594516245</v>
       </c>
     </row>
     <row r="11">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001994297951204127</v>
+        <v>0.001994297951204193</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0003342616438628584</v>
+        <v>0.0003342616438628758</v>
       </c>
     </row>
     <row r="12">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001468179813453951</v>
+        <v>0.001468179813454051</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0005916779556746199</v>
+        <v>0.0005916779556746105</v>
       </c>
     </row>
     <row r="13">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001371583978240276</v>
+        <v>0.001371583978240421</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008166311074285969</v>
+        <v>0.000816631107428605</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001298517390580056</v>
+        <v>0.001298517390580178</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004506783649985769</v>
+        <v>0.000450678364998555</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001203068630195558</v>
+        <v>0.001203068630195692</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0003205316879511416</v>
+        <v>0.0003205316879511447</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001199055892000522</v>
+        <v>0.001199055892000633</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004887136503401856</v>
+        <v>0.0004887136503402225</v>
       </c>
     </row>
     <row r="17">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0009362629714557257</v>
+        <v>0.0009362629714558479</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003387140973519214</v>
+        <v>0.0003387140973519308</v>
       </c>
     </row>
     <row r="18">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009174934430464688</v>
+        <v>0.0009174934430465686</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0003191821293565187</v>
+        <v>0.0003191821293565314</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0008720295904171227</v>
+        <v>0.0008720295904172781</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0005568892976235559</v>
+        <v>0.0005568892976235649</v>
       </c>
     </row>
     <row r="20">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0008274528163536576</v>
+        <v>0.0008274528163537242</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002367955934665124</v>
+        <v>0.0002367955934665113</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0007384543079383077</v>
+        <v>0.0007384543079383854</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000363259904288909</v>
+        <v>0.0003632599042889215</v>
       </c>
     </row>
     <row r="22">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0007376550915579871</v>
+        <v>0.0007376550915580537</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0006034839796972832</v>
+        <v>0.0006034839796972433</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004980251420097836</v>
+        <v>0.0004980251420098836</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0003977421186679194</v>
+        <v>0.0003977421186679232</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004977753261798168</v>
+        <v>0.0004977753261799056</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000352275326366964</v>
+        <v>0.00035227532636696</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004925881431233625</v>
+        <v>0.0004925881431234846</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000295463675228595</v>
+        <v>0.000295463675228583</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0004247586407363446</v>
+        <v>0.0004247586407364334</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001571132393653013</v>
+        <v>0.0001571132393652933</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003737078159174123</v>
+        <v>0.0003737078159175455</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001808774615860588</v>
+        <v>0.0001808774615860889</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.000357700841847286</v>
+        <v>0.0003577008418473859</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001254973962729597</v>
+        <v>0.0001254973962729336</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002911331417709828</v>
+        <v>0.000291133141771105</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0002061970932727222</v>
+        <v>0.0002061970932727106</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.000282216434646343</v>
+        <v>0.0002822164346464873</v>
       </c>
       <c r="D30" t="n">
-        <v>8.934620799273859e-05</v>
+        <v>8.934620799277309e-05</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002053057573325412</v>
+        <v>0.0002053057573326633</v>
       </c>
       <c r="D31" t="n">
-        <v>9.770461187118603e-05</v>
+        <v>9.770461187122551e-05</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002009597504211702</v>
+        <v>0.0002009597504212701</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001884746095905928</v>
+        <v>0.000188474609590588</v>
       </c>
     </row>
     <row r="33">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001678639336499033</v>
+        <v>0.0001678639336500143</v>
       </c>
       <c r="D33" t="n">
         <v>9.294777128641642e-05</v>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001628362567438035</v>
+        <v>0.000162836256743959</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0003491156731842648</v>
+        <v>0.0003491156731842745</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9.819472509370319e-05</v>
+        <v>9.819472509383642e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001433059865535373</v>
+        <v>0.000143305986553526</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9.124614615965143e-05</v>
+        <v>9.124614615974025e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0002304749620182342</v>
+        <v>0.0002304749620182028</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.924446304518052e-05</v>
+        <v>7.924446304525823e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>3.618811264371063e-05</v>
+        <v>3.618811264370233e-05</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7.759509954886612e-05</v>
+        <v>7.759509954898824e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.000231849276150103</v>
+        <v>0.0002318492761500915</v>
       </c>
     </row>
     <row r="39">
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7.085618611180067e-05</v>
+        <v>7.085618611188949e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001995517907383684</v>
+        <v>0.0001995517907383726</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.706794649815716e-05</v>
+        <v>5.706794649823488e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0002066002025036027</v>
+        <v>0.0002066002025036031</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.623479426105748e-05</v>
+        <v>4.62347942611685e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>2.488269909435861e-05</v>
+        <v>2.488269909438007e-05</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.256222595352741e-05</v>
+        <v>1.256222595363843e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>1.52615584480706e-05</v>
+        <v>1.52615584480679e-05</v>
       </c>
     </row>
     <row r="43">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-7.880653300020856e-05</v>
+        <v>-7.880653300009754e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>3.254056014070438e-05</v>
+        <v>3.254056014069544e-05</v>
       </c>
     </row>
     <row r="44">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0001436746150003887</v>
+        <v>-0.0001436746150002888</v>
       </c>
       <c r="D44" t="n">
-        <v>0.000151125619662043</v>
+        <v>0.0001511256196620485</v>
       </c>
     </row>
     <row r="45">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0001548931951984356</v>
+        <v>-0.0001548931951983246</v>
       </c>
       <c r="D45" t="n">
         <v>0.000215128270584015</v>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0003255485579054196</v>
+        <v>-0.0003255485579052864</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003965749009709757</v>
+        <v>0.0003965749009709647</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:50:39 UTC</t>
+          <t>2026-06-16 14:09:01 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_moisture.xlsx
+++ b/NN/reports/feature_importance_white_moisture.xlsx
@@ -513,7 +513,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08218501444886407</v>
+        <v>0.0821850144488642</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07162232356024348</v>
+        <v>0.07162232356024359</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04169327757849408</v>
+        <v>0.0416932775784942</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06790920862648733</v>
+        <v>0.06790920862648749</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403367403849274</v>
+        <v>0.01403367403853244</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06739341884767287</v>
+        <v>0.067393418847673</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01051785434685317</v>
+        <v>0.01051785434685324</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02109745917280919</v>
+        <v>0.02109745917280935</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002592940647117026</v>
+        <v>0.002592940647117081</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002420162849803742</v>
+        <v>0.002420162849803864</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -883,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009235213308433566</v>
+        <v>0.009235213308433677</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -920,7 +920,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006130076013525665</v>
+        <v>0.0006130076013526886</v>
       </c>
       <c r="H13" t="n">
         <v>18</v>
@@ -957,7 +957,7 @@
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005878733118516611</v>
+        <v>0.0005878733118517832</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -994,7 +994,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001027549058435584</v>
+        <v>0.001027549058435695</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -1031,7 +1031,7 @@
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000643083991171689</v>
+        <v>0.0006430839911718</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004073596329023266</v>
+        <v>0.0004073596329024154</v>
       </c>
       <c r="H17" t="n">
         <v>22</v>
@@ -1105,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005685433167898823</v>
+        <v>0.0005685433167899601</v>
       </c>
       <c r="H18" t="n">
         <v>20</v>
@@ -1142,7 +1142,7 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001139467083597867</v>
+        <v>0.001139467083598</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -1179,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>9.419230065841334e-05</v>
+        <v>9.419230065854656e-05</v>
       </c>
       <c r="H20" t="n">
         <v>41</v>
@@ -1216,7 +1216,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001651166613885435</v>
+        <v>0.001651166613885524</v>
       </c>
       <c r="H21" t="n">
         <v>12</v>
@@ -1253,7 +1253,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0002508035987043522</v>
+        <v>0.0002508035987044743</v>
       </c>
       <c r="H22" t="n">
         <v>29</v>
@@ -1290,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000282624680491228</v>
+        <v>0.0002826246804913279</v>
       </c>
       <c r="H23" t="n">
         <v>26</v>
@@ -1327,7 +1327,7 @@
         <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001103279195960572</v>
+        <v>0.001103279195960671</v>
       </c>
       <c r="H24" t="n">
         <v>14</v>
@@ -1364,7 +1364,7 @@
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000324552027778946</v>
+        <v>0.0003245520277790792</v>
       </c>
       <c r="H25" t="n">
         <v>25</v>
@@ -1401,7 +1401,7 @@
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0006761052879341589</v>
+        <v>0.0006761052879342034</v>
       </c>
       <c r="H26" t="n">
         <v>16</v>
@@ -1438,7 +1438,7 @@
         <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0001490539406376556</v>
+        <v>0.0001490539406377778</v>
       </c>
       <c r="H27" t="n">
         <v>34</v>
@@ -1475,7 +1475,7 @@
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0003997428023372551</v>
+        <v>-0.000399742802337133</v>
       </c>
       <c r="H28" t="n">
         <v>53</v>
@@ -1512,7 +1512,7 @@
         <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0005390648583790458</v>
+        <v>0.000539064858379168</v>
       </c>
       <c r="H29" t="n">
         <v>21</v>
@@ -1549,7 +1549,7 @@
         <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0001259134161154862</v>
+        <v>-0.000125913416115353</v>
       </c>
       <c r="H30" t="n">
         <v>49</v>
@@ -1586,7 +1586,7 @@
         <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003586824013083745</v>
+        <v>0.0003586824013084855</v>
       </c>
       <c r="H31" t="n">
         <v>23</v>
@@ -1623,7 +1623,7 @@
         <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002606351639304116</v>
+        <v>0.0002606351639305116</v>
       </c>
       <c r="H32" t="n">
         <v>27</v>
@@ -1660,7 +1660,7 @@
         <v>26</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.0001155041660675815</v>
+        <v>-0.0001155041660674816</v>
       </c>
       <c r="H33" t="n">
         <v>48</v>
@@ -1697,7 +1697,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0001113065420641712</v>
+        <v>0.0001113065420642601</v>
       </c>
       <c r="H34" t="n">
         <v>39</v>
@@ -1734,7 +1734,7 @@
         <v>37</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0001328263492481829</v>
+        <v>0.0001328263492482829</v>
       </c>
       <c r="H35" t="n">
         <v>35</v>
@@ -1771,7 +1771,7 @@
         <v>48</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002131281393188966</v>
+        <v>0.0002131281393190188</v>
       </c>
       <c r="H36" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>23</v>
       </c>
       <c r="G37" t="n">
-        <v>5.023641873698192e-05</v>
+        <v>5.023641873711515e-05</v>
       </c>
       <c r="H37" t="n">
         <v>44</v>
@@ -1845,7 +1845,7 @@
         <v>31</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0002475134427031844</v>
+        <v>0.0002475134427032954</v>
       </c>
       <c r="H38" t="n">
         <v>31</v>
@@ -1882,7 +1882,7 @@
         <v>44</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0003265698677199391</v>
+        <v>0.0003265698677200835</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1919,7 +1919,7 @@
         <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002586429798237311</v>
+        <v>0.0002586429798238643</v>
       </c>
       <c r="H40" t="n">
         <v>28</v>
@@ -1956,7 +1956,7 @@
         <v>38</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0001214486152627092</v>
+        <v>0.0001214486152628202</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -1993,7 +1993,7 @@
         <v>35</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001663068606845841</v>
+        <v>0.0001663068606846618</v>
       </c>
       <c r="H42" t="n">
         <v>33</v>
@@ -2030,7 +2030,7 @@
         <v>46</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001178070486130389</v>
+        <v>0.0001178070486131499</v>
       </c>
       <c r="H43" t="n">
         <v>38</v>
@@ -2067,7 +2067,7 @@
         <v>41</v>
       </c>
       <c r="G44" t="n">
-        <v>0.000249494465474287</v>
+        <v>0.000249494465474398</v>
       </c>
       <c r="H44" t="n">
         <v>30</v>
@@ -2104,7 +2104,7 @@
         <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.0001087868324821439</v>
+        <v>-0.0001087868324819996</v>
       </c>
       <c r="H45" t="n">
         <v>47</v>
@@ -2141,7 +2141,7 @@
         <v>30</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0001576675489359247</v>
+        <v>-0.0001576675489357693</v>
       </c>
       <c r="H46" t="n">
         <v>51</v>
@@ -2178,7 +2178,7 @@
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0001482889034667201</v>
+        <v>-0.0001482889034666091</v>
       </c>
       <c r="H47" t="n">
         <v>50</v>
@@ -2215,7 +2215,7 @@
         <v>49</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0001310618297204469</v>
+        <v>0.000131061829720569</v>
       </c>
       <c r="H48" t="n">
         <v>36</v>
@@ -2252,7 +2252,7 @@
         <v>39</v>
       </c>
       <c r="G49" t="n">
-        <v>4.006854685429939e-05</v>
+        <v>4.006854685438821e-05</v>
       </c>
       <c r="H49" t="n">
         <v>45</v>
@@ -2289,7 +2289,7 @@
         <v>50</v>
       </c>
       <c r="G50" t="n">
-        <v>8.039867084361774e-05</v>
+        <v>8.039867084371765e-05</v>
       </c>
       <c r="H50" t="n">
         <v>42</v>
@@ -2326,7 +2326,7 @@
         <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0001067792396374334</v>
+        <v>0.0001067792396375666</v>
       </c>
       <c r="H51" t="n">
         <v>40</v>
@@ -2363,7 +2363,7 @@
         <v>53</v>
       </c>
       <c r="G52" t="n">
-        <v>3.786355455392965e-05</v>
+        <v>3.786355455406287e-05</v>
       </c>
       <c r="H52" t="n">
         <v>46</v>
@@ -2400,7 +2400,7 @@
         <v>42</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.0001886907285609918</v>
+        <v>-0.0001886907285608697</v>
       </c>
       <c r="H53" t="n">
         <v>52</v>
@@ -2437,7 +2437,7 @@
         <v>51</v>
       </c>
       <c r="G54" t="n">
-        <v>7.768872334517063e-05</v>
+        <v>7.768872334529275e-05</v>
       </c>
       <c r="H54" t="n">
         <v>43</v>
@@ -2545,7 +2545,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08218501444886407</v>
+        <v>0.0821850144488642</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07162232356024348</v>
+        <v>0.07162232356024359</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04169327757849408</v>
+        <v>0.0416932775784942</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06790920862648733</v>
+        <v>0.06790920862648749</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01403367403849274</v>
+        <v>0.01403367403853244</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06739341884767287</v>
+        <v>0.067393418847673</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01051785434685317</v>
+        <v>0.01051785434685324</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -2804,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02109745917280919</v>
+        <v>0.02109745917280935</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002592940647117026</v>
+        <v>0.002592940647117081</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -2878,7 +2878,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002420162849803742</v>
+        <v>0.002420162849803864</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.009235213308433566</v>
+        <v>0.009235213308433677</v>
       </c>
       <c r="H12" t="n">
         <v>9</v>
@@ -2952,7 +2952,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0006130076013525665</v>
+        <v>0.0006130076013526886</v>
       </c>
       <c r="H13" t="n">
         <v>18</v>
@@ -2989,7 +2989,7 @@
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005878733118516611</v>
+        <v>0.0005878733118517832</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -3026,7 +3026,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001027549058435584</v>
+        <v>0.001027549058435695</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -3063,7 +3063,7 @@
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000643083991171689</v>
+        <v>0.0006430839911718</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004073596329023266</v>
+        <v>0.0004073596329024154</v>
       </c>
       <c r="H17" t="n">
         <v>22</v>
@@ -3137,7 +3137,7 @@
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005685433167898823</v>
+        <v>0.0005685433167899601</v>
       </c>
       <c r="H18" t="n">
         <v>20</v>
@@ -3174,7 +3174,7 @@
         <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001139467083597867</v>
+        <v>0.001139467083598</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
@@ -3211,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>9.419230065841334e-05</v>
+        <v>9.419230065854656e-05</v>
       </c>
       <c r="H20" t="n">
         <v>41</v>
@@ -3248,7 +3248,7 @@
         <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001651166613885435</v>
+        <v>0.001651166613885524</v>
       </c>
       <c r="H21" t="n">
         <v>12</v>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08218501444886407</v>
+        <v>0.0821850144488642</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01141698427518707</v>
+        <v>0.01141698427518706</v>
       </c>
     </row>
     <row r="3">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07162232356024348</v>
+        <v>0.07162232356024359</v>
       </c>
       <c r="D3" t="n">
         <v>0.01066177504862114</v>
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06790920862648733</v>
+        <v>0.06790920862648749</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01155419516112018</v>
+        <v>0.01155419516112015</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06739341884767287</v>
+        <v>0.067393418847673</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01008795011191899</v>
+        <v>0.01008795011191897</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04169327757849408</v>
+        <v>0.0416932775784942</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007623898478615744</v>
+        <v>0.007623898478615728</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02109745917280919</v>
+        <v>0.02109745917280935</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002949417463791526</v>
+        <v>0.002949417463791542</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01403367403849274</v>
+        <v>0.01403367403853244</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003242892811433474</v>
+        <v>0.003242892811432616</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01051785434685317</v>
+        <v>0.01051785434685324</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001076174911258317</v>
+        <v>0.001076174911258304</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009235213308433566</v>
+        <v>0.009235213308433677</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001324303416572418</v>
+        <v>0.00132430341657239</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002592940647117026</v>
+        <v>0.002592940647117081</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001015796128366716</v>
+        <v>0.001015796128366729</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002420162849803742</v>
+        <v>0.002420162849803864</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001109082392080396</v>
+        <v>0.001109082392080425</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001651166613885435</v>
+        <v>0.001651166613885524</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003524536365500912</v>
+        <v>0.0003524536365501352</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001139467083597867</v>
+        <v>0.001139467083598</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006208881009843724</v>
+        <v>0.0006208881009843705</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001103279195960572</v>
+        <v>0.001103279195960671</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002989338058261137</v>
+        <v>0.0002989338058261146</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001027549058435584</v>
+        <v>0.001027549058435695</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0007335523118561347</v>
+        <v>0.0007335523118561276</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0006761052879341589</v>
+        <v>0.0006761052879342034</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003901997982442598</v>
+        <v>0.0003901997982442713</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.000643083991171689</v>
+        <v>0.0006430839911718</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0002453005202181975</v>
+        <v>0.0002453005202181778</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006130076013525665</v>
+        <v>0.0006130076013526886</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003736264974452768</v>
+        <v>0.0003736264974452881</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005878733118516611</v>
+        <v>0.0005878733118517832</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002528177755247611</v>
+        <v>0.0002528177755247532</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0005685433167898823</v>
+        <v>0.0005685433167899601</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000134007416767915</v>
+        <v>0.0001340074167679311</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005390648583790458</v>
+        <v>0.000539064858379168</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0002809560041175864</v>
+        <v>0.0002809560041176197</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004073596329023266</v>
+        <v>0.0004073596329024154</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0004590466294514283</v>
+        <v>0.0004590466294514291</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0003586824013083745</v>
+        <v>0.0003586824013084855</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0002046317526306413</v>
+        <v>0.0002046317526306516</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003265698677199391</v>
+        <v>0.0003265698677200835</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001039044267277166</v>
+        <v>0.0001039044267277335</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.000324552027778946</v>
+        <v>0.0003245520277790792</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001704088168848761</v>
+        <v>0.0001704088168848554</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.000282624680491228</v>
+        <v>0.0002826246804913279</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002098198022891136</v>
+        <v>0.0002098198022891265</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0002606351639304116</v>
+        <v>0.0002606351639305116</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002308650490474039</v>
+        <v>0.0002308650490473911</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002586429798237311</v>
+        <v>0.0002586429798238643</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001351089986179497</v>
+        <v>0.000135108998617967</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002508035987043522</v>
+        <v>0.0002508035987044743</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0004872567478689483</v>
+        <v>0.0004872567478689331</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.000249494465474287</v>
+        <v>0.000249494465474398</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001399111512442106</v>
+        <v>0.0001399111512442163</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0002475134427031844</v>
+        <v>0.0002475134427032954</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001698229151201552</v>
+        <v>0.0001698229151201876</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002131281393188966</v>
+        <v>0.0002131281393190188</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0001764127558914285</v>
+        <v>0.0001764127558914425</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001663068606845841</v>
+        <v>0.0001663068606846618</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001967176820286803</v>
+        <v>0.0001967176820286429</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001490539406376556</v>
+        <v>0.0001490539406377778</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0003291413621283385</v>
+        <v>0.0003291413621283322</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0001328263492481829</v>
+        <v>0.0001328263492482829</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0001153909443612429</v>
+        <v>0.0001153909443612449</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001310618297204469</v>
+        <v>0.000131061829720569</v>
       </c>
       <c r="D37" t="n">
-        <v>3.08437602860138e-05</v>
+        <v>3.084376028602125e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001214486152627092</v>
+        <v>0.0001214486152628202</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0001039616189406464</v>
+        <v>0.0001039616189406716</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0001178070486130389</v>
+        <v>0.0001178070486131499</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001030200286077411</v>
+        <v>0.0001030200286077217</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0001113065420641712</v>
+        <v>0.0001113065420642601</v>
       </c>
       <c r="D40" t="n">
-        <v>7.446805171638141e-05</v>
+        <v>7.44680517163795e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0001067792396374334</v>
+        <v>0.0001067792396375666</v>
       </c>
       <c r="D41" t="n">
-        <v>6.09335495997491e-05</v>
+        <v>6.09335495997246e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9.419230065841334e-05</v>
+        <v>9.419230065854656e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001731845965015959</v>
+        <v>0.0001731845965016128</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8.039867084361774e-05</v>
+        <v>8.039867084371765e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>5.127768626722146e-05</v>
+        <v>5.127768626723446e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.768872334517063e-05</v>
+        <v>7.768872334529275e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>7.258119592487347e-05</v>
+        <v>7.258119592485825e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.023641873698192e-05</v>
+        <v>5.023641873711515e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002133286720324505</v>
+        <v>0.0002133286720324564</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.006854685429939e-05</v>
+        <v>4.006854685438821e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>1.572502966742423e-05</v>
+        <v>1.57250296673873e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.786355455392965e-05</v>
+        <v>3.786355455406287e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>1.556803031836518e-05</v>
+        <v>1.556803031836323e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.0001087868324821439</v>
+        <v>-0.0001087868324819996</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001130451266013766</v>
+        <v>0.0001130451266013906</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.0001155041660675815</v>
+        <v>-0.0001155041660674816</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0003357481855654086</v>
+        <v>0.0003357481855653691</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001259134161154862</v>
+        <v>-0.000125913416115353</v>
       </c>
       <c r="D50" t="n">
-        <v>0.000205731715837911</v>
+        <v>0.0002057317158378874</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001482889034667201</v>
+        <v>-0.0001482889034666091</v>
       </c>
       <c r="D51" t="n">
-        <v>8.77721560419013e-05</v>
+        <v>8.777215604188843e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001576675489359247</v>
+        <v>-0.0001576675489357693</v>
       </c>
       <c r="D52" t="n">
-        <v>0.000194874282553393</v>
+        <v>0.0001948742825534055</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0001886907285609918</v>
+        <v>-0.0001886907285608697</v>
       </c>
       <c r="D53" t="n">
-        <v>9.028791264926092e-05</v>
+        <v>9.028791264926733e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0003997428023372551</v>
+        <v>-0.000399742802337133</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003761327267890014</v>
+        <v>0.0003761327267890372</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:01:33 UTC</t>
+          <t>2026-06-16 19:27:02 UTC</t>
         </is>
       </c>
     </row>
